--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5359</v>
+        <v>1.5447</v>
       </c>
       <c r="E2" t="n">
-        <v>73.29000000000001</v>
+        <v>73.58</v>
       </c>
       <c r="F2" t="n">
         <v>1753.4</v>
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.4059</v>
+        <v>1.4114</v>
       </c>
       <c r="E3" t="n">
-        <v>67.92</v>
+        <v>68.13</v>
       </c>
       <c r="F3" t="n">
         <v>1722.4</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.383</v>
+        <v>1.3895</v>
       </c>
       <c r="E4" t="n">
-        <v>67.08</v>
+        <v>67.31</v>
       </c>
       <c r="F4" t="n">
         <v>1659.2</v>
@@ -611,10 +611,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.3666</v>
+        <v>1.376</v>
       </c>
       <c r="E5" t="n">
-        <v>66.59</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="F5" t="n">
         <v>1661</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.3481</v>
+        <v>1.3554</v>
       </c>
       <c r="E6" t="n">
-        <v>65.45</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="F6" t="n">
         <v>1645.2</v>
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.3456</v>
+        <v>1.3151</v>
       </c>
       <c r="E7" t="n">
-        <v>65.41</v>
+        <v>64.16</v>
       </c>
       <c r="F7" t="n">
         <v>1590.5</v>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.3017</v>
+        <v>1.2962</v>
       </c>
       <c r="E8" t="n">
-        <v>63.79</v>
+        <v>63.49</v>
       </c>
       <c r="F8" t="n">
         <v>1562.7</v>
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.2351</v>
+        <v>1.2396</v>
       </c>
       <c r="E9" t="n">
-        <v>60.39</v>
+        <v>60.67</v>
       </c>
       <c r="F9" t="n">
         <v>1677.7</v>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.2129</v>
+        <v>1.2181</v>
       </c>
       <c r="E10" t="n">
-        <v>60.65</v>
+        <v>60.89</v>
       </c>
       <c r="F10" t="n">
         <v>1583.6</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.2087</v>
+        <v>1.2171</v>
       </c>
       <c r="E11" t="n">
-        <v>59.86</v>
+        <v>60.18</v>
       </c>
       <c r="F11" t="n">
         <v>1546.7</v>
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.1859</v>
+        <v>1.197</v>
       </c>
       <c r="E12" t="n">
-        <v>58.73</v>
+        <v>59.12</v>
       </c>
       <c r="F12" t="n">
         <v>1507.1</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.1538</v>
+        <v>1.1259</v>
       </c>
       <c r="E13" t="n">
-        <v>57.64</v>
+        <v>56.4</v>
       </c>
       <c r="F13" t="n">
         <v>1572.5</v>
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.112</v>
+        <v>1.118</v>
       </c>
       <c r="E14" t="n">
-        <v>55.77</v>
+        <v>56.04</v>
       </c>
       <c r="F14" t="n">
         <v>1579.2</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.078</v>
+        <v>1.0848</v>
       </c>
       <c r="E15" t="n">
-        <v>54.37</v>
+        <v>54.65</v>
       </c>
       <c r="F15" t="n">
         <v>1538</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.0679</v>
+        <v>1.0581</v>
       </c>
       <c r="E16" t="n">
-        <v>54.05</v>
+        <v>53.63</v>
       </c>
       <c r="F16" t="n">
         <v>1507.8</v>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.0153</v>
+        <v>1.0209</v>
       </c>
       <c r="E17" t="n">
-        <v>51.63</v>
+        <v>51.93</v>
       </c>
       <c r="F17" t="n">
         <v>1507.6</v>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9403</v>
+        <v>0.9447</v>
       </c>
       <c r="E18" t="n">
-        <v>48.35</v>
+        <v>48.58</v>
       </c>
       <c r="F18" t="n">
         <v>1525.5</v>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9439</v>
       </c>
       <c r="E19" t="n">
-        <v>48</v>
+        <v>48.34</v>
       </c>
       <c r="F19" t="n">
         <v>1457.9</v>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.9054</v>
+        <v>0.9104</v>
       </c>
       <c r="E20" t="n">
-        <v>46.99</v>
+        <v>47.19</v>
       </c>
       <c r="F20" t="n">
         <v>1477.3</v>
@@ -1254,32 +1254,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1610612741</v>
+        <v>1610612755</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8502999999999999</v>
+        <v>0.8859</v>
       </c>
       <c r="E21" t="n">
-        <v>43.69</v>
+        <v>46.09</v>
       </c>
       <c r="F21" t="n">
-        <v>1381</v>
+        <v>1470.3</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.27</v>
+        <v>-0.58</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8</v>
+        <v>-3.68</v>
       </c>
       <c r="I21" t="n">
         <v>155</v>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.8452</v>
+        <v>0.8489</v>
       </c>
       <c r="E22" t="n">
-        <v>43.57</v>
+        <v>43.7</v>
       </c>
       <c r="F22" t="n">
         <v>1384.3</v>
@@ -1336,32 +1336,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1610612755</v>
+        <v>1610612741</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.822</v>
+        <v>0.7973</v>
       </c>
       <c r="E23" t="n">
-        <v>42.89</v>
+        <v>41.42</v>
       </c>
       <c r="F23" t="n">
-        <v>1470.3</v>
+        <v>1381</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.58</v>
+        <v>-3.27</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.68</v>
+        <v>-0.8</v>
       </c>
       <c r="I23" t="n">
         <v>155</v>
@@ -1377,32 +1377,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1610612749</v>
+        <v>1610612763</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6697</v>
+        <v>0.6671</v>
       </c>
       <c r="E24" t="n">
-        <v>35.18</v>
+        <v>34.55</v>
       </c>
       <c r="F24" t="n">
-        <v>1403.5</v>
+        <v>1391.5</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.93</v>
+        <v>-5.48</v>
       </c>
       <c r="H24" t="n">
-        <v>-13.1</v>
+        <v>-15.14</v>
       </c>
       <c r="I24" t="n">
         <v>155</v>
@@ -1418,32 +1418,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6647</v>
+        <v>0.6296</v>
       </c>
       <c r="E25" t="n">
-        <v>34.41</v>
+        <v>33.52</v>
       </c>
       <c r="F25" t="n">
-        <v>1391.5</v>
+        <v>1371.4</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.48</v>
+        <v>-5.28</v>
       </c>
       <c r="H25" t="n">
-        <v>-15.14</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="I25" t="n">
         <v>155</v>
@@ -1459,32 +1459,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1610612742</v>
+        <v>1610612749</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6341</v>
+        <v>0.6247</v>
       </c>
       <c r="E26" t="n">
-        <v>33.68</v>
+        <v>32.72</v>
       </c>
       <c r="F26" t="n">
-        <v>1371.4</v>
+        <v>1403.5</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.28</v>
+        <v>-5.93</v>
       </c>
       <c r="H26" t="n">
-        <v>-9.470000000000001</v>
+        <v>-13.1</v>
       </c>
       <c r="I26" t="n">
         <v>155</v>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.5899</v>
+        <v>0.5909</v>
       </c>
       <c r="E27" t="n">
-        <v>30.06</v>
+        <v>30.17</v>
       </c>
       <c r="F27" t="n">
         <v>1316.3</v>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.5898</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>30.23</v>
+        <v>30.31</v>
       </c>
       <c r="F28" t="n">
         <v>1316.6</v>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.5756</v>
+        <v>0.5766</v>
       </c>
       <c r="E29" t="n">
-        <v>29.81</v>
+        <v>29.86</v>
       </c>
       <c r="F29" t="n">
         <v>1332</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.5127</v>
       </c>
       <c r="E30" t="n">
-        <v>25.79</v>
+        <v>25.83</v>
       </c>
       <c r="F30" t="n">
         <v>1296.5</v>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.507</v>
+        <v>0.5092</v>
       </c>
       <c r="E31" t="n">
-        <v>24.73</v>
+        <v>24.88</v>
       </c>
       <c r="F31" t="n">
         <v>1258</v>

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -503,11 +503,11 @@
         <v>12.54</v>
       </c>
       <c r="I2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -544,11 +544,11 @@
         <v>12.63</v>
       </c>
       <c r="I3" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -585,11 +585,11 @@
         <v>3.84</v>
       </c>
       <c r="I4" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -626,11 +626,11 @@
         <v>10.01</v>
       </c>
       <c r="I5" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -667,11 +667,11 @@
         <v>5.49</v>
       </c>
       <c r="I6" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -708,11 +708,11 @@
         <v>4.75</v>
       </c>
       <c r="I7" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -749,11 +749,11 @@
         <v>7.86</v>
       </c>
       <c r="I8" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -790,11 +790,11 @@
         <v>7.68</v>
       </c>
       <c r="I9" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -831,11 +831,11 @@
         <v>12.06</v>
       </c>
       <c r="I10" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -872,11 +872,11 @@
         <v>5.48</v>
       </c>
       <c r="I11" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -913,11 +913,11 @@
         <v>15.77</v>
       </c>
       <c r="I12" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -954,11 +954,11 @@
         <v>0.15</v>
       </c>
       <c r="I13" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -995,11 +995,11 @@
         <v>-5.7</v>
       </c>
       <c r="I14" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1036,11 +1036,11 @@
         <v>2.97</v>
       </c>
       <c r="I15" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1077,11 +1077,11 @@
         <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1118,11 +1118,11 @@
         <v>3.21</v>
       </c>
       <c r="I17" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1159,11 +1159,11 @@
         <v>-0.24</v>
       </c>
       <c r="I18" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1200,11 +1200,11 @@
         <v>7.01</v>
       </c>
       <c r="I19" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1241,11 +1241,11 @@
         <v>-6.12</v>
       </c>
       <c r="I20" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1282,11 +1282,11 @@
         <v>-3.68</v>
       </c>
       <c r="I21" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1323,11 +1323,11 @@
         <v>4.18</v>
       </c>
       <c r="I22" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1364,11 +1364,11 @@
         <v>-0.8</v>
       </c>
       <c r="I23" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1405,11 +1405,11 @@
         <v>-15.14</v>
       </c>
       <c r="I24" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1446,11 +1446,11 @@
         <v>-9.470000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1487,11 +1487,11 @@
         <v>-13.1</v>
       </c>
       <c r="I26" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1528,11 +1528,11 @@
         <v>-4.93</v>
       </c>
       <c r="I27" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -1569,11 +1569,11 @@
         <v>-6.11</v>
       </c>
       <c r="I28" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -1610,11 +1610,11 @@
         <v>-11.31</v>
       </c>
       <c r="I29" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -1651,11 +1651,11 @@
         <v>-12.91</v>
       </c>
       <c r="I30" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -1692,11 +1692,11 @@
         <v>-16.77</v>
       </c>
       <c r="I31" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="K31" t="n">

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5447</v>
+        <v>1.5616</v>
       </c>
       <c r="E2" t="n">
-        <v>73.58</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="F2" t="n">
         <v>1753.4</v>
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.4114</v>
+        <v>1.4191</v>
       </c>
       <c r="E3" t="n">
-        <v>68.13</v>
+        <v>68.22</v>
       </c>
       <c r="F3" t="n">
         <v>1722.4</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.3895</v>
+        <v>1.3976</v>
       </c>
       <c r="E4" t="n">
-        <v>67.31</v>
+        <v>67.64</v>
       </c>
       <c r="F4" t="n">
         <v>1659.2</v>
@@ -611,10 +611,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.376</v>
+        <v>1.3865</v>
       </c>
       <c r="E5" t="n">
-        <v>66.95999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="F5" t="n">
         <v>1661</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.3554</v>
+        <v>1.3618</v>
       </c>
       <c r="E6" t="n">
-        <v>65.70999999999999</v>
+        <v>66.28</v>
       </c>
       <c r="F6" t="n">
         <v>1645.2</v>
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.3151</v>
+        <v>1.3239</v>
       </c>
       <c r="E7" t="n">
-        <v>64.16</v>
+        <v>64.67</v>
       </c>
       <c r="F7" t="n">
         <v>1590.5</v>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.2962</v>
+        <v>1.3054</v>
       </c>
       <c r="E8" t="n">
-        <v>63.49</v>
+        <v>63.89</v>
       </c>
       <c r="F8" t="n">
         <v>1562.7</v>
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.2396</v>
+        <v>1.2435</v>
       </c>
       <c r="E9" t="n">
-        <v>60.67</v>
+        <v>60.71</v>
       </c>
       <c r="F9" t="n">
         <v>1677.7</v>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.2181</v>
+        <v>1.2294</v>
       </c>
       <c r="E10" t="n">
-        <v>60.89</v>
+        <v>60.79</v>
       </c>
       <c r="F10" t="n">
         <v>1583.6</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.2171</v>
+        <v>1.2156</v>
       </c>
       <c r="E11" t="n">
-        <v>60.18</v>
+        <v>60.27</v>
       </c>
       <c r="F11" t="n">
         <v>1546.7</v>
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.197</v>
+        <v>1.2095</v>
       </c>
       <c r="E12" t="n">
-        <v>59.12</v>
+        <v>59.92</v>
       </c>
       <c r="F12" t="n">
         <v>1507.1</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.1259</v>
+        <v>1.1602</v>
       </c>
       <c r="E13" t="n">
-        <v>56.4</v>
+        <v>57.96</v>
       </c>
       <c r="F13" t="n">
         <v>1572.5</v>
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.118</v>
+        <v>1.1072</v>
       </c>
       <c r="E14" t="n">
-        <v>56.04</v>
+        <v>55.67</v>
       </c>
       <c r="F14" t="n">
         <v>1579.2</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.0848</v>
+        <v>1.0833</v>
       </c>
       <c r="E15" t="n">
-        <v>54.65</v>
+        <v>54.74</v>
       </c>
       <c r="F15" t="n">
         <v>1538</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.0581</v>
+        <v>1.0621</v>
       </c>
       <c r="E16" t="n">
-        <v>53.63</v>
+        <v>53.79</v>
       </c>
       <c r="F16" t="n">
         <v>1507.8</v>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.0209</v>
+        <v>1.0161</v>
       </c>
       <c r="E17" t="n">
-        <v>51.93</v>
+        <v>51.82</v>
       </c>
       <c r="F17" t="n">
         <v>1507.6</v>
@@ -1131,32 +1131,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1610612753</v>
+        <v>1610612757</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9447</v>
+        <v>0.9422</v>
       </c>
       <c r="E18" t="n">
-        <v>48.58</v>
+        <v>48.24</v>
       </c>
       <c r="F18" t="n">
-        <v>1525.5</v>
+        <v>1457.9</v>
       </c>
       <c r="G18" t="n">
-        <v>0.35</v>
+        <v>-1.79</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.24</v>
+        <v>7.01</v>
       </c>
       <c r="I18" t="n">
         <v>156</v>
@@ -1172,32 +1172,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1610612757</v>
+        <v>1610612753</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.9439</v>
+        <v>0.9337</v>
       </c>
       <c r="E19" t="n">
-        <v>48.34</v>
+        <v>48.16</v>
       </c>
       <c r="F19" t="n">
-        <v>1457.9</v>
+        <v>1525.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.79</v>
+        <v>0.35</v>
       </c>
       <c r="H19" t="n">
-        <v>7.01</v>
+        <v>-0.24</v>
       </c>
       <c r="I19" t="n">
         <v>156</v>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.9104</v>
+        <v>0.9059</v>
       </c>
       <c r="E20" t="n">
-        <v>47.19</v>
+        <v>46.92</v>
       </c>
       <c r="F20" t="n">
         <v>1477.3</v>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8859</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>46.09</v>
+        <v>45.46</v>
       </c>
       <c r="F21" t="n">
         <v>1470.3</v>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.8489</v>
+        <v>0.8458</v>
       </c>
       <c r="E22" t="n">
-        <v>43.7</v>
+        <v>43.65</v>
       </c>
       <c r="F22" t="n">
         <v>1384.3</v>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.7973</v>
+        <v>0.7968</v>
       </c>
       <c r="E23" t="n">
-        <v>41.42</v>
+        <v>41.44</v>
       </c>
       <c r="F23" t="n">
         <v>1381</v>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6671</v>
+        <v>0.6422</v>
       </c>
       <c r="E24" t="n">
-        <v>34.55</v>
+        <v>33.78</v>
       </c>
       <c r="F24" t="n">
         <v>1391.5</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6296</v>
+        <v>0.6288</v>
       </c>
       <c r="E25" t="n">
-        <v>33.52</v>
+        <v>33.13</v>
       </c>
       <c r="F25" t="n">
         <v>1371.4</v>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6247</v>
+        <v>0.6214</v>
       </c>
       <c r="E26" t="n">
-        <v>32.72</v>
+        <v>32.48</v>
       </c>
       <c r="F26" t="n">
         <v>1403.5</v>
@@ -1500,32 +1500,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.5909</v>
+        <v>0.5856</v>
       </c>
       <c r="E27" t="n">
-        <v>30.17</v>
+        <v>30.22</v>
       </c>
       <c r="F27" t="n">
-        <v>1316.3</v>
+        <v>1316.6</v>
       </c>
       <c r="G27" t="n">
-        <v>-7.62</v>
+        <v>-10.06</v>
       </c>
       <c r="H27" t="n">
-        <v>-4.93</v>
+        <v>-6.11</v>
       </c>
       <c r="I27" t="n">
         <v>156</v>
@@ -1541,32 +1541,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.5808</v>
       </c>
       <c r="E28" t="n">
-        <v>30.31</v>
+        <v>30.12</v>
       </c>
       <c r="F28" t="n">
-        <v>1316.6</v>
+        <v>1316.3</v>
       </c>
       <c r="G28" t="n">
-        <v>-10.06</v>
+        <v>-7.62</v>
       </c>
       <c r="H28" t="n">
-        <v>-6.11</v>
+        <v>-4.93</v>
       </c>
       <c r="I28" t="n">
         <v>156</v>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.5766</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>29.86</v>
+        <v>29.42</v>
       </c>
       <c r="F29" t="n">
         <v>1332</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5127</v>
+        <v>0.5062</v>
       </c>
       <c r="E30" t="n">
-        <v>25.83</v>
+        <v>25.42</v>
       </c>
       <c r="F30" t="n">
         <v>1296.5</v>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.5092</v>
+        <v>0.4893</v>
       </c>
       <c r="E31" t="n">
-        <v>24.88</v>
+        <v>24.21</v>
       </c>
       <c r="F31" t="n">
         <v>1258</v>

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5616</v>
+        <v>1.5488</v>
       </c>
       <c r="E2" t="n">
-        <v>73.79000000000001</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>1753.4</v>
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.4191</v>
+        <v>1.4606</v>
       </c>
       <c r="E3" t="n">
-        <v>68.22</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="F3" t="n">
         <v>1722.4</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.3976</v>
+        <v>1.3894</v>
       </c>
       <c r="E4" t="n">
-        <v>67.64</v>
+        <v>67.27</v>
       </c>
       <c r="F4" t="n">
         <v>1659.2</v>
@@ -611,10 +611,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.3865</v>
+        <v>1.3751</v>
       </c>
       <c r="E5" t="n">
-        <v>67.2</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="F5" t="n">
         <v>1661</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.3618</v>
+        <v>1.3681</v>
       </c>
       <c r="E6" t="n">
-        <v>66.28</v>
+        <v>66.5</v>
       </c>
       <c r="F6" t="n">
         <v>1645.2</v>
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.3239</v>
+        <v>1.3554</v>
       </c>
       <c r="E7" t="n">
-        <v>64.67</v>
+        <v>65.92</v>
       </c>
       <c r="F7" t="n">
         <v>1590.5</v>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.3054</v>
+        <v>1.3115</v>
       </c>
       <c r="E8" t="n">
-        <v>63.89</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="F8" t="n">
         <v>1562.7</v>
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.2435</v>
+        <v>1.2363</v>
       </c>
       <c r="E9" t="n">
-        <v>60.71</v>
+        <v>60.37</v>
       </c>
       <c r="F9" t="n">
         <v>1677.7</v>
@@ -803,32 +803,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1610612766</v>
+        <v>1610612746</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.2294</v>
+        <v>1.2203</v>
       </c>
       <c r="E10" t="n">
-        <v>60.79</v>
+        <v>60.47</v>
       </c>
       <c r="F10" t="n">
-        <v>1583.6</v>
+        <v>1546.7</v>
       </c>
       <c r="G10" t="n">
-        <v>3.93</v>
+        <v>2.28</v>
       </c>
       <c r="H10" t="n">
-        <v>12.06</v>
+        <v>5.48</v>
       </c>
       <c r="I10" t="n">
         <v>156</v>
@@ -844,32 +844,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1610612746</v>
+        <v>1610612766</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.2156</v>
+        <v>1.2186</v>
       </c>
       <c r="E11" t="n">
-        <v>60.27</v>
+        <v>60.34</v>
       </c>
       <c r="F11" t="n">
-        <v>1546.7</v>
+        <v>1583.6</v>
       </c>
       <c r="G11" t="n">
-        <v>2.28</v>
+        <v>3.93</v>
       </c>
       <c r="H11" t="n">
-        <v>5.48</v>
+        <v>12.06</v>
       </c>
       <c r="I11" t="n">
         <v>156</v>
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.2095</v>
+        <v>1.1962</v>
       </c>
       <c r="E12" t="n">
-        <v>59.92</v>
+        <v>59.44</v>
       </c>
       <c r="F12" t="n">
         <v>1507.1</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.1602</v>
+        <v>1.1488</v>
       </c>
       <c r="E13" t="n">
-        <v>57.96</v>
+        <v>57.47</v>
       </c>
       <c r="F13" t="n">
         <v>1572.5</v>
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.1072</v>
+        <v>1.095</v>
       </c>
       <c r="E14" t="n">
-        <v>55.67</v>
+        <v>55.2</v>
       </c>
       <c r="F14" t="n">
         <v>1579.2</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.0833</v>
+        <v>1.0732</v>
       </c>
       <c r="E15" t="n">
-        <v>54.74</v>
+        <v>54.32</v>
       </c>
       <c r="F15" t="n">
         <v>1538</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.0621</v>
+        <v>1.0658</v>
       </c>
       <c r="E16" t="n">
-        <v>53.79</v>
+        <v>53.97</v>
       </c>
       <c r="F16" t="n">
         <v>1507.8</v>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.0161</v>
+        <v>1.0076</v>
       </c>
       <c r="E17" t="n">
-        <v>51.82</v>
+        <v>51.4</v>
       </c>
       <c r="F17" t="n">
         <v>1507.6</v>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9422</v>
+        <v>0.9337</v>
       </c>
       <c r="E18" t="n">
-        <v>48.24</v>
+        <v>47.82</v>
       </c>
       <c r="F18" t="n">
         <v>1457.9</v>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.9337</v>
+        <v>0.9296</v>
       </c>
       <c r="E19" t="n">
-        <v>48.16</v>
+        <v>47.95</v>
       </c>
       <c r="F19" t="n">
         <v>1525.5</v>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.9059</v>
+        <v>0.8968</v>
       </c>
       <c r="E20" t="n">
-        <v>46.92</v>
+        <v>46.5</v>
       </c>
       <c r="F20" t="n">
         <v>1477.3</v>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8715000000000001</v>
+        <v>0.8655</v>
       </c>
       <c r="E21" t="n">
-        <v>45.46</v>
+        <v>45.13</v>
       </c>
       <c r="F21" t="n">
         <v>1470.3</v>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.8458</v>
+        <v>0.8376</v>
       </c>
       <c r="E22" t="n">
-        <v>43.65</v>
+        <v>43.25</v>
       </c>
       <c r="F22" t="n">
         <v>1384.3</v>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.7968</v>
+        <v>0.791</v>
       </c>
       <c r="E23" t="n">
-        <v>41.44</v>
+        <v>41.1</v>
       </c>
       <c r="F23" t="n">
         <v>1381</v>
@@ -1377,32 +1377,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1610612763</v>
+        <v>1610612749</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6422</v>
+        <v>0.6596</v>
       </c>
       <c r="E24" t="n">
-        <v>33.78</v>
+        <v>34.59</v>
       </c>
       <c r="F24" t="n">
-        <v>1391.5</v>
+        <v>1403.5</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.48</v>
+        <v>-5.93</v>
       </c>
       <c r="H24" t="n">
-        <v>-15.14</v>
+        <v>-13.1</v>
       </c>
       <c r="I24" t="n">
         <v>156</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6288</v>
+        <v>0.6481</v>
       </c>
       <c r="E25" t="n">
-        <v>33.13</v>
+        <v>34.03</v>
       </c>
       <c r="F25" t="n">
         <v>1371.4</v>
@@ -1459,32 +1459,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1610612749</v>
+        <v>1610612763</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6214</v>
+        <v>0.6262</v>
       </c>
       <c r="E26" t="n">
-        <v>32.48</v>
+        <v>32.94</v>
       </c>
       <c r="F26" t="n">
-        <v>1403.5</v>
+        <v>1391.5</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.93</v>
+        <v>-5.48</v>
       </c>
       <c r="H26" t="n">
-        <v>-13.1</v>
+        <v>-15.14</v>
       </c>
       <c r="I26" t="n">
         <v>156</v>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.5856</v>
+        <v>0.5857</v>
       </c>
       <c r="E27" t="n">
         <v>30.22</v>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.5808</v>
+        <v>0.5853</v>
       </c>
       <c r="E28" t="n">
-        <v>30.12</v>
+        <v>30.38</v>
       </c>
       <c r="F28" t="n">
         <v>1316.3</v>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5689</v>
       </c>
       <c r="E29" t="n">
-        <v>29.42</v>
+        <v>29.5</v>
       </c>
       <c r="F29" t="n">
         <v>1332</v>
@@ -1623,32 +1623,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5062</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>25.42</v>
+        <v>24.89</v>
       </c>
       <c r="F30" t="n">
-        <v>1296.5</v>
+        <v>1258</v>
       </c>
       <c r="G30" t="n">
-        <v>-10.38</v>
+        <v>-11.61</v>
       </c>
       <c r="H30" t="n">
-        <v>-12.91</v>
+        <v>-16.77</v>
       </c>
       <c r="I30" t="n">
         <v>156</v>
@@ -1664,32 +1664,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.4893</v>
+        <v>0.4998</v>
       </c>
       <c r="E31" t="n">
-        <v>24.21</v>
+        <v>24.75</v>
       </c>
       <c r="F31" t="n">
-        <v>1258</v>
+        <v>1296.5</v>
       </c>
       <c r="G31" t="n">
-        <v>-11.61</v>
+        <v>-10.38</v>
       </c>
       <c r="H31" t="n">
-        <v>-16.77</v>
+        <v>-12.91</v>
       </c>
       <c r="I31" t="n">
         <v>156</v>

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5488</v>
+        <v>1.5444</v>
       </c>
       <c r="E2" t="n">
-        <v>73.31999999999999</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1753.4</v>
+        <v>1756.9</v>
       </c>
       <c r="G2" t="n">
-        <v>11.57</v>
+        <v>10.95</v>
       </c>
       <c r="H2" t="n">
-        <v>12.54</v>
+        <v>10.7</v>
       </c>
       <c r="I2" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -529,26 +529,26 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.4606</v>
+        <v>1.4841</v>
       </c>
       <c r="E3" t="n">
-        <v>70.06999999999999</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>1722.4</v>
+        <v>1728.8</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>8.48</v>
       </c>
       <c r="H3" t="n">
-        <v>12.63</v>
+        <v>14.04</v>
       </c>
       <c r="I3" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -570,26 +570,26 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.3894</v>
+        <v>1.3782</v>
       </c>
       <c r="E4" t="n">
-        <v>67.27</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>1659.2</v>
+        <v>1652.3</v>
       </c>
       <c r="G4" t="n">
-        <v>6.72</v>
+        <v>6.88</v>
       </c>
       <c r="H4" t="n">
-        <v>3.84</v>
+        <v>1.69</v>
       </c>
       <c r="I4" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -611,26 +611,26 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.3751</v>
+        <v>1.37</v>
       </c>
       <c r="E5" t="n">
-        <v>66.70999999999999</v>
+        <v>66.55</v>
       </c>
       <c r="F5" t="n">
-        <v>1661</v>
+        <v>1661.9</v>
       </c>
       <c r="G5" t="n">
-        <v>7.19</v>
+        <v>6.62</v>
       </c>
       <c r="H5" t="n">
-        <v>10.01</v>
+        <v>9.4</v>
       </c>
       <c r="I5" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -639,39 +639,39 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1610612739</v>
+        <v>1610612743</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.3681</v>
+        <v>1.3589</v>
       </c>
       <c r="E6" t="n">
-        <v>66.5</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1645.2</v>
+        <v>1593.9</v>
       </c>
       <c r="G6" t="n">
-        <v>4.44</v>
+        <v>4.49</v>
       </c>
       <c r="H6" t="n">
-        <v>5.49</v>
+        <v>4.97</v>
       </c>
       <c r="I6" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -680,39 +680,39 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612743</v>
+        <v>1610612739</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.3554</v>
+        <v>1.3534</v>
       </c>
       <c r="E7" t="n">
-        <v>65.92</v>
+        <v>65.84</v>
       </c>
       <c r="F7" t="n">
-        <v>1590.5</v>
+        <v>1647.3</v>
       </c>
       <c r="G7" t="n">
-        <v>4.43</v>
+        <v>3.83</v>
       </c>
       <c r="H7" t="n">
-        <v>4.75</v>
+        <v>2.85</v>
       </c>
       <c r="I7" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -734,26 +734,26 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.3115</v>
+        <v>1.3084</v>
       </c>
       <c r="E8" t="n">
-        <v>64.20999999999999</v>
+        <v>64.12</v>
       </c>
       <c r="F8" t="n">
-        <v>1562.7</v>
+        <v>1560.4</v>
       </c>
       <c r="G8" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.86</v>
+        <v>8.82</v>
       </c>
       <c r="I8" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -775,26 +775,26 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.2363</v>
+        <v>1.262</v>
       </c>
       <c r="E9" t="n">
-        <v>60.37</v>
+        <v>61.4</v>
       </c>
       <c r="F9" t="n">
-        <v>1677.7</v>
+        <v>1673.8</v>
       </c>
       <c r="G9" t="n">
-        <v>6.81</v>
+        <v>7.23</v>
       </c>
       <c r="H9" t="n">
-        <v>7.68</v>
+        <v>11.54</v>
       </c>
       <c r="I9" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -816,26 +816,26 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.2203</v>
+        <v>1.2564</v>
       </c>
       <c r="E10" t="n">
-        <v>60.47</v>
+        <v>62.01</v>
       </c>
       <c r="F10" t="n">
-        <v>1546.7</v>
+        <v>1550.4</v>
       </c>
       <c r="G10" t="n">
-        <v>2.28</v>
+        <v>2.57</v>
       </c>
       <c r="H10" t="n">
-        <v>5.48</v>
+        <v>8.49</v>
       </c>
       <c r="I10" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -857,26 +857,26 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.2186</v>
+        <v>1.2116</v>
       </c>
       <c r="E11" t="n">
-        <v>60.34</v>
+        <v>60.06</v>
       </c>
       <c r="F11" t="n">
-        <v>1583.6</v>
+        <v>1585.8</v>
       </c>
       <c r="G11" t="n">
-        <v>3.93</v>
+        <v>3.51</v>
       </c>
       <c r="H11" t="n">
-        <v>12.06</v>
+        <v>10.08</v>
       </c>
       <c r="I11" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -898,26 +898,26 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.1962</v>
+        <v>1.1791</v>
       </c>
       <c r="E12" t="n">
-        <v>59.44</v>
+        <v>58.7</v>
       </c>
       <c r="F12" t="n">
-        <v>1507.1</v>
+        <v>1511.4</v>
       </c>
       <c r="G12" t="n">
-        <v>2.37</v>
+        <v>1.54</v>
       </c>
       <c r="H12" t="n">
-        <v>15.77</v>
+        <v>11.63</v>
       </c>
       <c r="I12" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -939,26 +939,26 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.1488</v>
+        <v>1.1535</v>
       </c>
       <c r="E13" t="n">
-        <v>57.47</v>
+        <v>57.69</v>
       </c>
       <c r="F13" t="n">
-        <v>1572.5</v>
+        <v>1579.3</v>
       </c>
       <c r="G13" t="n">
-        <v>4.58</v>
+        <v>4.25</v>
       </c>
       <c r="H13" t="n">
-        <v>0.15</v>
+        <v>-0.97</v>
       </c>
       <c r="I13" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -980,26 +980,26 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.095</v>
+        <v>1.0936</v>
       </c>
       <c r="E14" t="n">
-        <v>55.2</v>
+        <v>55.18</v>
       </c>
       <c r="F14" t="n">
-        <v>1579.2</v>
+        <v>1575</v>
       </c>
       <c r="G14" t="n">
-        <v>3.34</v>
+        <v>3.52</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.7</v>
+        <v>-5.11</v>
       </c>
       <c r="I14" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1021,26 +1021,26 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.0732</v>
+        <v>1.0807</v>
       </c>
       <c r="E15" t="n">
-        <v>54.32</v>
+        <v>54.61</v>
       </c>
       <c r="F15" t="n">
-        <v>1538</v>
+        <v>1531.6</v>
       </c>
       <c r="G15" t="n">
-        <v>2.02</v>
+        <v>2.77</v>
       </c>
       <c r="H15" t="n">
-        <v>2.97</v>
+        <v>1.91</v>
       </c>
       <c r="I15" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1062,26 +1062,26 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.0658</v>
+        <v>1.0194</v>
       </c>
       <c r="E16" t="n">
-        <v>53.97</v>
+        <v>51.99</v>
       </c>
       <c r="F16" t="n">
-        <v>1507.8</v>
+        <v>1510.3</v>
       </c>
       <c r="G16" t="n">
-        <v>1.77</v>
+        <v>0.6</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>-1.02</v>
       </c>
       <c r="I16" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1103,26 +1103,26 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.0076</v>
+        <v>1.0094</v>
       </c>
       <c r="E17" t="n">
-        <v>51.4</v>
+        <v>51.54</v>
       </c>
       <c r="F17" t="n">
         <v>1507.6</v>
       </c>
       <c r="G17" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="H17" t="n">
         <v>3.21</v>
       </c>
       <c r="I17" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1144,26 +1144,26 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9337</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>47.82</v>
+        <v>48.64</v>
       </c>
       <c r="F18" t="n">
-        <v>1457.9</v>
+        <v>1460.4</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.79</v>
+        <v>-1.3</v>
       </c>
       <c r="H18" t="n">
-        <v>7.01</v>
+        <v>8.58</v>
       </c>
       <c r="I18" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1185,26 +1185,26 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.9296</v>
+        <v>0.9242</v>
       </c>
       <c r="E19" t="n">
-        <v>47.95</v>
+        <v>47.66</v>
       </c>
       <c r="F19" t="n">
-        <v>1525.5</v>
+        <v>1523.4</v>
       </c>
       <c r="G19" t="n">
-        <v>0.35</v>
+        <v>0.64</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.24</v>
+        <v>-1.67</v>
       </c>
       <c r="I19" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1226,26 +1226,26 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.8968</v>
+        <v>0.9084</v>
       </c>
       <c r="E20" t="n">
-        <v>46.5</v>
+        <v>47.04</v>
       </c>
       <c r="F20" t="n">
-        <v>1477.3</v>
+        <v>1479.6</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H20" t="n">
-        <v>-6.12</v>
+        <v>-6.05</v>
       </c>
       <c r="I20" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1267,26 +1267,26 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8655</v>
+        <v>0.883</v>
       </c>
       <c r="E21" t="n">
-        <v>45.13</v>
+        <v>45.85</v>
       </c>
       <c r="F21" t="n">
-        <v>1470.3</v>
+        <v>1466.8</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.58</v>
+        <v>0.3</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.68</v>
+        <v>-1.84</v>
       </c>
       <c r="I21" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1308,26 +1308,26 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.8376</v>
+        <v>0.8252</v>
       </c>
       <c r="E22" t="n">
-        <v>43.25</v>
+        <v>42.67</v>
       </c>
       <c r="F22" t="n">
-        <v>1384.3</v>
+        <v>1383.4</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.5</v>
+        <v>-3.9</v>
       </c>
       <c r="H22" t="n">
-        <v>4.18</v>
+        <v>3.1</v>
       </c>
       <c r="I22" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1349,26 +1349,26 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.791</v>
+        <v>0.7611</v>
       </c>
       <c r="E23" t="n">
-        <v>41.1</v>
+        <v>39.73</v>
       </c>
       <c r="F23" t="n">
-        <v>1381</v>
+        <v>1385.2</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.27</v>
+        <v>-3.86</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8</v>
+        <v>-5.05</v>
       </c>
       <c r="I23" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1390,26 +1390,26 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6596</v>
+        <v>0.6535</v>
       </c>
       <c r="E24" t="n">
-        <v>34.59</v>
+        <v>34.23</v>
       </c>
       <c r="F24" t="n">
-        <v>1403.5</v>
+        <v>1399.8</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.93</v>
+        <v>-5.87</v>
       </c>
       <c r="H24" t="n">
-        <v>-13.1</v>
+        <v>-14.47</v>
       </c>
       <c r="I24" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1418,39 +1418,39 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6481</v>
+        <v>0.6352</v>
       </c>
       <c r="E25" t="n">
-        <v>34.03</v>
+        <v>33.33</v>
       </c>
       <c r="F25" t="n">
-        <v>1371.4</v>
+        <v>1387.3</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.28</v>
+        <v>-5.43</v>
       </c>
       <c r="H25" t="n">
-        <v>-9.470000000000001</v>
+        <v>-16.21</v>
       </c>
       <c r="I25" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1459,39 +1459,39 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6262</v>
+        <v>0.6252</v>
       </c>
       <c r="E26" t="n">
-        <v>32.94</v>
+        <v>32.86</v>
       </c>
       <c r="F26" t="n">
-        <v>1391.5</v>
+        <v>1369.1</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.48</v>
+        <v>-5.43</v>
       </c>
       <c r="H26" t="n">
-        <v>-15.14</v>
+        <v>-10.25</v>
       </c>
       <c r="I26" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1513,26 +1513,26 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.5857</v>
+        <v>0.594</v>
       </c>
       <c r="E27" t="n">
-        <v>30.22</v>
+        <v>30.67</v>
       </c>
       <c r="F27" t="n">
-        <v>1316.6</v>
+        <v>1314.4</v>
       </c>
       <c r="G27" t="n">
-        <v>-10.06</v>
+        <v>-9.42</v>
       </c>
       <c r="H27" t="n">
-        <v>-6.11</v>
+        <v>-5.56</v>
       </c>
       <c r="I27" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -1554,26 +1554,26 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.5853</v>
+        <v>0.574</v>
       </c>
       <c r="E28" t="n">
-        <v>30.38</v>
+        <v>29.75</v>
       </c>
       <c r="F28" t="n">
-        <v>1316.3</v>
+        <v>1313.8</v>
       </c>
       <c r="G28" t="n">
-        <v>-7.62</v>
+        <v>-7.92</v>
       </c>
       <c r="H28" t="n">
-        <v>-4.93</v>
+        <v>-6.75</v>
       </c>
       <c r="I28" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -1595,26 +1595,26 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.5689</v>
+        <v>0.5727</v>
       </c>
       <c r="E29" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="F29" t="n">
-        <v>1332</v>
+        <v>1336.3</v>
       </c>
       <c r="G29" t="n">
-        <v>-7.74</v>
+        <v>-8.16</v>
       </c>
       <c r="H29" t="n">
-        <v>-11.31</v>
+        <v>-10.1</v>
       </c>
       <c r="I29" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -1636,26 +1636,26 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.5162</v>
       </c>
       <c r="E30" t="n">
-        <v>24.89</v>
+        <v>25.85</v>
       </c>
       <c r="F30" t="n">
-        <v>1258</v>
+        <v>1257.1</v>
       </c>
       <c r="G30" t="n">
-        <v>-11.61</v>
+        <v>-10.46</v>
       </c>
       <c r="H30" t="n">
-        <v>-16.77</v>
+        <v>-12.31</v>
       </c>
       <c r="I30" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -1677,26 +1677,26 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.4998</v>
+        <v>0.5121</v>
       </c>
       <c r="E31" t="n">
-        <v>24.75</v>
+        <v>25.4</v>
       </c>
       <c r="F31" t="n">
-        <v>1296.5</v>
+        <v>1294</v>
       </c>
       <c r="G31" t="n">
-        <v>-10.38</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>-12.91</v>
+        <v>-11.51</v>
       </c>
       <c r="I31" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K31" t="n">

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5444</v>
+        <v>1.5569</v>
       </c>
       <c r="E2" t="n">
-        <v>73.15000000000001</v>
+        <v>73.69</v>
       </c>
       <c r="F2" t="n">
         <v>1756.9</v>
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.4841</v>
+        <v>1.4818</v>
       </c>
       <c r="E3" t="n">
-        <v>70.98999999999999</v>
+        <v>70.88</v>
       </c>
       <c r="F3" t="n">
         <v>1728.8</v>
@@ -557,32 +557,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1610612738</v>
+        <v>1610612739</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.3782</v>
+        <v>1.3871</v>
       </c>
       <c r="E4" t="n">
-        <v>66.84999999999999</v>
+        <v>67.17</v>
       </c>
       <c r="F4" t="n">
-        <v>1652.3</v>
+        <v>1647.3</v>
       </c>
       <c r="G4" t="n">
-        <v>6.88</v>
+        <v>3.83</v>
       </c>
       <c r="H4" t="n">
-        <v>1.69</v>
+        <v>2.85</v>
       </c>
       <c r="I4" t="n">
         <v>157</v>
@@ -611,10 +611,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.37</v>
+        <v>1.3597</v>
       </c>
       <c r="E5" t="n">
-        <v>66.55</v>
+        <v>66.17</v>
       </c>
       <c r="F5" t="n">
         <v>1661.9</v>
@@ -639,32 +639,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1610612743</v>
+        <v>1610612738</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1.3589</v>
       </c>
       <c r="E6" t="n">
-        <v>66.04000000000001</v>
+        <v>66.08</v>
       </c>
       <c r="F6" t="n">
-        <v>1593.9</v>
+        <v>1652.3</v>
       </c>
       <c r="G6" t="n">
-        <v>4.49</v>
+        <v>6.88</v>
       </c>
       <c r="H6" t="n">
-        <v>4.97</v>
+        <v>1.69</v>
       </c>
       <c r="I6" t="n">
         <v>157</v>
@@ -680,32 +680,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612739</v>
+        <v>1610612743</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.3534</v>
+        <v>1.3517</v>
       </c>
       <c r="E7" t="n">
-        <v>65.84</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>1647.3</v>
+        <v>1593.9</v>
       </c>
       <c r="G7" t="n">
-        <v>3.83</v>
+        <v>4.49</v>
       </c>
       <c r="H7" t="n">
-        <v>2.85</v>
+        <v>4.97</v>
       </c>
       <c r="I7" t="n">
         <v>157</v>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.3084</v>
+        <v>1.2974</v>
       </c>
       <c r="E8" t="n">
-        <v>64.12</v>
+        <v>63.73</v>
       </c>
       <c r="F8" t="n">
         <v>1560.4</v>
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.262</v>
+        <v>1.2814</v>
       </c>
       <c r="E9" t="n">
-        <v>61.4</v>
+        <v>62.23</v>
       </c>
       <c r="F9" t="n">
         <v>1673.8</v>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.2564</v>
+        <v>1.2588</v>
       </c>
       <c r="E10" t="n">
-        <v>62.01</v>
+        <v>62.13</v>
       </c>
       <c r="F10" t="n">
         <v>1550.4</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.2116</v>
+        <v>1.2092</v>
       </c>
       <c r="E11" t="n">
-        <v>60.06</v>
+        <v>59.99</v>
       </c>
       <c r="F11" t="n">
         <v>1585.8</v>
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.1791</v>
+        <v>1.1847</v>
       </c>
       <c r="E12" t="n">
-        <v>58.7</v>
+        <v>58.98</v>
       </c>
       <c r="F12" t="n">
         <v>1511.4</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.1535</v>
+        <v>1.1326</v>
       </c>
       <c r="E13" t="n">
-        <v>57.69</v>
+        <v>56.79</v>
       </c>
       <c r="F13" t="n">
         <v>1579.3</v>
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.0936</v>
+        <v>1.0841</v>
       </c>
       <c r="E14" t="n">
-        <v>55.18</v>
+        <v>54.8</v>
       </c>
       <c r="F14" t="n">
         <v>1575</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.0807</v>
+        <v>1.077</v>
       </c>
       <c r="E15" t="n">
-        <v>54.61</v>
+        <v>54.45</v>
       </c>
       <c r="F15" t="n">
         <v>1531.6</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.0194</v>
+        <v>1.0172</v>
       </c>
       <c r="E16" t="n">
-        <v>51.99</v>
+        <v>51.89</v>
       </c>
       <c r="F16" t="n">
         <v>1510.3</v>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.0094</v>
+        <v>1.0103</v>
       </c>
       <c r="E17" t="n">
-        <v>51.54</v>
+        <v>51.57</v>
       </c>
       <c r="F17" t="n">
         <v>1507.6</v>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.9534</v>
       </c>
       <c r="E18" t="n">
-        <v>48.64</v>
+        <v>48.7</v>
       </c>
       <c r="F18" t="n">
         <v>1460.4</v>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.9242</v>
+        <v>0.9265</v>
       </c>
       <c r="E19" t="n">
-        <v>47.66</v>
+        <v>47.77</v>
       </c>
       <c r="F19" t="n">
         <v>1523.4</v>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.9084</v>
+        <v>0.8812</v>
       </c>
       <c r="E20" t="n">
-        <v>47.04</v>
+        <v>45.77</v>
       </c>
       <c r="F20" t="n">
         <v>1479.6</v>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.883</v>
+        <v>0.8759</v>
       </c>
       <c r="E21" t="n">
-        <v>45.85</v>
+        <v>45.53</v>
       </c>
       <c r="F21" t="n">
         <v>1466.8</v>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.8252</v>
+        <v>0.8437</v>
       </c>
       <c r="E22" t="n">
-        <v>42.67</v>
+        <v>43.44</v>
       </c>
       <c r="F22" t="n">
         <v>1383.4</v>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.7611</v>
+        <v>0.7631</v>
       </c>
       <c r="E23" t="n">
-        <v>39.73</v>
+        <v>39.85</v>
       </c>
       <c r="F23" t="n">
         <v>1385.2</v>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6535</v>
+        <v>0.6592</v>
       </c>
       <c r="E24" t="n">
-        <v>34.23</v>
+        <v>34.5</v>
       </c>
       <c r="F24" t="n">
         <v>1399.8</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6352</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>33.33</v>
+        <v>34.29</v>
       </c>
       <c r="F25" t="n">
         <v>1387.3</v>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6252</v>
+        <v>0.6325</v>
       </c>
       <c r="E26" t="n">
-        <v>32.86</v>
+        <v>33.22</v>
       </c>
       <c r="F26" t="n">
         <v>1369.1</v>
@@ -1500,32 +1500,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.594</v>
+        <v>0.5782</v>
       </c>
       <c r="E27" t="n">
-        <v>30.67</v>
+        <v>29.91</v>
       </c>
       <c r="F27" t="n">
-        <v>1314.4</v>
+        <v>1313.8</v>
       </c>
       <c r="G27" t="n">
-        <v>-9.42</v>
+        <v>-7.92</v>
       </c>
       <c r="H27" t="n">
-        <v>-5.56</v>
+        <v>-6.75</v>
       </c>
       <c r="I27" t="n">
         <v>157</v>
@@ -1541,32 +1541,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.574</v>
+        <v>0.5773</v>
       </c>
       <c r="E28" t="n">
-        <v>29.75</v>
+        <v>29.72</v>
       </c>
       <c r="F28" t="n">
-        <v>1313.8</v>
+        <v>1314.4</v>
       </c>
       <c r="G28" t="n">
-        <v>-7.92</v>
+        <v>-9.42</v>
       </c>
       <c r="H28" t="n">
-        <v>-6.75</v>
+        <v>-5.56</v>
       </c>
       <c r="I28" t="n">
         <v>157</v>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.5727</v>
+        <v>0.5734</v>
       </c>
       <c r="E29" t="n">
-        <v>29.6</v>
+        <v>29.55</v>
       </c>
       <c r="F29" t="n">
         <v>1336.3</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5162</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>25.85</v>
+        <v>25.8</v>
       </c>
       <c r="F30" t="n">
         <v>1257.1</v>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.5121</v>
+        <v>0.5154</v>
       </c>
       <c r="E31" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="F31" t="n">
         <v>1294</v>

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5569</v>
+        <v>1.5539</v>
       </c>
       <c r="E2" t="n">
-        <v>73.69</v>
+        <v>73.53</v>
       </c>
       <c r="F2" t="n">
-        <v>1756.9</v>
+        <v>1750.8</v>
       </c>
       <c r="G2" t="n">
-        <v>10.95</v>
+        <v>11.34</v>
       </c>
       <c r="H2" t="n">
-        <v>10.7</v>
+        <v>11.71</v>
       </c>
       <c r="I2" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.4818</v>
+        <v>1.4802</v>
       </c>
       <c r="E3" t="n">
-        <v>70.88</v>
+        <v>70.78</v>
       </c>
       <c r="F3" t="n">
         <v>1728.8</v>
@@ -544,11 +544,11 @@
         <v>14.04</v>
       </c>
       <c r="I3" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -570,26 +570,26 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.3871</v>
+        <v>1.3883</v>
       </c>
       <c r="E4" t="n">
-        <v>67.17</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>1647.3</v>
+        <v>1637.7</v>
       </c>
       <c r="G4" t="n">
-        <v>3.83</v>
+        <v>4.44</v>
       </c>
       <c r="H4" t="n">
-        <v>2.85</v>
+        <v>4.62</v>
       </c>
       <c r="I4" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -598,39 +598,39 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1610612752</v>
+        <v>1610612738</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.3597</v>
+        <v>1.3851</v>
       </c>
       <c r="E5" t="n">
-        <v>66.17</v>
+        <v>67.06</v>
       </c>
       <c r="F5" t="n">
-        <v>1661.9</v>
+        <v>1658.4</v>
       </c>
       <c r="G5" t="n">
-        <v>6.62</v>
+        <v>6.9</v>
       </c>
       <c r="H5" t="n">
-        <v>9.4</v>
+        <v>5.32</v>
       </c>
       <c r="I5" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -639,39 +639,39 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1610612738</v>
+        <v>1610612743</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.3589</v>
+        <v>1.3768</v>
       </c>
       <c r="E6" t="n">
-        <v>66.08</v>
+        <v>66.83</v>
       </c>
       <c r="F6" t="n">
-        <v>1652.3</v>
+        <v>1594.9</v>
       </c>
       <c r="G6" t="n">
-        <v>6.88</v>
+        <v>4.37</v>
       </c>
       <c r="H6" t="n">
-        <v>1.69</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -680,39 +680,39 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612743</v>
+        <v>1610612752</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.3517</v>
+        <v>1.3607</v>
       </c>
       <c r="E7" t="n">
-        <v>65.79000000000001</v>
+        <v>66.14</v>
       </c>
       <c r="F7" t="n">
-        <v>1593.9</v>
+        <v>1661.9</v>
       </c>
       <c r="G7" t="n">
-        <v>4.49</v>
+        <v>6.62</v>
       </c>
       <c r="H7" t="n">
-        <v>4.97</v>
+        <v>9.4</v>
       </c>
       <c r="I7" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -734,26 +734,26 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.2974</v>
+        <v>1.3352</v>
       </c>
       <c r="E8" t="n">
-        <v>63.73</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>1560.4</v>
+        <v>1561.9</v>
       </c>
       <c r="G8" t="n">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="H8" t="n">
-        <v>8.82</v>
+        <v>10.22</v>
       </c>
       <c r="I8" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.2814</v>
+        <v>1.2852</v>
       </c>
       <c r="E9" t="n">
-        <v>62.23</v>
+        <v>62.41</v>
       </c>
       <c r="F9" t="n">
         <v>1673.8</v>
@@ -790,11 +790,11 @@
         <v>11.54</v>
       </c>
       <c r="I9" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -816,26 +816,26 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.2588</v>
+        <v>1.2544</v>
       </c>
       <c r="E10" t="n">
-        <v>62.13</v>
+        <v>61.96</v>
       </c>
       <c r="F10" t="n">
-        <v>1550.4</v>
+        <v>1555.7</v>
       </c>
       <c r="G10" t="n">
-        <v>2.57</v>
+        <v>2.23</v>
       </c>
       <c r="H10" t="n">
-        <v>8.49</v>
+        <v>8.01</v>
       </c>
       <c r="I10" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.2092</v>
+        <v>1.2102</v>
       </c>
       <c r="E11" t="n">
-        <v>59.99</v>
+        <v>59.97</v>
       </c>
       <c r="F11" t="n">
         <v>1585.8</v>
@@ -872,11 +872,11 @@
         <v>10.08</v>
       </c>
       <c r="I11" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -898,26 +898,26 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.1847</v>
+        <v>1.1732</v>
       </c>
       <c r="E12" t="n">
-        <v>58.98</v>
+        <v>58.44</v>
       </c>
       <c r="F12" t="n">
-        <v>1511.4</v>
+        <v>1517.6</v>
       </c>
       <c r="G12" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="H12" t="n">
-        <v>11.63</v>
+        <v>9.59</v>
       </c>
       <c r="I12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -926,39 +926,39 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.1326</v>
+        <v>1.0875</v>
       </c>
       <c r="E13" t="n">
-        <v>56.79</v>
+        <v>54.99</v>
       </c>
       <c r="F13" t="n">
-        <v>1579.3</v>
+        <v>1572</v>
       </c>
       <c r="G13" t="n">
-        <v>4.25</v>
+        <v>3.68</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.97</v>
+        <v>-4.53</v>
       </c>
       <c r="I13" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -967,39 +967,39 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.0841</v>
+        <v>1.0816</v>
       </c>
       <c r="E14" t="n">
-        <v>54.8</v>
+        <v>54.64</v>
       </c>
       <c r="F14" t="n">
-        <v>1575</v>
+        <v>1579.3</v>
       </c>
       <c r="G14" t="n">
-        <v>3.52</v>
+        <v>4.25</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.11</v>
+        <v>-0.97</v>
       </c>
       <c r="I14" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1021,26 +1021,26 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.077</v>
+        <v>1.0496</v>
       </c>
       <c r="E15" t="n">
-        <v>54.45</v>
+        <v>53.28</v>
       </c>
       <c r="F15" t="n">
-        <v>1531.6</v>
+        <v>1541.1</v>
       </c>
       <c r="G15" t="n">
-        <v>2.77</v>
+        <v>2.05</v>
       </c>
       <c r="H15" t="n">
-        <v>1.91</v>
+        <v>-1.27</v>
       </c>
       <c r="I15" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1062,26 +1062,26 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.0172</v>
+        <v>1.025</v>
       </c>
       <c r="E16" t="n">
-        <v>51.89</v>
+        <v>52.32</v>
       </c>
       <c r="F16" t="n">
-        <v>1510.3</v>
+        <v>1505</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6</v>
+        <v>1.52</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.02</v>
+        <v>1.17</v>
       </c>
       <c r="I16" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.0103</v>
+        <v>1.0144</v>
       </c>
       <c r="E17" t="n">
-        <v>51.57</v>
+        <v>51.8</v>
       </c>
       <c r="F17" t="n">
         <v>1507.6</v>
@@ -1118,11 +1118,11 @@
         <v>3.21</v>
       </c>
       <c r="I17" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1131,39 +1131,39 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1610612757</v>
+        <v>1610612753</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9534</v>
+        <v>0.9331</v>
       </c>
       <c r="E18" t="n">
-        <v>48.7</v>
+        <v>48.06</v>
       </c>
       <c r="F18" t="n">
-        <v>1460.4</v>
+        <v>1523.4</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.3</v>
+        <v>0.64</v>
       </c>
       <c r="H18" t="n">
-        <v>8.58</v>
+        <v>-1.67</v>
       </c>
       <c r="I18" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1172,39 +1172,39 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1610612753</v>
+        <v>1610612757</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.9265</v>
+        <v>0.9152</v>
       </c>
       <c r="E19" t="n">
-        <v>47.77</v>
+        <v>46.91</v>
       </c>
       <c r="F19" t="n">
-        <v>1523.4</v>
+        <v>1464.5</v>
       </c>
       <c r="G19" t="n">
-        <v>0.64</v>
+        <v>-1.89</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.67</v>
+        <v>7.89</v>
       </c>
       <c r="I19" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1226,26 +1226,26 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.8812</v>
+        <v>0.9072</v>
       </c>
       <c r="E20" t="n">
-        <v>45.77</v>
+        <v>47.1</v>
       </c>
       <c r="F20" t="n">
-        <v>1479.6</v>
+        <v>1480.4</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="H20" t="n">
-        <v>-6.05</v>
+        <v>-4.85</v>
       </c>
       <c r="I20" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8759</v>
+        <v>0.8809</v>
       </c>
       <c r="E21" t="n">
-        <v>45.53</v>
+        <v>45.8</v>
       </c>
       <c r="F21" t="n">
         <v>1466.8</v>
@@ -1282,11 +1282,11 @@
         <v>-1.84</v>
       </c>
       <c r="I21" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1308,26 +1308,26 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.8437</v>
+        <v>0.8294</v>
       </c>
       <c r="E22" t="n">
-        <v>43.44</v>
+        <v>42.92</v>
       </c>
       <c r="F22" t="n">
-        <v>1383.4</v>
+        <v>1381.9</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.9</v>
+        <v>-4.02</v>
       </c>
       <c r="H22" t="n">
-        <v>3.1</v>
+        <v>1.14</v>
       </c>
       <c r="I22" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1349,26 +1349,26 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.7631</v>
+        <v>0.7509</v>
       </c>
       <c r="E23" t="n">
-        <v>39.85</v>
+        <v>39.31</v>
       </c>
       <c r="F23" t="n">
-        <v>1385.2</v>
+        <v>1382.4</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.86</v>
+        <v>-4.05</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.05</v>
+        <v>-5.84</v>
       </c>
       <c r="I23" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6592</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>34.5</v>
+        <v>34.85</v>
       </c>
       <c r="F24" t="n">
         <v>1399.8</v>
@@ -1405,11 +1405,11 @@
         <v>-14.47</v>
       </c>
       <c r="I24" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1431,26 +1431,26 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.6637</v>
       </c>
       <c r="E25" t="n">
-        <v>34.29</v>
+        <v>34.75</v>
       </c>
       <c r="F25" t="n">
-        <v>1387.3</v>
+        <v>1384.6</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.43</v>
+        <v>-4.92</v>
       </c>
       <c r="H25" t="n">
-        <v>-16.21</v>
+        <v>-16.42</v>
       </c>
       <c r="I25" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1472,26 +1472,26 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6325</v>
+        <v>0.6481</v>
       </c>
       <c r="E26" t="n">
-        <v>33.22</v>
+        <v>34.05</v>
       </c>
       <c r="F26" t="n">
-        <v>1369.1</v>
+        <v>1368.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.43</v>
+        <v>-5.1</v>
       </c>
       <c r="H26" t="n">
-        <v>-10.25</v>
+        <v>-7.7</v>
       </c>
       <c r="I26" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1500,39 +1500,39 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1610612762</v>
+        <v>1610612754</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.5782</v>
+        <v>0.5853</v>
       </c>
       <c r="E27" t="n">
-        <v>29.91</v>
+        <v>30.19</v>
       </c>
       <c r="F27" t="n">
-        <v>1313.8</v>
+        <v>1334.8</v>
       </c>
       <c r="G27" t="n">
-        <v>-7.92</v>
+        <v>-8.02</v>
       </c>
       <c r="H27" t="n">
-        <v>-6.75</v>
+        <v>-8.99</v>
       </c>
       <c r="I27" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -1541,39 +1541,39 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.5773</v>
+        <v>0.5806</v>
       </c>
       <c r="E28" t="n">
-        <v>29.72</v>
+        <v>29.98</v>
       </c>
       <c r="F28" t="n">
-        <v>1314.4</v>
+        <v>1310.4</v>
       </c>
       <c r="G28" t="n">
-        <v>-9.42</v>
+        <v>-7.57</v>
       </c>
       <c r="H28" t="n">
-        <v>-5.56</v>
+        <v>-7.76</v>
       </c>
       <c r="I28" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -1582,39 +1582,39 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1610612754</v>
+        <v>1610612758</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.5734</v>
+        <v>0.5568</v>
       </c>
       <c r="E29" t="n">
-        <v>29.55</v>
+        <v>28.53</v>
       </c>
       <c r="F29" t="n">
-        <v>1336.3</v>
+        <v>1314.4</v>
       </c>
       <c r="G29" t="n">
-        <v>-8.16</v>
+        <v>-9.42</v>
       </c>
       <c r="H29" t="n">
-        <v>-10.1</v>
+        <v>-5.56</v>
       </c>
       <c r="I29" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -1636,26 +1636,26 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.5179</v>
       </c>
       <c r="E30" t="n">
-        <v>25.8</v>
+        <v>25.85</v>
       </c>
       <c r="F30" t="n">
-        <v>1257.1</v>
+        <v>1260.5</v>
       </c>
       <c r="G30" t="n">
-        <v>-10.46</v>
+        <v>-10.81</v>
       </c>
       <c r="H30" t="n">
-        <v>-12.31</v>
+        <v>-12.37</v>
       </c>
       <c r="I30" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -1677,26 +1677,26 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.5154</v>
+        <v>0.5052</v>
       </c>
       <c r="E31" t="n">
-        <v>25.6</v>
+        <v>25.12</v>
       </c>
       <c r="F31" t="n">
-        <v>1294</v>
+        <v>1293.2</v>
       </c>
       <c r="G31" t="n">
-        <v>-9.970000000000001</v>
+        <v>-10.5</v>
       </c>
       <c r="H31" t="n">
-        <v>-11.51</v>
+        <v>-14.37</v>
       </c>
       <c r="I31" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K31" t="n">

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5539</v>
+        <v>1.551</v>
       </c>
       <c r="E2" t="n">
-        <v>73.53</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="F2" t="n">
         <v>1750.8</v>
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.4802</v>
+        <v>1.4672</v>
       </c>
       <c r="E3" t="n">
-        <v>70.78</v>
+        <v>70.33</v>
       </c>
       <c r="F3" t="n">
         <v>1728.8</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.3883</v>
+        <v>1.3767</v>
       </c>
       <c r="E4" t="n">
-        <v>67.23999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F4" t="n">
         <v>1637.7</v>
@@ -611,10 +611,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.3851</v>
+        <v>1.3756</v>
       </c>
       <c r="E5" t="n">
-        <v>67.06</v>
+        <v>67.03</v>
       </c>
       <c r="F5" t="n">
         <v>1658.4</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.3768</v>
+        <v>1.369</v>
       </c>
       <c r="E6" t="n">
-        <v>66.83</v>
+        <v>66.58</v>
       </c>
       <c r="F6" t="n">
         <v>1594.9</v>
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.3607</v>
+        <v>1.3481</v>
       </c>
       <c r="E7" t="n">
-        <v>66.14</v>
+        <v>65.69</v>
       </c>
       <c r="F7" t="n">
         <v>1661.9</v>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.3352</v>
+        <v>1.3269</v>
       </c>
       <c r="E8" t="n">
-        <v>65.20999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="F8" t="n">
         <v>1561.9</v>
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.2852</v>
+        <v>1.2703</v>
       </c>
       <c r="E9" t="n">
-        <v>62.41</v>
+        <v>61.89</v>
       </c>
       <c r="F9" t="n">
         <v>1673.8</v>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.2544</v>
+        <v>1.2409</v>
       </c>
       <c r="E10" t="n">
-        <v>61.96</v>
+        <v>61.47</v>
       </c>
       <c r="F10" t="n">
         <v>1555.7</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.2102</v>
+        <v>1.1952</v>
       </c>
       <c r="E11" t="n">
-        <v>59.97</v>
+        <v>59.31</v>
       </c>
       <c r="F11" t="n">
         <v>1585.8</v>
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.1732</v>
+        <v>1.1452</v>
       </c>
       <c r="E12" t="n">
-        <v>58.44</v>
+        <v>57.19</v>
       </c>
       <c r="F12" t="n">
         <v>1517.6</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.0875</v>
+        <v>1.1133</v>
       </c>
       <c r="E13" t="n">
-        <v>54.99</v>
+        <v>56.03</v>
       </c>
       <c r="F13" t="n">
         <v>1572</v>
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.0816</v>
+        <v>1.0926</v>
       </c>
       <c r="E14" t="n">
-        <v>54.64</v>
+        <v>55.02</v>
       </c>
       <c r="F14" t="n">
         <v>1579.3</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.0496</v>
+        <v>1.0605</v>
       </c>
       <c r="E15" t="n">
-        <v>53.28</v>
+        <v>53.76</v>
       </c>
       <c r="F15" t="n">
         <v>1541.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.025</v>
+        <v>1.032</v>
       </c>
       <c r="E16" t="n">
-        <v>52.32</v>
+        <v>52.42</v>
       </c>
       <c r="F16" t="n">
         <v>1505</v>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.0144</v>
+        <v>1.0153</v>
       </c>
       <c r="E17" t="n">
-        <v>51.8</v>
+        <v>51.76</v>
       </c>
       <c r="F17" t="n">
         <v>1507.6</v>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9331</v>
+        <v>0.9437</v>
       </c>
       <c r="E18" t="n">
-        <v>48.06</v>
+        <v>48.43</v>
       </c>
       <c r="F18" t="n">
         <v>1523.4</v>
@@ -1172,32 +1172,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1610612757</v>
+        <v>1610612744</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.9152</v>
+        <v>0.925</v>
       </c>
       <c r="E19" t="n">
-        <v>46.91</v>
+        <v>47.61</v>
       </c>
       <c r="F19" t="n">
-        <v>1464.5</v>
+        <v>1480.4</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.89</v>
+        <v>0.25</v>
       </c>
       <c r="H19" t="n">
-        <v>7.89</v>
+        <v>-4.85</v>
       </c>
       <c r="I19" t="n">
         <v>158</v>
@@ -1213,32 +1213,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1610612744</v>
+        <v>1610612757</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.9072</v>
+        <v>0.9058</v>
       </c>
       <c r="E20" t="n">
-        <v>47.1</v>
+        <v>46.29</v>
       </c>
       <c r="F20" t="n">
-        <v>1480.4</v>
+        <v>1464.5</v>
       </c>
       <c r="G20" t="n">
-        <v>0.25</v>
+        <v>-1.89</v>
       </c>
       <c r="H20" t="n">
-        <v>-4.85</v>
+        <v>7.89</v>
       </c>
       <c r="I20" t="n">
         <v>158</v>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8809</v>
+        <v>0.8974</v>
       </c>
       <c r="E21" t="n">
-        <v>45.8</v>
+        <v>46.31</v>
       </c>
       <c r="F21" t="n">
         <v>1466.8</v>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.8294</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>42.92</v>
+        <v>42.9</v>
       </c>
       <c r="F22" t="n">
         <v>1381.9</v>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.7509</v>
+        <v>0.759</v>
       </c>
       <c r="E23" t="n">
-        <v>39.31</v>
+        <v>39.52</v>
       </c>
       <c r="F23" t="n">
         <v>1382.4</v>
@@ -1377,32 +1377,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1610612749</v>
+        <v>1610612763</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.6836</v>
       </c>
       <c r="E24" t="n">
-        <v>34.85</v>
+        <v>35.7</v>
       </c>
       <c r="F24" t="n">
-        <v>1399.8</v>
+        <v>1384.6</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.87</v>
+        <v>-4.92</v>
       </c>
       <c r="H24" t="n">
-        <v>-14.47</v>
+        <v>-16.42</v>
       </c>
       <c r="I24" t="n">
         <v>158</v>
@@ -1418,32 +1418,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1610612763</v>
+        <v>1610612749</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6637</v>
+        <v>0.6594</v>
       </c>
       <c r="E25" t="n">
-        <v>34.75</v>
+        <v>34.55</v>
       </c>
       <c r="F25" t="n">
-        <v>1384.6</v>
+        <v>1399.8</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.92</v>
+        <v>-5.87</v>
       </c>
       <c r="H25" t="n">
-        <v>-16.42</v>
+        <v>-14.47</v>
       </c>
       <c r="I25" t="n">
         <v>158</v>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6481</v>
+        <v>0.6581</v>
       </c>
       <c r="E26" t="n">
-        <v>34.05</v>
+        <v>34.46</v>
       </c>
       <c r="F26" t="n">
         <v>1368.2</v>
@@ -1500,32 +1500,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1610612754</v>
+        <v>1610612762</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.5853</v>
+        <v>0.5895</v>
       </c>
       <c r="E27" t="n">
-        <v>30.19</v>
+        <v>30.34</v>
       </c>
       <c r="F27" t="n">
-        <v>1334.8</v>
+        <v>1310.4</v>
       </c>
       <c r="G27" t="n">
-        <v>-8.02</v>
+        <v>-7.57</v>
       </c>
       <c r="H27" t="n">
-        <v>-8.99</v>
+        <v>-7.76</v>
       </c>
       <c r="I27" t="n">
         <v>158</v>
@@ -1541,32 +1541,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1610612762</v>
+        <v>1610612754</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.5806</v>
+        <v>0.5825</v>
       </c>
       <c r="E28" t="n">
-        <v>29.98</v>
+        <v>30.24</v>
       </c>
       <c r="F28" t="n">
-        <v>1310.4</v>
+        <v>1334.8</v>
       </c>
       <c r="G28" t="n">
-        <v>-7.57</v>
+        <v>-8.02</v>
       </c>
       <c r="H28" t="n">
-        <v>-7.76</v>
+        <v>-8.99</v>
       </c>
       <c r="I28" t="n">
         <v>158</v>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.5568</v>
+        <v>0.5577</v>
       </c>
       <c r="E29" t="n">
-        <v>28.53</v>
+        <v>28.62</v>
       </c>
       <c r="F29" t="n">
         <v>1314.4</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5179</v>
+        <v>0.5178</v>
       </c>
       <c r="E30" t="n">
-        <v>25.85</v>
+        <v>26.04</v>
       </c>
       <c r="F30" t="n">
         <v>1260.5</v>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.5052</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>25.12</v>
+        <v>25.28</v>
       </c>
       <c r="F31" t="n">
         <v>1293.2</v>

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.551</v>
+        <v>1.5403</v>
       </c>
       <c r="E2" t="n">
-        <v>73.54000000000001</v>
+        <v>73.08</v>
       </c>
       <c r="F2" t="n">
         <v>1750.8</v>
@@ -503,11 +503,11 @@
         <v>11.71</v>
       </c>
       <c r="I2" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -529,26 +529,26 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.4672</v>
+        <v>1.4719</v>
       </c>
       <c r="E3" t="n">
-        <v>70.33</v>
+        <v>70.41</v>
       </c>
       <c r="F3" t="n">
-        <v>1728.8</v>
+        <v>1731.5</v>
       </c>
       <c r="G3" t="n">
-        <v>8.48</v>
+        <v>8.81</v>
       </c>
       <c r="H3" t="n">
-        <v>14.04</v>
+        <v>16.63</v>
       </c>
       <c r="I3" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.3767</v>
+        <v>1.367</v>
       </c>
       <c r="E4" t="n">
-        <v>66.90000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="F4" t="n">
         <v>1637.7</v>
@@ -585,11 +585,11 @@
         <v>4.62</v>
       </c>
       <c r="I4" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -611,10 +611,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.3756</v>
+        <v>1.3638</v>
       </c>
       <c r="E5" t="n">
-        <v>67.03</v>
+        <v>66.47</v>
       </c>
       <c r="F5" t="n">
         <v>1658.4</v>
@@ -626,11 +626,11 @@
         <v>5.32</v>
       </c>
       <c r="I5" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.369</v>
+        <v>1.361</v>
       </c>
       <c r="E6" t="n">
-        <v>66.58</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="F6" t="n">
         <v>1594.9</v>
@@ -667,11 +667,11 @@
         <v>8.789999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.3481</v>
+        <v>1.3424</v>
       </c>
       <c r="E7" t="n">
-        <v>65.69</v>
+        <v>65.38</v>
       </c>
       <c r="F7" t="n">
         <v>1661.9</v>
@@ -708,11 +708,11 @@
         <v>9.4</v>
       </c>
       <c r="I7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.3269</v>
+        <v>1.3169</v>
       </c>
       <c r="E8" t="n">
-        <v>64.8</v>
+        <v>64.42</v>
       </c>
       <c r="F8" t="n">
         <v>1561.9</v>
@@ -749,11 +749,11 @@
         <v>10.22</v>
       </c>
       <c r="I8" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -775,26 +775,26 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.2703</v>
+        <v>1.2964</v>
       </c>
       <c r="E9" t="n">
-        <v>61.89</v>
+        <v>62.9</v>
       </c>
       <c r="F9" t="n">
-        <v>1673.8</v>
+        <v>1675.2</v>
       </c>
       <c r="G9" t="n">
-        <v>7.23</v>
+        <v>7.55</v>
       </c>
       <c r="H9" t="n">
-        <v>11.54</v>
+        <v>14.38</v>
       </c>
       <c r="I9" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.2409</v>
+        <v>1.2331</v>
       </c>
       <c r="E10" t="n">
-        <v>61.47</v>
+        <v>61.06</v>
       </c>
       <c r="F10" t="n">
         <v>1555.7</v>
@@ -831,11 +831,11 @@
         <v>8.01</v>
       </c>
       <c r="I10" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -857,26 +857,26 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.1952</v>
+        <v>1.175</v>
       </c>
       <c r="E11" t="n">
-        <v>59.31</v>
+        <v>58.53</v>
       </c>
       <c r="F11" t="n">
-        <v>1585.8</v>
+        <v>1590.9</v>
       </c>
       <c r="G11" t="n">
-        <v>3.51</v>
+        <v>3.15</v>
       </c>
       <c r="H11" t="n">
-        <v>10.08</v>
+        <v>6.3</v>
       </c>
       <c r="I11" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -898,26 +898,26 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.1452</v>
+        <v>1.1564</v>
       </c>
       <c r="E12" t="n">
-        <v>57.19</v>
+        <v>57.61</v>
       </c>
       <c r="F12" t="n">
-        <v>1517.6</v>
+        <v>1515.9</v>
       </c>
       <c r="G12" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="H12" t="n">
-        <v>9.59</v>
+        <v>9.77</v>
       </c>
       <c r="I12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -926,39 +926,39 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.1133</v>
+        <v>1.1167</v>
       </c>
       <c r="E13" t="n">
-        <v>56.03</v>
+        <v>56.17</v>
       </c>
       <c r="F13" t="n">
-        <v>1572</v>
+        <v>1582.4</v>
       </c>
       <c r="G13" t="n">
-        <v>3.68</v>
+        <v>3.52</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.53</v>
+        <v>-3.83</v>
       </c>
       <c r="I13" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -967,39 +967,39 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.0926</v>
+        <v>1.104</v>
       </c>
       <c r="E14" t="n">
-        <v>55.02</v>
+        <v>55.65</v>
       </c>
       <c r="F14" t="n">
-        <v>1579.3</v>
+        <v>1572</v>
       </c>
       <c r="G14" t="n">
-        <v>4.25</v>
+        <v>3.68</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.97</v>
+        <v>-4.53</v>
       </c>
       <c r="I14" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.0605</v>
+        <v>1.0346</v>
       </c>
       <c r="E15" t="n">
-        <v>53.76</v>
+        <v>52.61</v>
       </c>
       <c r="F15" t="n">
         <v>1541.1</v>
@@ -1036,11 +1036,11 @@
         <v>-1.27</v>
       </c>
       <c r="I15" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1049,39 +1049,39 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1610612761</v>
+        <v>1610612756</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.032</v>
+        <v>1.0285</v>
       </c>
       <c r="E16" t="n">
-        <v>52.42</v>
+        <v>52.33</v>
       </c>
       <c r="F16" t="n">
-        <v>1505</v>
+        <v>1504.2</v>
       </c>
       <c r="G16" t="n">
-        <v>1.52</v>
+        <v>1.98</v>
       </c>
       <c r="H16" t="n">
-        <v>1.17</v>
+        <v>5.51</v>
       </c>
       <c r="I16" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1090,39 +1090,39 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1610612756</v>
+        <v>1610612761</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.0153</v>
+        <v>1.0253</v>
       </c>
       <c r="E17" t="n">
-        <v>51.76</v>
+        <v>52.14</v>
       </c>
       <c r="F17" t="n">
-        <v>1507.6</v>
+        <v>1505</v>
       </c>
       <c r="G17" t="n">
-        <v>1.15</v>
+        <v>1.52</v>
       </c>
       <c r="H17" t="n">
-        <v>3.21</v>
+        <v>1.17</v>
       </c>
       <c r="I17" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1131,39 +1131,39 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9437</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>48.43</v>
+        <v>50.7</v>
       </c>
       <c r="F18" t="n">
-        <v>1523.4</v>
+        <v>1469.6</v>
       </c>
       <c r="G18" t="n">
-        <v>0.64</v>
+        <v>0.26</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.67</v>
+        <v>-0.67</v>
       </c>
       <c r="I18" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1172,39 +1172,39 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1610612744</v>
+        <v>1610612753</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.925</v>
+        <v>0.9393</v>
       </c>
       <c r="E19" t="n">
-        <v>47.61</v>
+        <v>48.28</v>
       </c>
       <c r="F19" t="n">
-        <v>1480.4</v>
+        <v>1523.4</v>
       </c>
       <c r="G19" t="n">
-        <v>0.25</v>
+        <v>0.64</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.85</v>
+        <v>-1.67</v>
       </c>
       <c r="I19" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.9058</v>
+        <v>0.9383</v>
       </c>
       <c r="E20" t="n">
-        <v>46.29</v>
+        <v>47.82</v>
       </c>
       <c r="F20" t="n">
         <v>1464.5</v>
@@ -1241,11 +1241,11 @@
         <v>7.89</v>
       </c>
       <c r="I20" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1254,39 +1254,39 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1610612755</v>
+        <v>1610612744</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8974</v>
+        <v>0.9183</v>
       </c>
       <c r="E21" t="n">
-        <v>46.31</v>
+        <v>47.33</v>
       </c>
       <c r="F21" t="n">
-        <v>1466.8</v>
+        <v>1480.4</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.84</v>
+        <v>-4.85</v>
       </c>
       <c r="I21" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.829</v>
       </c>
       <c r="E22" t="n">
-        <v>42.9</v>
+        <v>42.79</v>
       </c>
       <c r="F22" t="n">
         <v>1381.9</v>
@@ -1323,11 +1323,11 @@
         <v>1.14</v>
       </c>
       <c r="I22" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1349,26 +1349,26 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.759</v>
+        <v>0.8051</v>
       </c>
       <c r="E23" t="n">
-        <v>39.52</v>
+        <v>41.78</v>
       </c>
       <c r="F23" t="n">
-        <v>1382.4</v>
+        <v>1381.5</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.05</v>
+        <v>-3.65</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.84</v>
+        <v>-5.86</v>
       </c>
       <c r="I23" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1377,39 +1377,39 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6836</v>
+        <v>0.6531</v>
       </c>
       <c r="E24" t="n">
-        <v>35.7</v>
+        <v>34.25</v>
       </c>
       <c r="F24" t="n">
-        <v>1384.6</v>
+        <v>1368.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.92</v>
+        <v>-5.1</v>
       </c>
       <c r="H24" t="n">
-        <v>-16.42</v>
+        <v>-7.7</v>
       </c>
       <c r="I24" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1431,26 +1431,26 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6594</v>
+        <v>0.6397</v>
       </c>
       <c r="E25" t="n">
-        <v>34.55</v>
+        <v>33.38</v>
       </c>
       <c r="F25" t="n">
-        <v>1399.8</v>
+        <v>1395.6</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.87</v>
+        <v>-6.19</v>
       </c>
       <c r="H25" t="n">
-        <v>-14.47</v>
+        <v>-18.44</v>
       </c>
       <c r="I25" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1459,39 +1459,39 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6581</v>
+        <v>0.6283</v>
       </c>
       <c r="E26" t="n">
-        <v>34.46</v>
+        <v>32.98</v>
       </c>
       <c r="F26" t="n">
-        <v>1368.2</v>
+        <v>1382.6</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.1</v>
+        <v>-4.85</v>
       </c>
       <c r="H26" t="n">
-        <v>-7.7</v>
+        <v>-15.55</v>
       </c>
       <c r="I26" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1500,39 +1500,39 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1610612762</v>
+        <v>1610612754</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.5895</v>
+        <v>0.5797</v>
       </c>
       <c r="E27" t="n">
-        <v>30.34</v>
+        <v>30.14</v>
       </c>
       <c r="F27" t="n">
-        <v>1310.4</v>
+        <v>1334.8</v>
       </c>
       <c r="G27" t="n">
-        <v>-7.57</v>
+        <v>-8.02</v>
       </c>
       <c r="H27" t="n">
-        <v>-7.76</v>
+        <v>-8.99</v>
       </c>
       <c r="I27" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -1541,39 +1541,39 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1610612754</v>
+        <v>1610612762</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.5825</v>
+        <v>0.5793</v>
       </c>
       <c r="E28" t="n">
-        <v>30.24</v>
+        <v>29.82</v>
       </c>
       <c r="F28" t="n">
-        <v>1334.8</v>
+        <v>1309.7</v>
       </c>
       <c r="G28" t="n">
-        <v>-8.02</v>
+        <v>-8.09</v>
       </c>
       <c r="H28" t="n">
-        <v>-8.99</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -1595,26 +1595,26 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.5577</v>
+        <v>0.5578</v>
       </c>
       <c r="E29" t="n">
-        <v>28.62</v>
+        <v>28.73</v>
       </c>
       <c r="F29" t="n">
-        <v>1314.4</v>
+        <v>1313.5</v>
       </c>
       <c r="G29" t="n">
-        <v>-9.42</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>-5.56</v>
+        <v>-5.63</v>
       </c>
       <c r="I29" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -1623,39 +1623,39 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5178</v>
+        <v>0.5069</v>
       </c>
       <c r="E30" t="n">
-        <v>26.04</v>
+        <v>25.47</v>
       </c>
       <c r="F30" t="n">
-        <v>1260.5</v>
+        <v>1293.2</v>
       </c>
       <c r="G30" t="n">
-        <v>-10.81</v>
+        <v>-10.5</v>
       </c>
       <c r="H30" t="n">
-        <v>-12.37</v>
+        <v>-14.37</v>
       </c>
       <c r="I30" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -1664,39 +1664,39 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.4974</v>
       </c>
       <c r="E31" t="n">
-        <v>25.28</v>
+        <v>25.01</v>
       </c>
       <c r="F31" t="n">
-        <v>1293.2</v>
+        <v>1260.5</v>
       </c>
       <c r="G31" t="n">
-        <v>-10.5</v>
+        <v>-10.81</v>
       </c>
       <c r="H31" t="n">
-        <v>-14.37</v>
+        <v>-12.37</v>
       </c>
       <c r="I31" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="K31" t="n">

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5403</v>
+        <v>1.5567</v>
       </c>
       <c r="E2" t="n">
-        <v>73.08</v>
+        <v>73.72</v>
       </c>
       <c r="F2" t="n">
         <v>1750.8</v>
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.4719</v>
+        <v>1.4871</v>
       </c>
       <c r="E3" t="n">
-        <v>70.41</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="F3" t="n">
         <v>1731.5</v>
@@ -557,32 +557,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1610612739</v>
+        <v>1610612743</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.367</v>
+        <v>1.3815</v>
       </c>
       <c r="E4" t="n">
-        <v>66.5</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1637.7</v>
+        <v>1594.9</v>
       </c>
       <c r="G4" t="n">
-        <v>4.44</v>
+        <v>4.37</v>
       </c>
       <c r="H4" t="n">
-        <v>4.62</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="I4" t="n">
         <v>159</v>
@@ -598,32 +598,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1610612738</v>
+        <v>1610612739</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.3638</v>
+        <v>1.3727</v>
       </c>
       <c r="E5" t="n">
-        <v>66.47</v>
+        <v>66.64</v>
       </c>
       <c r="F5" t="n">
-        <v>1658.4</v>
+        <v>1637.7</v>
       </c>
       <c r="G5" t="n">
-        <v>6.9</v>
+        <v>4.44</v>
       </c>
       <c r="H5" t="n">
-        <v>5.32</v>
+        <v>4.62</v>
       </c>
       <c r="I5" t="n">
         <v>159</v>
@@ -639,32 +639,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1610612743</v>
+        <v>1610612752</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.361</v>
+        <v>1.3499</v>
       </c>
       <c r="E6" t="n">
-        <v>66.23999999999999</v>
+        <v>65.72</v>
       </c>
       <c r="F6" t="n">
-        <v>1594.9</v>
+        <v>1661.9</v>
       </c>
       <c r="G6" t="n">
-        <v>4.37</v>
+        <v>6.62</v>
       </c>
       <c r="H6" t="n">
-        <v>8.789999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I6" t="n">
         <v>159</v>
@@ -680,32 +680,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612752</v>
+        <v>1610612738</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.3424</v>
+        <v>1.3432</v>
       </c>
       <c r="E7" t="n">
-        <v>65.38</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>1661.9</v>
+        <v>1658.4</v>
       </c>
       <c r="G7" t="n">
-        <v>6.62</v>
+        <v>6.9</v>
       </c>
       <c r="H7" t="n">
-        <v>9.4</v>
+        <v>5.32</v>
       </c>
       <c r="I7" t="n">
         <v>159</v>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.3169</v>
+        <v>1.3375</v>
       </c>
       <c r="E8" t="n">
-        <v>64.42</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="F8" t="n">
         <v>1561.9</v>
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.2964</v>
+        <v>1.3033</v>
       </c>
       <c r="E9" t="n">
-        <v>62.9</v>
+        <v>63.22</v>
       </c>
       <c r="F9" t="n">
         <v>1675.2</v>
@@ -803,32 +803,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1610612746</v>
+        <v>1610612766</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.2331</v>
+        <v>1.1887</v>
       </c>
       <c r="E10" t="n">
-        <v>61.06</v>
+        <v>59.16</v>
       </c>
       <c r="F10" t="n">
-        <v>1555.7</v>
+        <v>1590.9</v>
       </c>
       <c r="G10" t="n">
-        <v>2.23</v>
+        <v>3.15</v>
       </c>
       <c r="H10" t="n">
-        <v>8.01</v>
+        <v>6.3</v>
       </c>
       <c r="I10" t="n">
         <v>159</v>
@@ -844,32 +844,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1610612766</v>
+        <v>1610612746</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.175</v>
+        <v>1.1736</v>
       </c>
       <c r="E11" t="n">
-        <v>58.53</v>
+        <v>58.67</v>
       </c>
       <c r="F11" t="n">
-        <v>1590.9</v>
+        <v>1555.7</v>
       </c>
       <c r="G11" t="n">
-        <v>3.15</v>
+        <v>2.23</v>
       </c>
       <c r="H11" t="n">
-        <v>6.3</v>
+        <v>8.01</v>
       </c>
       <c r="I11" t="n">
         <v>159</v>
@@ -885,32 +885,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1610612737</v>
+        <v>1610612750</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.1564</v>
+        <v>1.1251</v>
       </c>
       <c r="E12" t="n">
-        <v>57.61</v>
+        <v>56.57</v>
       </c>
       <c r="F12" t="n">
-        <v>1515.9</v>
+        <v>1582.4</v>
       </c>
       <c r="G12" t="n">
-        <v>1.72</v>
+        <v>3.52</v>
       </c>
       <c r="H12" t="n">
-        <v>9.77</v>
+        <v>-3.83</v>
       </c>
       <c r="I12" t="n">
         <v>159</v>
@@ -926,32 +926,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1610612750</v>
+        <v>1610612737</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.1167</v>
+        <v>1.1136</v>
       </c>
       <c r="E13" t="n">
-        <v>56.17</v>
+        <v>55.89</v>
       </c>
       <c r="F13" t="n">
-        <v>1582.4</v>
+        <v>1515.9</v>
       </c>
       <c r="G13" t="n">
-        <v>3.52</v>
+        <v>1.72</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.83</v>
+        <v>9.77</v>
       </c>
       <c r="I13" t="n">
         <v>159</v>
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.104</v>
+        <v>1.1108</v>
       </c>
       <c r="E14" t="n">
-        <v>55.65</v>
+        <v>55.97</v>
       </c>
       <c r="F14" t="n">
         <v>1572</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.0346</v>
+        <v>1.0401</v>
       </c>
       <c r="E15" t="n">
-        <v>52.61</v>
+        <v>52.89</v>
       </c>
       <c r="F15" t="n">
         <v>1541.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.0285</v>
+        <v>1.0353</v>
       </c>
       <c r="E16" t="n">
-        <v>52.33</v>
+        <v>52.65</v>
       </c>
       <c r="F16" t="n">
         <v>1504.2</v>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.0253</v>
+        <v>1.0316</v>
       </c>
       <c r="E17" t="n">
-        <v>52.14</v>
+        <v>52.45</v>
       </c>
       <c r="F17" t="n">
         <v>1505</v>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9945000000000001</v>
+        <v>1.0025</v>
       </c>
       <c r="E18" t="n">
-        <v>50.7</v>
+        <v>51.09</v>
       </c>
       <c r="F18" t="n">
         <v>1469.6</v>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.9393</v>
+        <v>0.9433</v>
       </c>
       <c r="E19" t="n">
-        <v>48.28</v>
+        <v>48.46</v>
       </c>
       <c r="F19" t="n">
         <v>1523.4</v>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.9383</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>47.82</v>
+        <v>48.07</v>
       </c>
       <c r="F20" t="n">
         <v>1464.5</v>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.9183</v>
+        <v>0.9245</v>
       </c>
       <c r="E21" t="n">
-        <v>47.33</v>
+        <v>47.59</v>
       </c>
       <c r="F21" t="n">
         <v>1480.4</v>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.829</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>42.79</v>
+        <v>42.75</v>
       </c>
       <c r="F22" t="n">
         <v>1381.9</v>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.8051</v>
+        <v>0.7416</v>
       </c>
       <c r="E23" t="n">
-        <v>41.78</v>
+        <v>38.77</v>
       </c>
       <c r="F23" t="n">
         <v>1381.5</v>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6531</v>
+        <v>0.6529</v>
       </c>
       <c r="E24" t="n">
-        <v>34.25</v>
+        <v>34.22</v>
       </c>
       <c r="F24" t="n">
         <v>1368.2</v>
@@ -1418,32 +1418,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1610612749</v>
+        <v>1610612763</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6397</v>
+        <v>0.6373</v>
       </c>
       <c r="E25" t="n">
-        <v>33.38</v>
+        <v>33.42</v>
       </c>
       <c r="F25" t="n">
-        <v>1395.6</v>
+        <v>1382.6</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.19</v>
+        <v>-4.85</v>
       </c>
       <c r="H25" t="n">
-        <v>-18.44</v>
+        <v>-15.55</v>
       </c>
       <c r="I25" t="n">
         <v>159</v>
@@ -1459,32 +1459,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1610612763</v>
+        <v>1610612749</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6283</v>
+        <v>0.6361</v>
       </c>
       <c r="E26" t="n">
-        <v>32.98</v>
+        <v>33.18</v>
       </c>
       <c r="F26" t="n">
-        <v>1382.6</v>
+        <v>1395.6</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.85</v>
+        <v>-6.19</v>
       </c>
       <c r="H26" t="n">
-        <v>-15.55</v>
+        <v>-18.44</v>
       </c>
       <c r="I26" t="n">
         <v>159</v>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.5797</v>
+        <v>0.5824</v>
       </c>
       <c r="E27" t="n">
-        <v>30.14</v>
+        <v>30.28</v>
       </c>
       <c r="F27" t="n">
         <v>1334.8</v>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.5793</v>
+        <v>0.5679</v>
       </c>
       <c r="E28" t="n">
-        <v>29.82</v>
+        <v>29.16</v>
       </c>
       <c r="F28" t="n">
         <v>1309.7</v>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.5578</v>
+        <v>0.5571</v>
       </c>
       <c r="E29" t="n">
-        <v>28.73</v>
+        <v>28.6</v>
       </c>
       <c r="F29" t="n">
         <v>1313.5</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5069</v>
+        <v>0.5188</v>
       </c>
       <c r="E30" t="n">
-        <v>25.47</v>
+        <v>26.14</v>
       </c>
       <c r="F30" t="n">
         <v>1293.2</v>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.4974</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>25.01</v>
+        <v>25.86</v>
       </c>
       <c r="F31" t="n">
         <v>1260.5</v>

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5567</v>
+        <v>1.5542</v>
       </c>
       <c r="E2" t="n">
-        <v>73.72</v>
+        <v>73.63</v>
       </c>
       <c r="F2" t="n">
         <v>1750.8</v>
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.4871</v>
+        <v>1.49</v>
       </c>
       <c r="E3" t="n">
-        <v>71.06999999999999</v>
+        <v>71.17</v>
       </c>
       <c r="F3" t="n">
         <v>1731.5</v>
@@ -557,32 +557,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1610612743</v>
+        <v>1610612752</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.3815</v>
+        <v>1.3863</v>
       </c>
       <c r="E4" t="n">
-        <v>67.01000000000001</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>1594.9</v>
+        <v>1661.9</v>
       </c>
       <c r="G4" t="n">
-        <v>4.37</v>
+        <v>6.62</v>
       </c>
       <c r="H4" t="n">
-        <v>8.789999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I4" t="n">
         <v>159</v>
@@ -598,32 +598,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1610612739</v>
+        <v>1610612743</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.3727</v>
+        <v>1.3745</v>
       </c>
       <c r="E5" t="n">
         <v>66.64</v>
       </c>
       <c r="F5" t="n">
-        <v>1637.7</v>
+        <v>1594.9</v>
       </c>
       <c r="G5" t="n">
-        <v>4.44</v>
+        <v>4.37</v>
       </c>
       <c r="H5" t="n">
-        <v>4.62</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>159</v>
@@ -639,32 +639,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1610612752</v>
+        <v>1610612747</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.3499</v>
+        <v>1.3348</v>
       </c>
       <c r="E6" t="n">
-        <v>65.72</v>
+        <v>65.16</v>
       </c>
       <c r="F6" t="n">
-        <v>1661.9</v>
+        <v>1561.9</v>
       </c>
       <c r="G6" t="n">
-        <v>6.62</v>
+        <v>2.56</v>
       </c>
       <c r="H6" t="n">
-        <v>9.4</v>
+        <v>10.22</v>
       </c>
       <c r="I6" t="n">
         <v>159</v>
@@ -680,32 +680,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612738</v>
+        <v>1610612739</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.3432</v>
+        <v>1.3184</v>
       </c>
       <c r="E7" t="n">
-        <v>65.59999999999999</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>1658.4</v>
+        <v>1637.7</v>
       </c>
       <c r="G7" t="n">
-        <v>6.9</v>
+        <v>4.44</v>
       </c>
       <c r="H7" t="n">
-        <v>5.32</v>
+        <v>4.62</v>
       </c>
       <c r="I7" t="n">
         <v>159</v>
@@ -721,32 +721,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1610612747</v>
+        <v>1610612765</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.3375</v>
+        <v>1.3079</v>
       </c>
       <c r="E8" t="n">
-        <v>65.18000000000001</v>
+        <v>63.51</v>
       </c>
       <c r="F8" t="n">
-        <v>1561.9</v>
+        <v>1675.2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.56</v>
+        <v>7.55</v>
       </c>
       <c r="H8" t="n">
-        <v>10.22</v>
+        <v>14.38</v>
       </c>
       <c r="I8" t="n">
         <v>159</v>
@@ -762,32 +762,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1610612765</v>
+        <v>1610612738</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.3033</v>
+        <v>1.2972</v>
       </c>
       <c r="E9" t="n">
-        <v>63.22</v>
+        <v>63.48</v>
       </c>
       <c r="F9" t="n">
-        <v>1675.2</v>
+        <v>1658.4</v>
       </c>
       <c r="G9" t="n">
-        <v>7.55</v>
+        <v>6.9</v>
       </c>
       <c r="H9" t="n">
-        <v>14.38</v>
+        <v>5.32</v>
       </c>
       <c r="I9" t="n">
         <v>159</v>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.1887</v>
+        <v>1.196</v>
       </c>
       <c r="E10" t="n">
-        <v>59.16</v>
+        <v>59.51</v>
       </c>
       <c r="F10" t="n">
         <v>1590.9</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.1736</v>
+        <v>1.1791</v>
       </c>
       <c r="E11" t="n">
-        <v>58.67</v>
+        <v>58.96</v>
       </c>
       <c r="F11" t="n">
         <v>1555.7</v>
@@ -885,32 +885,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1610612750</v>
+        <v>1610612737</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.1251</v>
+        <v>1.1249</v>
       </c>
       <c r="E12" t="n">
-        <v>56.57</v>
+        <v>56.49</v>
       </c>
       <c r="F12" t="n">
-        <v>1582.4</v>
+        <v>1515.9</v>
       </c>
       <c r="G12" t="n">
-        <v>3.52</v>
+        <v>1.72</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.83</v>
+        <v>9.77</v>
       </c>
       <c r="I12" t="n">
         <v>159</v>
@@ -926,32 +926,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1610612737</v>
+        <v>1610612750</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.1136</v>
+        <v>1.1178</v>
       </c>
       <c r="E13" t="n">
-        <v>55.89</v>
+        <v>56.24</v>
       </c>
       <c r="F13" t="n">
-        <v>1515.9</v>
+        <v>1582.4</v>
       </c>
       <c r="G13" t="n">
-        <v>1.72</v>
+        <v>3.52</v>
       </c>
       <c r="H13" t="n">
-        <v>9.77</v>
+        <v>-3.83</v>
       </c>
       <c r="I13" t="n">
         <v>159</v>
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.1108</v>
+        <v>1.1128</v>
       </c>
       <c r="E14" t="n">
-        <v>55.97</v>
+        <v>56.04</v>
       </c>
       <c r="F14" t="n">
         <v>1572</v>
@@ -1008,32 +1008,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1610612748</v>
+        <v>1610612756</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.0401</v>
+        <v>1.0443</v>
       </c>
       <c r="E15" t="n">
-        <v>52.89</v>
+        <v>53.2</v>
       </c>
       <c r="F15" t="n">
-        <v>1541.1</v>
+        <v>1504.2</v>
       </c>
       <c r="G15" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.27</v>
+        <v>5.51</v>
       </c>
       <c r="I15" t="n">
         <v>159</v>
@@ -1049,32 +1049,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1610612756</v>
+        <v>1610612748</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.0353</v>
+        <v>1.036</v>
       </c>
       <c r="E16" t="n">
-        <v>52.65</v>
+        <v>52.81</v>
       </c>
       <c r="F16" t="n">
-        <v>1504.2</v>
+        <v>1541.1</v>
       </c>
       <c r="G16" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="H16" t="n">
-        <v>5.51</v>
+        <v>-1.27</v>
       </c>
       <c r="I16" t="n">
         <v>159</v>
@@ -1090,32 +1090,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.0316</v>
+        <v>1.0019</v>
       </c>
       <c r="E17" t="n">
-        <v>52.45</v>
+        <v>51.21</v>
       </c>
       <c r="F17" t="n">
-        <v>1505</v>
+        <v>1469.6</v>
       </c>
       <c r="G17" t="n">
-        <v>1.52</v>
+        <v>0.26</v>
       </c>
       <c r="H17" t="n">
-        <v>1.17</v>
+        <v>-0.67</v>
       </c>
       <c r="I17" t="n">
         <v>159</v>
@@ -1131,32 +1131,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.0025</v>
+        <v>0.992</v>
       </c>
       <c r="E18" t="n">
-        <v>51.09</v>
+        <v>50.85</v>
       </c>
       <c r="F18" t="n">
-        <v>1469.6</v>
+        <v>1505</v>
       </c>
       <c r="G18" t="n">
-        <v>0.26</v>
+        <v>1.52</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.67</v>
+        <v>1.17</v>
       </c>
       <c r="I18" t="n">
         <v>159</v>
@@ -1172,32 +1172,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1610612753</v>
+        <v>1610612757</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.9433</v>
+        <v>0.9664</v>
       </c>
       <c r="E19" t="n">
-        <v>48.46</v>
+        <v>49.3</v>
       </c>
       <c r="F19" t="n">
-        <v>1523.4</v>
+        <v>1464.5</v>
       </c>
       <c r="G19" t="n">
-        <v>0.64</v>
+        <v>-1.89</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.67</v>
+        <v>7.89</v>
       </c>
       <c r="I19" t="n">
         <v>159</v>
@@ -1213,32 +1213,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1610612757</v>
+        <v>1610612753</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9386</v>
       </c>
       <c r="E20" t="n">
-        <v>48.07</v>
+        <v>48.43</v>
       </c>
       <c r="F20" t="n">
-        <v>1464.5</v>
+        <v>1523.4</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.89</v>
+        <v>0.64</v>
       </c>
       <c r="H20" t="n">
-        <v>7.89</v>
+        <v>-1.67</v>
       </c>
       <c r="I20" t="n">
         <v>159</v>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.9245</v>
+        <v>0.9286</v>
       </c>
       <c r="E21" t="n">
-        <v>47.59</v>
+        <v>47.85</v>
       </c>
       <c r="F21" t="n">
         <v>1480.4</v>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.7901</v>
       </c>
       <c r="E22" t="n">
-        <v>42.75</v>
+        <v>41.13</v>
       </c>
       <c r="F22" t="n">
         <v>1381.9</v>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.7416</v>
+        <v>0.7511</v>
       </c>
       <c r="E23" t="n">
-        <v>38.77</v>
+        <v>39.18</v>
       </c>
       <c r="F23" t="n">
         <v>1381.5</v>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6529</v>
+        <v>0.6662</v>
       </c>
       <c r="E24" t="n">
-        <v>34.22</v>
+        <v>34.85</v>
       </c>
       <c r="F24" t="n">
         <v>1368.2</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6373</v>
+        <v>0.6513</v>
       </c>
       <c r="E25" t="n">
-        <v>33.42</v>
+        <v>33.93</v>
       </c>
       <c r="F25" t="n">
         <v>1382.6</v>
@@ -1459,32 +1459,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1610612749</v>
+        <v>1610612754</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6361</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>33.18</v>
+        <v>33.36</v>
       </c>
       <c r="F26" t="n">
-        <v>1395.6</v>
+        <v>1334.8</v>
       </c>
       <c r="G26" t="n">
-        <v>-6.19</v>
+        <v>-8.02</v>
       </c>
       <c r="H26" t="n">
-        <v>-18.44</v>
+        <v>-8.99</v>
       </c>
       <c r="I26" t="n">
         <v>159</v>
@@ -1500,32 +1500,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1610612754</v>
+        <v>1610612749</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.5824</v>
+        <v>0.6045</v>
       </c>
       <c r="E27" t="n">
-        <v>30.28</v>
+        <v>30.91</v>
       </c>
       <c r="F27" t="n">
-        <v>1334.8</v>
+        <v>1395.6</v>
       </c>
       <c r="G27" t="n">
-        <v>-8.02</v>
+        <v>-6.19</v>
       </c>
       <c r="H27" t="n">
-        <v>-8.99</v>
+        <v>-18.44</v>
       </c>
       <c r="I27" t="n">
         <v>159</v>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.5679</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>29.16</v>
+        <v>29.65</v>
       </c>
       <c r="F28" t="n">
         <v>1309.7</v>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.5571</v>
+        <v>0.5513</v>
       </c>
       <c r="E29" t="n">
-        <v>28.6</v>
+        <v>27.94</v>
       </c>
       <c r="F29" t="n">
         <v>1313.5</v>
@@ -1623,32 +1623,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5188</v>
+        <v>0.534</v>
       </c>
       <c r="E30" t="n">
-        <v>26.14</v>
+        <v>26.65</v>
       </c>
       <c r="F30" t="n">
-        <v>1293.2</v>
+        <v>1260.5</v>
       </c>
       <c r="G30" t="n">
-        <v>-10.5</v>
+        <v>-10.81</v>
       </c>
       <c r="H30" t="n">
-        <v>-14.37</v>
+        <v>-12.37</v>
       </c>
       <c r="I30" t="n">
         <v>159</v>
@@ -1664,32 +1664,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.5242</v>
       </c>
       <c r="E31" t="n">
-        <v>25.86</v>
+        <v>26.06</v>
       </c>
       <c r="F31" t="n">
-        <v>1260.5</v>
+        <v>1293.2</v>
       </c>
       <c r="G31" t="n">
-        <v>-10.81</v>
+        <v>-10.5</v>
       </c>
       <c r="H31" t="n">
-        <v>-12.37</v>
+        <v>-14.37</v>
       </c>
       <c r="I31" t="n">
         <v>159</v>

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5542</v>
+        <v>1.5018</v>
       </c>
       <c r="E2" t="n">
-        <v>73.63</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1750.8</v>
+        <v>1751.8</v>
       </c>
       <c r="G2" t="n">
-        <v>11.34</v>
+        <v>11.26</v>
       </c>
       <c r="H2" t="n">
-        <v>11.71</v>
+        <v>12.16</v>
       </c>
       <c r="I2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -529,26 +529,26 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.49</v>
+        <v>1.5002</v>
       </c>
       <c r="E3" t="n">
-        <v>71.17</v>
+        <v>71.61</v>
       </c>
       <c r="F3" t="n">
         <v>1731.5</v>
       </c>
       <c r="G3" t="n">
-        <v>8.81</v>
+        <v>8.83</v>
       </c>
       <c r="H3" t="n">
         <v>16.63</v>
       </c>
       <c r="I3" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -557,39 +557,39 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1610612752</v>
+        <v>1610612743</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.3863</v>
+        <v>1.4122</v>
       </c>
       <c r="E4" t="n">
-        <v>67.34999999999999</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>1661.9</v>
+        <v>1595.5</v>
       </c>
       <c r="G4" t="n">
-        <v>6.62</v>
+        <v>4.75</v>
       </c>
       <c r="H4" t="n">
-        <v>9.4</v>
+        <v>10.92</v>
       </c>
       <c r="I4" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -598,39 +598,39 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1610612743</v>
+        <v>1610612738</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.3745</v>
+        <v>1.3723</v>
       </c>
       <c r="E5" t="n">
-        <v>66.64</v>
+        <v>66.7</v>
       </c>
       <c r="F5" t="n">
-        <v>1594.9</v>
+        <v>1660.1</v>
       </c>
       <c r="G5" t="n">
-        <v>4.37</v>
+        <v>7.29</v>
       </c>
       <c r="H5" t="n">
-        <v>8.789999999999999</v>
+        <v>5.39</v>
       </c>
       <c r="I5" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.3348</v>
+        <v>1.3499</v>
       </c>
       <c r="E6" t="n">
-        <v>65.16</v>
+        <v>65.7</v>
       </c>
       <c r="F6" t="n">
         <v>1561.9</v>
@@ -667,11 +667,11 @@
         <v>10.22</v>
       </c>
       <c r="I6" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -680,39 +680,39 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612739</v>
+        <v>1610612752</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.3184</v>
+        <v>1.3315</v>
       </c>
       <c r="E7" t="n">
-        <v>64.51000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>1637.7</v>
+        <v>1656.8</v>
       </c>
       <c r="G7" t="n">
-        <v>4.44</v>
+        <v>6.4</v>
       </c>
       <c r="H7" t="n">
-        <v>4.62</v>
+        <v>4.58</v>
       </c>
       <c r="I7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -721,39 +721,39 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1610612765</v>
+        <v>1610612739</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.3079</v>
+        <v>1.3292</v>
       </c>
       <c r="E8" t="n">
-        <v>63.51</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>1675.2</v>
+        <v>1637.7</v>
       </c>
       <c r="G8" t="n">
-        <v>7.55</v>
+        <v>4.44</v>
       </c>
       <c r="H8" t="n">
-        <v>14.38</v>
+        <v>4.62</v>
       </c>
       <c r="I8" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -762,39 +762,39 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1610612738</v>
+        <v>1610612765</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.2972</v>
+        <v>1.2174</v>
       </c>
       <c r="E9" t="n">
-        <v>63.48</v>
+        <v>59.27</v>
       </c>
       <c r="F9" t="n">
-        <v>1658.4</v>
+        <v>1675.2</v>
       </c>
       <c r="G9" t="n">
-        <v>6.9</v>
+        <v>7.55</v>
       </c>
       <c r="H9" t="n">
-        <v>5.32</v>
+        <v>14.38</v>
       </c>
       <c r="I9" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -803,39 +803,39 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1610612766</v>
+        <v>1610612746</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.196</v>
+        <v>1.2072</v>
       </c>
       <c r="E10" t="n">
-        <v>59.51</v>
+        <v>60.14</v>
       </c>
       <c r="F10" t="n">
-        <v>1590.9</v>
+        <v>1557.2</v>
       </c>
       <c r="G10" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="H10" t="n">
-        <v>6.3</v>
+        <v>9.23</v>
       </c>
       <c r="I10" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -844,39 +844,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1610612746</v>
+        <v>1610612766</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.1791</v>
+        <v>1.1896</v>
       </c>
       <c r="E11" t="n">
-        <v>58.96</v>
+        <v>59.29</v>
       </c>
       <c r="F11" t="n">
-        <v>1555.7</v>
+        <v>1586.1</v>
       </c>
       <c r="G11" t="n">
-        <v>2.23</v>
+        <v>2.61</v>
       </c>
       <c r="H11" t="n">
-        <v>8.01</v>
+        <v>5.24</v>
       </c>
       <c r="I11" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -885,39 +885,39 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1610612737</v>
+        <v>1610612745</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.1249</v>
+        <v>1.1597</v>
       </c>
       <c r="E12" t="n">
-        <v>56.49</v>
+        <v>58.07</v>
       </c>
       <c r="F12" t="n">
-        <v>1515.9</v>
+        <v>1574</v>
       </c>
       <c r="G12" t="n">
-        <v>1.72</v>
+        <v>4.53</v>
       </c>
       <c r="H12" t="n">
-        <v>9.77</v>
+        <v>1.51</v>
       </c>
       <c r="I12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -926,39 +926,39 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1610612750</v>
+        <v>1610612737</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.1178</v>
+        <v>1.1354</v>
       </c>
       <c r="E13" t="n">
-        <v>56.24</v>
+        <v>56.91</v>
       </c>
       <c r="F13" t="n">
-        <v>1582.4</v>
+        <v>1515.9</v>
       </c>
       <c r="G13" t="n">
-        <v>3.52</v>
+        <v>1.71</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.83</v>
+        <v>9.77</v>
       </c>
       <c r="I13" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -967,39 +967,39 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.1128</v>
+        <v>1.1224</v>
       </c>
       <c r="E14" t="n">
-        <v>56.04</v>
+        <v>56.45</v>
       </c>
       <c r="F14" t="n">
-        <v>1572</v>
+        <v>1582.4</v>
       </c>
       <c r="G14" t="n">
-        <v>3.68</v>
+        <v>3.47</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.53</v>
+        <v>-3.83</v>
       </c>
       <c r="I14" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1008,39 +1008,39 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1610612756</v>
+        <v>1610612761</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.0443</v>
+        <v>1.0762</v>
       </c>
       <c r="E15" t="n">
-        <v>53.2</v>
+        <v>54.48</v>
       </c>
       <c r="F15" t="n">
-        <v>1504.2</v>
+        <v>1506.8</v>
       </c>
       <c r="G15" t="n">
-        <v>1.98</v>
+        <v>2.67</v>
       </c>
       <c r="H15" t="n">
-        <v>5.51</v>
+        <v>3.59</v>
       </c>
       <c r="I15" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1049,39 +1049,39 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1610612748</v>
+        <v>1610612756</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.036</v>
+        <v>1.0459</v>
       </c>
       <c r="E16" t="n">
-        <v>52.81</v>
+        <v>53.24</v>
       </c>
       <c r="F16" t="n">
-        <v>1541.1</v>
+        <v>1504.2</v>
       </c>
       <c r="G16" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.27</v>
+        <v>5.51</v>
       </c>
       <c r="I16" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1090,39 +1090,39 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1610612755</v>
+        <v>1610612748</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.0019</v>
+        <v>1.0294</v>
       </c>
       <c r="E17" t="n">
-        <v>51.21</v>
+        <v>52.5</v>
       </c>
       <c r="F17" t="n">
-        <v>1469.6</v>
+        <v>1537</v>
       </c>
       <c r="G17" t="n">
-        <v>0.26</v>
+        <v>1.84</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.67</v>
+        <v>-3.41</v>
       </c>
       <c r="I17" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1131,39 +1131,39 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.992</v>
+        <v>1.0073</v>
       </c>
       <c r="E18" t="n">
-        <v>50.85</v>
+        <v>51.45</v>
       </c>
       <c r="F18" t="n">
-        <v>1505</v>
+        <v>1469.6</v>
       </c>
       <c r="G18" t="n">
-        <v>1.52</v>
+        <v>0.26</v>
       </c>
       <c r="H18" t="n">
-        <v>1.17</v>
+        <v>-0.67</v>
       </c>
       <c r="I18" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1185,26 +1185,26 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.9664</v>
+        <v>0.9463</v>
       </c>
       <c r="E19" t="n">
-        <v>49.3</v>
+        <v>48.31</v>
       </c>
       <c r="F19" t="n">
-        <v>1464.5</v>
+        <v>1461.2</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.89</v>
+        <v>-0.9</v>
       </c>
       <c r="H19" t="n">
-        <v>7.89</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1213,39 +1213,39 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1610612753</v>
+        <v>1610612744</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.9386</v>
+        <v>0.9166</v>
       </c>
       <c r="E20" t="n">
-        <v>48.43</v>
+        <v>47.35</v>
       </c>
       <c r="F20" t="n">
-        <v>1523.4</v>
+        <v>1481</v>
       </c>
       <c r="G20" t="n">
-        <v>0.64</v>
+        <v>-0.38</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.67</v>
+        <v>-6.76</v>
       </c>
       <c r="I20" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1254,39 +1254,39 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1610612744</v>
+        <v>1610612753</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.9286</v>
+        <v>0.8842</v>
       </c>
       <c r="E21" t="n">
-        <v>47.85</v>
+        <v>45.71</v>
       </c>
       <c r="F21" t="n">
-        <v>1480.4</v>
+        <v>1524.2</v>
       </c>
       <c r="G21" t="n">
-        <v>0.25</v>
+        <v>-1</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.85</v>
+        <v>-9.93</v>
       </c>
       <c r="I21" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1308,26 +1308,26 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.7901</v>
+        <v>0.7677</v>
       </c>
       <c r="E22" t="n">
-        <v>41.13</v>
+        <v>40.13</v>
       </c>
       <c r="F22" t="n">
-        <v>1381.9</v>
+        <v>1380.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.02</v>
+        <v>-4.75</v>
       </c>
       <c r="H22" t="n">
-        <v>1.14</v>
+        <v>-2.14</v>
       </c>
       <c r="I22" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.7511</v>
+        <v>0.7487</v>
       </c>
       <c r="E23" t="n">
-        <v>39.18</v>
+        <v>39.15</v>
       </c>
       <c r="F23" t="n">
         <v>1381.5</v>
@@ -1364,11 +1364,11 @@
         <v>-5.86</v>
       </c>
       <c r="I23" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1390,26 +1390,26 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6662</v>
+        <v>0.6652</v>
       </c>
       <c r="E24" t="n">
-        <v>34.85</v>
+        <v>34.8</v>
       </c>
       <c r="F24" t="n">
         <v>1368.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.1</v>
+        <v>-5.09</v>
       </c>
       <c r="H24" t="n">
         <v>-7.7</v>
       </c>
       <c r="I24" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6513</v>
+        <v>0.649</v>
       </c>
       <c r="E25" t="n">
-        <v>33.93</v>
+        <v>33.81</v>
       </c>
       <c r="F25" t="n">
         <v>1382.6</v>
@@ -1446,11 +1446,11 @@
         <v>-15.55</v>
       </c>
       <c r="I25" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1459,39 +1459,39 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1610612754</v>
+        <v>1610612749</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.6358</v>
       </c>
       <c r="E26" t="n">
-        <v>33.36</v>
+        <v>32.87</v>
       </c>
       <c r="F26" t="n">
-        <v>1334.8</v>
+        <v>1392.6</v>
       </c>
       <c r="G26" t="n">
-        <v>-8.02</v>
+        <v>-6.25</v>
       </c>
       <c r="H26" t="n">
-        <v>-8.99</v>
+        <v>-16.74</v>
       </c>
       <c r="I26" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1500,39 +1500,39 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1610612749</v>
+        <v>1610612754</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.6045</v>
+        <v>0.6076</v>
       </c>
       <c r="E27" t="n">
-        <v>30.91</v>
+        <v>31.55</v>
       </c>
       <c r="F27" t="n">
-        <v>1395.6</v>
+        <v>1333.3</v>
       </c>
       <c r="G27" t="n">
-        <v>-6.19</v>
+        <v>-7.56</v>
       </c>
       <c r="H27" t="n">
-        <v>-18.44</v>
+        <v>-5.86</v>
       </c>
       <c r="I27" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -1554,26 +1554,26 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.5759</v>
       </c>
       <c r="E28" t="n">
-        <v>29.65</v>
+        <v>29.51</v>
       </c>
       <c r="F28" t="n">
         <v>1309.7</v>
       </c>
       <c r="G28" t="n">
-        <v>-8.09</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="H28" t="n">
         <v>-8.859999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -1595,26 +1595,26 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.5513</v>
+        <v>0.5572</v>
       </c>
       <c r="E29" t="n">
-        <v>27.94</v>
+        <v>28.44</v>
       </c>
       <c r="F29" t="n">
-        <v>1313.5</v>
+        <v>1312.7</v>
       </c>
       <c r="G29" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.68</v>
       </c>
       <c r="H29" t="n">
-        <v>-5.63</v>
+        <v>-8.68</v>
       </c>
       <c r="I29" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -1623,39 +1623,39 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.534</v>
+        <v>0.5434</v>
       </c>
       <c r="E30" t="n">
-        <v>26.65</v>
+        <v>27.37</v>
       </c>
       <c r="F30" t="n">
-        <v>1260.5</v>
+        <v>1292.1</v>
       </c>
       <c r="G30" t="n">
-        <v>-10.81</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>-12.37</v>
+        <v>-13.35</v>
       </c>
       <c r="I30" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -1664,39 +1664,39 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.5242</v>
+        <v>0.5148</v>
       </c>
       <c r="E31" t="n">
-        <v>26.06</v>
+        <v>25.61</v>
       </c>
       <c r="F31" t="n">
-        <v>1293.2</v>
+        <v>1259.9</v>
       </c>
       <c r="G31" t="n">
-        <v>-10.5</v>
+        <v>-11.38</v>
       </c>
       <c r="H31" t="n">
-        <v>-14.37</v>
+        <v>-13.82</v>
       </c>
       <c r="I31" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K31" t="n">

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5018</v>
+        <v>1.5072</v>
       </c>
       <c r="E2" t="n">
-        <v>71.43000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="F2" t="n">
-        <v>1751.8</v>
+        <v>1754.9</v>
       </c>
       <c r="G2" t="n">
-        <v>11.26</v>
+        <v>11.09</v>
       </c>
       <c r="H2" t="n">
-        <v>12.16</v>
+        <v>12.32</v>
       </c>
       <c r="I2" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -529,26 +529,26 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.5002</v>
+        <v>1.4885</v>
       </c>
       <c r="E3" t="n">
-        <v>71.61</v>
+        <v>71.03</v>
       </c>
       <c r="F3" t="n">
-        <v>1731.5</v>
+        <v>1734.5</v>
       </c>
       <c r="G3" t="n">
-        <v>8.83</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>16.63</v>
+        <v>15.53</v>
       </c>
       <c r="I3" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -570,26 +570,26 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.4122</v>
+        <v>1.4079</v>
       </c>
       <c r="E4" t="n">
-        <v>68.06999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="F4" t="n">
         <v>1595.5</v>
       </c>
       <c r="G4" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="H4" t="n">
         <v>10.92</v>
       </c>
       <c r="I4" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -611,26 +611,26 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.3723</v>
+        <v>1.3957</v>
       </c>
       <c r="E5" t="n">
-        <v>66.7</v>
+        <v>67.5</v>
       </c>
       <c r="F5" t="n">
-        <v>1660.1</v>
+        <v>1665.8</v>
       </c>
       <c r="G5" t="n">
-        <v>7.29</v>
+        <v>6.63</v>
       </c>
       <c r="H5" t="n">
-        <v>5.39</v>
+        <v>3.2</v>
       </c>
       <c r="I5" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -639,39 +639,39 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1610612747</v>
+        <v>1610612739</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.3499</v>
+        <v>1.385</v>
       </c>
       <c r="E6" t="n">
-        <v>65.7</v>
+        <v>67</v>
       </c>
       <c r="F6" t="n">
-        <v>1561.9</v>
+        <v>1641.9</v>
       </c>
       <c r="G6" t="n">
-        <v>2.56</v>
+        <v>4.37</v>
       </c>
       <c r="H6" t="n">
-        <v>10.22</v>
+        <v>6.14</v>
       </c>
       <c r="I6" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -693,26 +693,26 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.3315</v>
+        <v>1.3536</v>
       </c>
       <c r="E7" t="n">
-        <v>65.09999999999999</v>
+        <v>65.86</v>
       </c>
       <c r="F7" t="n">
-        <v>1656.8</v>
+        <v>1653.7</v>
       </c>
       <c r="G7" t="n">
-        <v>6.4</v>
+        <v>5.68</v>
       </c>
       <c r="H7" t="n">
-        <v>4.58</v>
+        <v>3.41</v>
       </c>
       <c r="I7" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -721,39 +721,39 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1610612739</v>
+        <v>1610612747</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.3292</v>
+        <v>1.323</v>
       </c>
       <c r="E8" t="n">
-        <v>65.01000000000001</v>
+        <v>64.44</v>
       </c>
       <c r="F8" t="n">
-        <v>1637.7</v>
+        <v>1563</v>
       </c>
       <c r="G8" t="n">
-        <v>4.44</v>
+        <v>2.91</v>
       </c>
       <c r="H8" t="n">
-        <v>4.62</v>
+        <v>10.76</v>
       </c>
       <c r="I8" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -762,39 +762,39 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1610612765</v>
+        <v>1610612766</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.2174</v>
+        <v>1.2416</v>
       </c>
       <c r="E9" t="n">
-        <v>59.27</v>
+        <v>61.43</v>
       </c>
       <c r="F9" t="n">
-        <v>1675.2</v>
+        <v>1580.4</v>
       </c>
       <c r="G9" t="n">
-        <v>7.55</v>
+        <v>3.77</v>
       </c>
       <c r="H9" t="n">
-        <v>14.38</v>
+        <v>10.41</v>
       </c>
       <c r="I9" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -803,39 +803,39 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1610612746</v>
+        <v>1610612765</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.2072</v>
+        <v>1.2385</v>
       </c>
       <c r="E10" t="n">
-        <v>60.14</v>
+        <v>60.43</v>
       </c>
       <c r="F10" t="n">
-        <v>1557.2</v>
+        <v>1679.7</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7</v>
+        <v>7.59</v>
       </c>
       <c r="H10" t="n">
-        <v>9.23</v>
+        <v>11.51</v>
       </c>
       <c r="I10" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -844,39 +844,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1610612766</v>
+        <v>1610612745</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.1896</v>
+        <v>1.2286</v>
       </c>
       <c r="E11" t="n">
-        <v>59.29</v>
+        <v>60.97</v>
       </c>
       <c r="F11" t="n">
-        <v>1586.1</v>
+        <v>1578.4</v>
       </c>
       <c r="G11" t="n">
-        <v>2.61</v>
+        <v>4.81</v>
       </c>
       <c r="H11" t="n">
-        <v>5.24</v>
+        <v>2.69</v>
       </c>
       <c r="I11" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -885,39 +885,39 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.1597</v>
+        <v>1.2156</v>
       </c>
       <c r="E12" t="n">
-        <v>58.07</v>
+        <v>60.38</v>
       </c>
       <c r="F12" t="n">
-        <v>1574</v>
+        <v>1575.1</v>
       </c>
       <c r="G12" t="n">
-        <v>4.53</v>
+        <v>4.54</v>
       </c>
       <c r="H12" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="I12" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -926,39 +926,39 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1610612737</v>
+        <v>1610612746</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.1354</v>
+        <v>1.1799</v>
       </c>
       <c r="E13" t="n">
-        <v>56.91</v>
+        <v>58.9</v>
       </c>
       <c r="F13" t="n">
-        <v>1515.9</v>
+        <v>1557.2</v>
       </c>
       <c r="G13" t="n">
-        <v>1.71</v>
+        <v>2.68</v>
       </c>
       <c r="H13" t="n">
-        <v>9.77</v>
+        <v>9.23</v>
       </c>
       <c r="I13" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -967,39 +967,39 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1610612750</v>
+        <v>1610612737</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.1224</v>
+        <v>1.1462</v>
       </c>
       <c r="E14" t="n">
-        <v>56.45</v>
+        <v>57.34</v>
       </c>
       <c r="F14" t="n">
-        <v>1582.4</v>
+        <v>1516.8</v>
       </c>
       <c r="G14" t="n">
-        <v>3.47</v>
+        <v>1.85</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.83</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1008,39 +1008,39 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1610612761</v>
+        <v>1610612756</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.0762</v>
+        <v>1.0363</v>
       </c>
       <c r="E15" t="n">
-        <v>54.48</v>
+        <v>52.93</v>
       </c>
       <c r="F15" t="n">
-        <v>1506.8</v>
+        <v>1510.5</v>
       </c>
       <c r="G15" t="n">
-        <v>2.67</v>
+        <v>1.66</v>
       </c>
       <c r="H15" t="n">
-        <v>3.59</v>
+        <v>3.47</v>
       </c>
       <c r="I15" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1049,39 +1049,39 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1610612756</v>
+        <v>1610612761</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.0459</v>
+        <v>1.0307</v>
       </c>
       <c r="E16" t="n">
-        <v>53.24</v>
+        <v>52.78</v>
       </c>
       <c r="F16" t="n">
-        <v>1504.2</v>
+        <v>1515.8</v>
       </c>
       <c r="G16" t="n">
-        <v>1.93</v>
+        <v>1.1</v>
       </c>
       <c r="H16" t="n">
-        <v>5.51</v>
+        <v>1.69</v>
       </c>
       <c r="I16" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1090,39 +1090,39 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1610612748</v>
+        <v>1610612755</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.0294</v>
+        <v>0.9957</v>
       </c>
       <c r="E17" t="n">
-        <v>52.5</v>
+        <v>50.92</v>
       </c>
       <c r="F17" t="n">
-        <v>1537</v>
+        <v>1474.3</v>
       </c>
       <c r="G17" t="n">
-        <v>1.84</v>
+        <v>-0.2</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.41</v>
+        <v>-0.67</v>
       </c>
       <c r="I17" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1131,39 +1131,39 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1610612755</v>
+        <v>1610612748</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.0073</v>
+        <v>0.9779</v>
       </c>
       <c r="E18" t="n">
-        <v>51.45</v>
+        <v>50.29</v>
       </c>
       <c r="F18" t="n">
-        <v>1469.6</v>
+        <v>1531.5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.26</v>
+        <v>2.36</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.67</v>
+        <v>-2.54</v>
       </c>
       <c r="I18" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1185,26 +1185,26 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.9463</v>
+        <v>0.9131</v>
       </c>
       <c r="E19" t="n">
-        <v>48.31</v>
+        <v>46.8</v>
       </c>
       <c r="F19" t="n">
         <v>1461.2</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9</v>
+        <v>-0.84</v>
       </c>
       <c r="H19" t="n">
         <v>9.609999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1213,39 +1213,39 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1610612744</v>
+        <v>1610612753</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.9166</v>
+        <v>0.9003</v>
       </c>
       <c r="E20" t="n">
-        <v>47.35</v>
+        <v>46.59</v>
       </c>
       <c r="F20" t="n">
-        <v>1481</v>
+        <v>1515.3</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.38</v>
+        <v>-0.09</v>
       </c>
       <c r="H20" t="n">
-        <v>-6.76</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1254,39 +1254,39 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1610612753</v>
+        <v>1610612744</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8842</v>
+        <v>0.84</v>
       </c>
       <c r="E21" t="n">
-        <v>45.71</v>
+        <v>43.67</v>
       </c>
       <c r="F21" t="n">
-        <v>1524.2</v>
+        <v>1481</v>
       </c>
       <c r="G21" t="n">
-        <v>-1</v>
+        <v>-0.34</v>
       </c>
       <c r="H21" t="n">
-        <v>-9.93</v>
+        <v>-6.76</v>
       </c>
       <c r="I21" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1308,26 +1308,26 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.7677</v>
+        <v>0.7418</v>
       </c>
       <c r="E22" t="n">
-        <v>40.13</v>
+        <v>39.02</v>
       </c>
       <c r="F22" t="n">
         <v>1380.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.75</v>
+        <v>-4.73</v>
       </c>
       <c r="H22" t="n">
         <v>-2.14</v>
       </c>
       <c r="I22" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1349,26 +1349,26 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.7487</v>
+        <v>0.7361</v>
       </c>
       <c r="E23" t="n">
-        <v>39.15</v>
+        <v>38.68</v>
       </c>
       <c r="F23" t="n">
-        <v>1381.5</v>
+        <v>1379.9</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.65</v>
+        <v>-4.25</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.86</v>
+        <v>-6.5</v>
       </c>
       <c r="I23" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1377,39 +1377,39 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1610612742</v>
+        <v>1610612749</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6652</v>
+        <v>0.6855</v>
       </c>
       <c r="E24" t="n">
-        <v>34.8</v>
+        <v>36.03</v>
       </c>
       <c r="F24" t="n">
-        <v>1368.2</v>
+        <v>1389.8</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.09</v>
+        <v>-5.21</v>
       </c>
       <c r="H24" t="n">
-        <v>-7.7</v>
+        <v>-11.77</v>
       </c>
       <c r="I24" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1418,39 +1418,39 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.649</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>33.81</v>
+        <v>33.55</v>
       </c>
       <c r="F25" t="n">
-        <v>1382.6</v>
+        <v>1367.4</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.85</v>
+        <v>-6.31</v>
       </c>
       <c r="H25" t="n">
-        <v>-15.55</v>
+        <v>-10.09</v>
       </c>
       <c r="I25" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1459,39 +1459,39 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1610612749</v>
+        <v>1610612754</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6358</v>
+        <v>0.6362</v>
       </c>
       <c r="E26" t="n">
-        <v>32.87</v>
+        <v>33.31</v>
       </c>
       <c r="F26" t="n">
-        <v>1392.6</v>
+        <v>1333.3</v>
       </c>
       <c r="G26" t="n">
-        <v>-6.25</v>
+        <v>-7.59</v>
       </c>
       <c r="H26" t="n">
-        <v>-16.74</v>
+        <v>-5.86</v>
       </c>
       <c r="I26" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1500,39 +1500,39 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1610612754</v>
+        <v>1610612763</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.6076</v>
+        <v>0.613</v>
       </c>
       <c r="E27" t="n">
-        <v>31.55</v>
+        <v>31.95</v>
       </c>
       <c r="F27" t="n">
-        <v>1333.3</v>
+        <v>1384.2</v>
       </c>
       <c r="G27" t="n">
-        <v>-7.56</v>
+        <v>-5.36</v>
       </c>
       <c r="H27" t="n">
-        <v>-5.86</v>
+        <v>-16.59</v>
       </c>
       <c r="I27" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -1541,39 +1541,39 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1610612762</v>
+        <v>1610612751</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.5759</v>
+        <v>0.5448</v>
       </c>
       <c r="E28" t="n">
-        <v>29.51</v>
+        <v>27.67</v>
       </c>
       <c r="F28" t="n">
-        <v>1309.7</v>
+        <v>1294</v>
       </c>
       <c r="G28" t="n">
-        <v>-8.119999999999999</v>
+        <v>-10.41</v>
       </c>
       <c r="H28" t="n">
-        <v>-8.859999999999999</v>
+        <v>-13.46</v>
       </c>
       <c r="I28" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -1582,39 +1582,39 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.5572</v>
+        <v>0.542</v>
       </c>
       <c r="E29" t="n">
-        <v>28.44</v>
+        <v>27.84</v>
       </c>
       <c r="F29" t="n">
-        <v>1312.7</v>
+        <v>1308</v>
       </c>
       <c r="G29" t="n">
-        <v>-9.68</v>
+        <v>-7.85</v>
       </c>
       <c r="H29" t="n">
-        <v>-8.68</v>
+        <v>-9.5</v>
       </c>
       <c r="I29" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -1623,39 +1623,39 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1610612751</v>
+        <v>1610612758</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5434</v>
+        <v>0.5355</v>
       </c>
       <c r="E30" t="n">
-        <v>27.37</v>
+        <v>27.33</v>
       </c>
       <c r="F30" t="n">
-        <v>1292.1</v>
+        <v>1312.7</v>
       </c>
       <c r="G30" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>-13.35</v>
+        <v>-8.68</v>
       </c>
       <c r="I30" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -1677,26 +1677,26 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.5148</v>
+        <v>0.5212</v>
       </c>
       <c r="E31" t="n">
-        <v>25.61</v>
+        <v>26.16</v>
       </c>
       <c r="F31" t="n">
-        <v>1259.9</v>
+        <v>1258.2</v>
       </c>
       <c r="G31" t="n">
-        <v>-11.38</v>
+        <v>-11.44</v>
       </c>
       <c r="H31" t="n">
-        <v>-13.82</v>
+        <v>-13.96</v>
       </c>
       <c r="I31" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="K31" t="n">

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5072</v>
+        <v>1.5106</v>
       </c>
       <c r="E2" t="n">
-        <v>71.5</v>
+        <v>71.69</v>
       </c>
       <c r="F2" t="n">
         <v>1754.9</v>
@@ -503,11 +503,11 @@
         <v>12.32</v>
       </c>
       <c r="I2" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.4885</v>
+        <v>1.4714</v>
       </c>
       <c r="E3" t="n">
-        <v>71.03</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>1734.5</v>
@@ -544,11 +544,11 @@
         <v>15.53</v>
       </c>
       <c r="I3" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -557,39 +557,39 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1610612743</v>
+        <v>1610612738</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.4079</v>
+        <v>1.3819</v>
       </c>
       <c r="E4" t="n">
-        <v>67.7</v>
+        <v>67.19</v>
       </c>
       <c r="F4" t="n">
-        <v>1595.5</v>
+        <v>1665.8</v>
       </c>
       <c r="G4" t="n">
-        <v>4.76</v>
+        <v>6.63</v>
       </c>
       <c r="H4" t="n">
-        <v>10.92</v>
+        <v>3.2</v>
       </c>
       <c r="I4" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -598,39 +598,39 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1610612738</v>
+        <v>1610612743</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.3957</v>
+        <v>1.3741</v>
       </c>
       <c r="E5" t="n">
-        <v>67.5</v>
+        <v>66.58</v>
       </c>
       <c r="F5" t="n">
-        <v>1665.8</v>
+        <v>1595.5</v>
       </c>
       <c r="G5" t="n">
-        <v>6.63</v>
+        <v>4.76</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2</v>
+        <v>10.92</v>
       </c>
       <c r="I5" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -639,39 +639,39 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1610612739</v>
+        <v>1610612752</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.385</v>
+        <v>1.3477</v>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>65.91</v>
       </c>
       <c r="F6" t="n">
-        <v>1641.9</v>
+        <v>1653.7</v>
       </c>
       <c r="G6" t="n">
-        <v>4.37</v>
+        <v>5.81</v>
       </c>
       <c r="H6" t="n">
-        <v>6.14</v>
+        <v>3.87</v>
       </c>
       <c r="I6" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -680,39 +680,39 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612752</v>
+        <v>1610612739</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.3536</v>
+        <v>1.3443</v>
       </c>
       <c r="E7" t="n">
-        <v>65.86</v>
+        <v>65.38</v>
       </c>
       <c r="F7" t="n">
-        <v>1653.7</v>
+        <v>1642.8</v>
       </c>
       <c r="G7" t="n">
-        <v>5.68</v>
+        <v>3.8</v>
       </c>
       <c r="H7" t="n">
-        <v>3.41</v>
+        <v>2.96</v>
       </c>
       <c r="I7" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -734,26 +734,26 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.323</v>
+        <v>1.3294</v>
       </c>
       <c r="E8" t="n">
-        <v>64.44</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>1563</v>
+        <v>1563.8</v>
       </c>
       <c r="G8" t="n">
-        <v>2.91</v>
+        <v>3.05</v>
       </c>
       <c r="H8" t="n">
-        <v>10.76</v>
+        <v>11.01</v>
       </c>
       <c r="I8" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -762,39 +762,39 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1610612766</v>
+        <v>1610612765</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.2416</v>
+        <v>1.2611</v>
       </c>
       <c r="E9" t="n">
-        <v>61.43</v>
+        <v>61.34</v>
       </c>
       <c r="F9" t="n">
-        <v>1580.4</v>
+        <v>1679.7</v>
       </c>
       <c r="G9" t="n">
-        <v>3.77</v>
+        <v>7.33</v>
       </c>
       <c r="H9" t="n">
-        <v>10.41</v>
+        <v>10.4</v>
       </c>
       <c r="I9" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -803,39 +803,39 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1610612765</v>
+        <v>1610612766</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.2385</v>
+        <v>1.229</v>
       </c>
       <c r="E10" t="n">
-        <v>60.43</v>
+        <v>60.82</v>
       </c>
       <c r="F10" t="n">
-        <v>1679.7</v>
+        <v>1580.4</v>
       </c>
       <c r="G10" t="n">
-        <v>7.59</v>
+        <v>3.77</v>
       </c>
       <c r="H10" t="n">
-        <v>11.51</v>
+        <v>10.41</v>
       </c>
       <c r="I10" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -844,39 +844,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.2286</v>
+        <v>1.2202</v>
       </c>
       <c r="E11" t="n">
-        <v>60.97</v>
+        <v>60.52</v>
       </c>
       <c r="F11" t="n">
-        <v>1578.4</v>
+        <v>1575.1</v>
       </c>
       <c r="G11" t="n">
-        <v>4.81</v>
+        <v>4.54</v>
       </c>
       <c r="H11" t="n">
-        <v>2.69</v>
+        <v>1.42</v>
       </c>
       <c r="I11" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -885,39 +885,39 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.2156</v>
+        <v>1.1945</v>
       </c>
       <c r="E12" t="n">
-        <v>60.38</v>
+        <v>59.65</v>
       </c>
       <c r="F12" t="n">
-        <v>1575.1</v>
+        <v>1578.4</v>
       </c>
       <c r="G12" t="n">
-        <v>4.54</v>
+        <v>4.67</v>
       </c>
       <c r="H12" t="n">
-        <v>1.42</v>
+        <v>2.24</v>
       </c>
       <c r="I12" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -939,26 +939,26 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.1799</v>
+        <v>1.155</v>
       </c>
       <c r="E13" t="n">
-        <v>58.9</v>
+        <v>57.78</v>
       </c>
       <c r="F13" t="n">
-        <v>1557.2</v>
+        <v>1559.9</v>
       </c>
       <c r="G13" t="n">
-        <v>2.68</v>
+        <v>2.2</v>
       </c>
       <c r="H13" t="n">
-        <v>9.23</v>
+        <v>5.77</v>
       </c>
       <c r="I13" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.1462</v>
+        <v>1.1263</v>
       </c>
       <c r="E14" t="n">
-        <v>57.34</v>
+        <v>56.42</v>
       </c>
       <c r="F14" t="n">
         <v>1516.8</v>
@@ -995,11 +995,11 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1008,39 +1008,39 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1610612756</v>
+        <v>1610612761</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.0363</v>
+        <v>1.0587</v>
       </c>
       <c r="E15" t="n">
-        <v>52.93</v>
+        <v>53.81</v>
       </c>
       <c r="F15" t="n">
-        <v>1510.5</v>
+        <v>1515.8</v>
       </c>
       <c r="G15" t="n">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="H15" t="n">
-        <v>3.47</v>
+        <v>2.8</v>
       </c>
       <c r="I15" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1049,39 +1049,39 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1610612761</v>
+        <v>1610612756</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.0307</v>
+        <v>1.0476</v>
       </c>
       <c r="E16" t="n">
-        <v>52.78</v>
+        <v>53.36</v>
       </c>
       <c r="F16" t="n">
-        <v>1515.8</v>
+        <v>1510.5</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1</v>
+        <v>1.66</v>
       </c>
       <c r="H16" t="n">
-        <v>1.69</v>
+        <v>3.47</v>
       </c>
       <c r="I16" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1090,39 +1090,39 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1610612755</v>
+        <v>1610612748</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.9957</v>
+        <v>0.9952</v>
       </c>
       <c r="E17" t="n">
-        <v>50.92</v>
+        <v>50.96</v>
       </c>
       <c r="F17" t="n">
-        <v>1474.3</v>
+        <v>1531.5</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2</v>
+        <v>2.36</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.67</v>
+        <v>-2.54</v>
       </c>
       <c r="I17" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1131,39 +1131,39 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1610612748</v>
+        <v>1610612755</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9779</v>
+        <v>0.9916</v>
       </c>
       <c r="E18" t="n">
-        <v>50.29</v>
+        <v>50.68</v>
       </c>
       <c r="F18" t="n">
-        <v>1531.5</v>
+        <v>1474.3</v>
       </c>
       <c r="G18" t="n">
-        <v>2.36</v>
+        <v>-0.2</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.54</v>
+        <v>-0.67</v>
       </c>
       <c r="I18" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1185,26 +1185,26 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.9131</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>46.8</v>
+        <v>47.12</v>
       </c>
       <c r="F19" t="n">
-        <v>1461.2</v>
+        <v>1463</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.84</v>
+        <v>-1.13</v>
       </c>
       <c r="H19" t="n">
-        <v>9.609999999999999</v>
+        <v>10.17</v>
       </c>
       <c r="I19" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1213,39 +1213,39 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1610612753</v>
+        <v>1610612744</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.9003</v>
+        <v>0.8956</v>
       </c>
       <c r="E20" t="n">
-        <v>46.59</v>
+        <v>46.38</v>
       </c>
       <c r="F20" t="n">
-        <v>1515.3</v>
+        <v>1481</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.09</v>
+        <v>-0.34</v>
       </c>
       <c r="H20" t="n">
-        <v>-9.460000000000001</v>
+        <v>-6.76</v>
       </c>
       <c r="I20" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1254,39 +1254,39 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1610612744</v>
+        <v>1610612753</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.84</v>
+        <v>0.8879</v>
       </c>
       <c r="E21" t="n">
-        <v>43.67</v>
+        <v>45.91</v>
       </c>
       <c r="F21" t="n">
-        <v>1481</v>
+        <v>1515.3</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.34</v>
+        <v>-0.09</v>
       </c>
       <c r="H21" t="n">
-        <v>-6.76</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.7418</v>
+        <v>0.7518</v>
       </c>
       <c r="E22" t="n">
-        <v>39.02</v>
+        <v>39.14</v>
       </c>
       <c r="F22" t="n">
         <v>1380.2</v>
@@ -1323,11 +1323,11 @@
         <v>-2.14</v>
       </c>
       <c r="I22" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.7361</v>
+        <v>0.7331</v>
       </c>
       <c r="E23" t="n">
-        <v>38.68</v>
+        <v>38.36</v>
       </c>
       <c r="F23" t="n">
         <v>1379.9</v>
@@ -1364,11 +1364,11 @@
         <v>-6.5</v>
       </c>
       <c r="I23" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1390,26 +1390,26 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6855</v>
+        <v>0.6704</v>
       </c>
       <c r="E24" t="n">
-        <v>36.03</v>
+        <v>35.05</v>
       </c>
       <c r="F24" t="n">
         <v>1389.8</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.21</v>
+        <v>-5.42</v>
       </c>
       <c r="H24" t="n">
-        <v>-11.77</v>
+        <v>-12.65</v>
       </c>
       <c r="I24" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1418,39 +1418,39 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1610612742</v>
+        <v>1610612754</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.636</v>
       </c>
       <c r="E25" t="n">
-        <v>33.55</v>
+        <v>33.09</v>
       </c>
       <c r="F25" t="n">
-        <v>1367.4</v>
+        <v>1333.3</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.31</v>
+        <v>-7.59</v>
       </c>
       <c r="H25" t="n">
-        <v>-10.09</v>
+        <v>-5.86</v>
       </c>
       <c r="I25" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1459,39 +1459,39 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1610612754</v>
+        <v>1610612763</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6362</v>
+        <v>0.6321</v>
       </c>
       <c r="E26" t="n">
-        <v>33.31</v>
+        <v>33.01</v>
       </c>
       <c r="F26" t="n">
-        <v>1333.3</v>
+        <v>1384.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-7.59</v>
+        <v>-5.36</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.86</v>
+        <v>-16.59</v>
       </c>
       <c r="I26" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1500,39 +1500,39 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.613</v>
+        <v>0.6274</v>
       </c>
       <c r="E27" t="n">
-        <v>31.95</v>
+        <v>32.85</v>
       </c>
       <c r="F27" t="n">
-        <v>1384.2</v>
+        <v>1367.4</v>
       </c>
       <c r="G27" t="n">
-        <v>-5.36</v>
+        <v>-6.06</v>
       </c>
       <c r="H27" t="n">
-        <v>-16.59</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -1541,39 +1541,39 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1610612751</v>
+        <v>1610612762</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.5448</v>
+        <v>0.5746</v>
       </c>
       <c r="E28" t="n">
-        <v>27.67</v>
+        <v>29.39</v>
       </c>
       <c r="F28" t="n">
-        <v>1294</v>
+        <v>1308</v>
       </c>
       <c r="G28" t="n">
-        <v>-10.41</v>
+        <v>-7.85</v>
       </c>
       <c r="H28" t="n">
-        <v>-13.46</v>
+        <v>-9.5</v>
       </c>
       <c r="I28" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -1582,39 +1582,39 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.542</v>
+        <v>0.5544</v>
       </c>
       <c r="E29" t="n">
-        <v>27.84</v>
+        <v>28.25</v>
       </c>
       <c r="F29" t="n">
-        <v>1308</v>
+        <v>1312.7</v>
       </c>
       <c r="G29" t="n">
-        <v>-7.85</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>-9.5</v>
+        <v>-8.68</v>
       </c>
       <c r="I29" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -1623,39 +1623,39 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1610612758</v>
+        <v>1610612751</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5355</v>
+        <v>0.5438</v>
       </c>
       <c r="E30" t="n">
-        <v>27.33</v>
+        <v>27.37</v>
       </c>
       <c r="F30" t="n">
-        <v>1312.7</v>
+        <v>1294</v>
       </c>
       <c r="G30" t="n">
-        <v>-9.699999999999999</v>
+        <v>-10.41</v>
       </c>
       <c r="H30" t="n">
-        <v>-8.68</v>
+        <v>-13.46</v>
       </c>
       <c r="I30" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.5212</v>
+        <v>0.5314</v>
       </c>
       <c r="E31" t="n">
-        <v>26.16</v>
+        <v>26.71</v>
       </c>
       <c r="F31" t="n">
         <v>1258.2</v>
@@ -1692,11 +1692,11 @@
         <v>-13.96</v>
       </c>
       <c r="I31" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K31" t="n">

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5106</v>
+        <v>1.5368</v>
       </c>
       <c r="E2" t="n">
-        <v>71.69</v>
+        <v>72.42</v>
       </c>
       <c r="F2" t="n">
         <v>1754.9</v>
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.4714</v>
+        <v>1.4893</v>
       </c>
       <c r="E3" t="n">
-        <v>70.43000000000001</v>
+        <v>70.95</v>
       </c>
       <c r="F3" t="n">
         <v>1734.5</v>
@@ -557,32 +557,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1610612738</v>
+        <v>1610612743</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.3819</v>
+        <v>1.4106</v>
       </c>
       <c r="E4" t="n">
-        <v>67.19</v>
+        <v>67.98</v>
       </c>
       <c r="F4" t="n">
-        <v>1665.8</v>
+        <v>1595.5</v>
       </c>
       <c r="G4" t="n">
-        <v>6.63</v>
+        <v>4.76</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2</v>
+        <v>10.92</v>
       </c>
       <c r="I4" t="n">
         <v>162</v>
@@ -598,32 +598,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1610612743</v>
+        <v>1610612738</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.3741</v>
+        <v>1.4021</v>
       </c>
       <c r="E5" t="n">
-        <v>66.58</v>
+        <v>67.73</v>
       </c>
       <c r="F5" t="n">
-        <v>1595.5</v>
+        <v>1665.8</v>
       </c>
       <c r="G5" t="n">
-        <v>4.76</v>
+        <v>6.63</v>
       </c>
       <c r="H5" t="n">
-        <v>10.92</v>
+        <v>3.2</v>
       </c>
       <c r="I5" t="n">
         <v>162</v>
@@ -639,32 +639,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1610612752</v>
+        <v>1610612739</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.3477</v>
+        <v>1.3823</v>
       </c>
       <c r="E6" t="n">
-        <v>65.91</v>
+        <v>66.83</v>
       </c>
       <c r="F6" t="n">
-        <v>1653.7</v>
+        <v>1642.8</v>
       </c>
       <c r="G6" t="n">
-        <v>5.81</v>
+        <v>3.8</v>
       </c>
       <c r="H6" t="n">
-        <v>3.87</v>
+        <v>2.96</v>
       </c>
       <c r="I6" t="n">
         <v>162</v>
@@ -680,32 +680,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612739</v>
+        <v>1610612752</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.3443</v>
+        <v>1.3649</v>
       </c>
       <c r="E7" t="n">
-        <v>65.38</v>
+        <v>66.36</v>
       </c>
       <c r="F7" t="n">
-        <v>1642.8</v>
+        <v>1653.7</v>
       </c>
       <c r="G7" t="n">
-        <v>3.8</v>
+        <v>5.81</v>
       </c>
       <c r="H7" t="n">
-        <v>2.96</v>
+        <v>3.87</v>
       </c>
       <c r="I7" t="n">
         <v>162</v>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.3294</v>
+        <v>1.3625</v>
       </c>
       <c r="E8" t="n">
-        <v>64.84999999999999</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="F8" t="n">
         <v>1563.8</v>
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.2611</v>
+        <v>1.2432</v>
       </c>
       <c r="E9" t="n">
-        <v>61.34</v>
+        <v>60.78</v>
       </c>
       <c r="F9" t="n">
         <v>1679.7</v>
@@ -803,32 +803,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1610612766</v>
+        <v>1610612750</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.229</v>
+        <v>1.2314</v>
       </c>
       <c r="E10" t="n">
-        <v>60.82</v>
+        <v>60.98</v>
       </c>
       <c r="F10" t="n">
-        <v>1580.4</v>
+        <v>1575.1</v>
       </c>
       <c r="G10" t="n">
-        <v>3.77</v>
+        <v>4.54</v>
       </c>
       <c r="H10" t="n">
-        <v>10.41</v>
+        <v>1.42</v>
       </c>
       <c r="I10" t="n">
         <v>162</v>
@@ -844,32 +844,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1610612750</v>
+        <v>1610612766</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.2202</v>
+        <v>1.2226</v>
       </c>
       <c r="E11" t="n">
-        <v>60.52</v>
+        <v>60.5</v>
       </c>
       <c r="F11" t="n">
-        <v>1575.1</v>
+        <v>1580.4</v>
       </c>
       <c r="G11" t="n">
-        <v>4.54</v>
+        <v>3.77</v>
       </c>
       <c r="H11" t="n">
-        <v>1.42</v>
+        <v>10.41</v>
       </c>
       <c r="I11" t="n">
         <v>162</v>
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.1945</v>
+        <v>1.1813</v>
       </c>
       <c r="E12" t="n">
-        <v>59.65</v>
+        <v>59</v>
       </c>
       <c r="F12" t="n">
         <v>1578.4</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.155</v>
+        <v>1.1502</v>
       </c>
       <c r="E13" t="n">
-        <v>57.78</v>
+        <v>57.7</v>
       </c>
       <c r="F13" t="n">
         <v>1559.9</v>
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.1263</v>
+        <v>1.1273</v>
       </c>
       <c r="E14" t="n">
-        <v>56.42</v>
+        <v>56.58</v>
       </c>
       <c r="F14" t="n">
         <v>1516.8</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.0587</v>
+        <v>1.0598</v>
       </c>
       <c r="E15" t="n">
-        <v>53.81</v>
+        <v>53.95</v>
       </c>
       <c r="F15" t="n">
         <v>1515.8</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.0476</v>
+        <v>1.0369</v>
       </c>
       <c r="E16" t="n">
-        <v>53.36</v>
+        <v>52.98</v>
       </c>
       <c r="F16" t="n">
         <v>1510.5</v>
@@ -1090,32 +1090,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1610612748</v>
+        <v>1610612755</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.9952</v>
+        <v>0.9959</v>
       </c>
       <c r="E17" t="n">
-        <v>50.96</v>
+        <v>51.06</v>
       </c>
       <c r="F17" t="n">
-        <v>1531.5</v>
+        <v>1474.3</v>
       </c>
       <c r="G17" t="n">
-        <v>2.36</v>
+        <v>-0.2</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.54</v>
+        <v>-0.67</v>
       </c>
       <c r="I17" t="n">
         <v>162</v>
@@ -1131,32 +1131,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1610612755</v>
+        <v>1610612748</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9916</v>
+        <v>0.9959</v>
       </c>
       <c r="E18" t="n">
-        <v>50.68</v>
+        <v>51.05</v>
       </c>
       <c r="F18" t="n">
-        <v>1474.3</v>
+        <v>1531.5</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2</v>
+        <v>2.36</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.67</v>
+        <v>-2.54</v>
       </c>
       <c r="I18" t="n">
         <v>162</v>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.9229000000000001</v>
+        <v>0.8991</v>
       </c>
       <c r="E19" t="n">
-        <v>47.12</v>
+        <v>46.38</v>
       </c>
       <c r="F19" t="n">
         <v>1463</v>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.8956</v>
+        <v>0.886</v>
       </c>
       <c r="E20" t="n">
-        <v>46.38</v>
+        <v>46.16</v>
       </c>
       <c r="F20" t="n">
         <v>1481</v>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8879</v>
+        <v>0.8779</v>
       </c>
       <c r="E21" t="n">
-        <v>45.91</v>
+        <v>45.68</v>
       </c>
       <c r="F21" t="n">
         <v>1515.3</v>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.7518</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>39.14</v>
+        <v>39</v>
       </c>
       <c r="F22" t="n">
         <v>1380.2</v>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.7331</v>
+        <v>0.7326</v>
       </c>
       <c r="E23" t="n">
-        <v>38.36</v>
+        <v>38.4</v>
       </c>
       <c r="F23" t="n">
         <v>1379.9</v>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6704</v>
+        <v>0.6564</v>
       </c>
       <c r="E24" t="n">
-        <v>35.05</v>
+        <v>34.53</v>
       </c>
       <c r="F24" t="n">
         <v>1389.8</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.636</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>33.09</v>
+        <v>33.25</v>
       </c>
       <c r="F25" t="n">
         <v>1333.3</v>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6321</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>33.01</v>
+        <v>32.4</v>
       </c>
       <c r="F26" t="n">
         <v>1384.2</v>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.6274</v>
+        <v>0.6161</v>
       </c>
       <c r="E27" t="n">
-        <v>32.85</v>
+        <v>32.45</v>
       </c>
       <c r="F27" t="n">
         <v>1367.4</v>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.5746</v>
+        <v>0.5597</v>
       </c>
       <c r="E28" t="n">
-        <v>29.39</v>
+        <v>28.55</v>
       </c>
       <c r="F28" t="n">
         <v>1308</v>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.5544</v>
+        <v>0.5426</v>
       </c>
       <c r="E29" t="n">
-        <v>28.25</v>
+        <v>27.8</v>
       </c>
       <c r="F29" t="n">
         <v>1312.7</v>
@@ -1623,32 +1623,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5438</v>
+        <v>0.5258</v>
       </c>
       <c r="E30" t="n">
-        <v>27.37</v>
+        <v>26.49</v>
       </c>
       <c r="F30" t="n">
-        <v>1294</v>
+        <v>1258.2</v>
       </c>
       <c r="G30" t="n">
-        <v>-10.41</v>
+        <v>-11.44</v>
       </c>
       <c r="H30" t="n">
-        <v>-13.46</v>
+        <v>-13.96</v>
       </c>
       <c r="I30" t="n">
         <v>162</v>
@@ -1664,32 +1664,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.5314</v>
+        <v>0.5144</v>
       </c>
       <c r="E31" t="n">
-        <v>26.71</v>
+        <v>25.99</v>
       </c>
       <c r="F31" t="n">
-        <v>1258.2</v>
+        <v>1294</v>
       </c>
       <c r="G31" t="n">
-        <v>-11.44</v>
+        <v>-10.41</v>
       </c>
       <c r="H31" t="n">
-        <v>-13.96</v>
+        <v>-13.46</v>
       </c>
       <c r="I31" t="n">
         <v>162</v>

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5368</v>
+        <v>1.5319</v>
       </c>
       <c r="E2" t="n">
-        <v>72.42</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>1754.9</v>
       </c>
       <c r="G2" t="n">
-        <v>11.09</v>
+        <v>11.12</v>
       </c>
       <c r="H2" t="n">
         <v>12.32</v>
       </c>
       <c r="I2" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -529,26 +529,26 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.4893</v>
+        <v>1.4885</v>
       </c>
       <c r="E3" t="n">
-        <v>70.95</v>
+        <v>70.77</v>
       </c>
       <c r="F3" t="n">
-        <v>1734.5</v>
+        <v>1735.4</v>
       </c>
       <c r="G3" t="n">
-        <v>8.720000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>15.53</v>
+        <v>15.4</v>
       </c>
       <c r="I3" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -557,39 +557,39 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1610612743</v>
+        <v>1610612738</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.4106</v>
+        <v>1.4115</v>
       </c>
       <c r="E4" t="n">
-        <v>67.98</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>1595.5</v>
+        <v>1660.9</v>
       </c>
       <c r="G4" t="n">
-        <v>4.76</v>
+        <v>7.21</v>
       </c>
       <c r="H4" t="n">
-        <v>10.92</v>
+        <v>6.25</v>
       </c>
       <c r="I4" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -598,39 +598,39 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1610612738</v>
+        <v>1610612743</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.4021</v>
+        <v>1.3876</v>
       </c>
       <c r="E5" t="n">
-        <v>67.73</v>
+        <v>67.05</v>
       </c>
       <c r="F5" t="n">
-        <v>1665.8</v>
+        <v>1599</v>
       </c>
       <c r="G5" t="n">
-        <v>6.63</v>
+        <v>4.8</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -652,26 +652,26 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.3823</v>
+        <v>1.381</v>
       </c>
       <c r="E6" t="n">
-        <v>66.83</v>
+        <v>66.73</v>
       </c>
       <c r="F6" t="n">
         <v>1642.8</v>
       </c>
       <c r="G6" t="n">
-        <v>3.8</v>
+        <v>3.69</v>
       </c>
       <c r="H6" t="n">
         <v>2.96</v>
       </c>
       <c r="I6" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -693,26 +693,26 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.3649</v>
+        <v>1.3654</v>
       </c>
       <c r="E7" t="n">
-        <v>66.36</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>1653.7</v>
+        <v>1647.3</v>
       </c>
       <c r="G7" t="n">
-        <v>5.81</v>
+        <v>6.42</v>
       </c>
       <c r="H7" t="n">
-        <v>3.87</v>
+        <v>5.64</v>
       </c>
       <c r="I7" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -734,26 +734,26 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.3625</v>
+        <v>1.3536</v>
       </c>
       <c r="E8" t="n">
-        <v>66.06999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="F8" t="n">
         <v>1563.8</v>
       </c>
       <c r="G8" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H8" t="n">
         <v>11.01</v>
       </c>
       <c r="I8" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -775,26 +775,26 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.2432</v>
+        <v>1.2443</v>
       </c>
       <c r="E9" t="n">
-        <v>60.78</v>
+        <v>60.72</v>
       </c>
       <c r="F9" t="n">
         <v>1679.7</v>
       </c>
       <c r="G9" t="n">
-        <v>7.33</v>
+        <v>7.41</v>
       </c>
       <c r="H9" t="n">
         <v>10.4</v>
       </c>
       <c r="I9" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -816,26 +816,26 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.2314</v>
+        <v>1.2267</v>
       </c>
       <c r="E10" t="n">
-        <v>60.98</v>
+        <v>60.75</v>
       </c>
       <c r="F10" t="n">
         <v>1575.1</v>
       </c>
       <c r="G10" t="n">
-        <v>4.54</v>
+        <v>4.69</v>
       </c>
       <c r="H10" t="n">
         <v>1.42</v>
       </c>
       <c r="I10" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -857,26 +857,26 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.2226</v>
+        <v>1.2203</v>
       </c>
       <c r="E11" t="n">
-        <v>60.5</v>
+        <v>60.39</v>
       </c>
       <c r="F11" t="n">
         <v>1580.4</v>
       </c>
       <c r="G11" t="n">
-        <v>3.77</v>
+        <v>3.62</v>
       </c>
       <c r="H11" t="n">
-        <v>10.41</v>
+        <v>10.53</v>
       </c>
       <c r="I11" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -898,26 +898,26 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.1813</v>
+        <v>1.2159</v>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>60.4</v>
       </c>
       <c r="F12" t="n">
-        <v>1578.4</v>
+        <v>1584.8</v>
       </c>
       <c r="G12" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="H12" t="n">
-        <v>2.24</v>
+        <v>6.9</v>
       </c>
       <c r="I12" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -926,39 +926,39 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1610612746</v>
+        <v>1610612737</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.1502</v>
+        <v>1.1553</v>
       </c>
       <c r="E13" t="n">
-        <v>57.7</v>
+        <v>57.77</v>
       </c>
       <c r="F13" t="n">
-        <v>1559.9</v>
+        <v>1521.6</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="H13" t="n">
-        <v>5.77</v>
+        <v>11.61</v>
       </c>
       <c r="I13" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -967,39 +967,39 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1610612737</v>
+        <v>1610612746</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.1273</v>
+        <v>1.1494</v>
       </c>
       <c r="E14" t="n">
-        <v>56.58</v>
+        <v>57.67</v>
       </c>
       <c r="F14" t="n">
-        <v>1516.8</v>
+        <v>1559.9</v>
       </c>
       <c r="G14" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="H14" t="n">
-        <v>9.800000000000001</v>
+        <v>5.77</v>
       </c>
       <c r="I14" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1021,26 +1021,26 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.0598</v>
+        <v>1.06</v>
       </c>
       <c r="E15" t="n">
-        <v>53.95</v>
+        <v>53.91</v>
       </c>
       <c r="F15" t="n">
-        <v>1515.8</v>
+        <v>1514</v>
       </c>
       <c r="G15" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8</v>
+        <v>3.16</v>
       </c>
       <c r="I15" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1062,26 +1062,26 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.0369</v>
+        <v>1.0358</v>
       </c>
       <c r="E16" t="n">
-        <v>52.98</v>
+        <v>52.9</v>
       </c>
       <c r="F16" t="n">
         <v>1510.5</v>
       </c>
       <c r="G16" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H16" t="n">
         <v>3.47</v>
       </c>
       <c r="I16" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1103,26 +1103,26 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.9959</v>
+        <v>1.0077</v>
       </c>
       <c r="E17" t="n">
-        <v>51.06</v>
+        <v>51.68</v>
       </c>
       <c r="F17" t="n">
-        <v>1474.3</v>
+        <v>1472.2</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2</v>
+        <v>0.57</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.67</v>
+        <v>0.53</v>
       </c>
       <c r="I17" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1144,26 +1144,26 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9959</v>
+        <v>0.9724</v>
       </c>
       <c r="E18" t="n">
-        <v>51.05</v>
+        <v>49.97</v>
       </c>
       <c r="F18" t="n">
-        <v>1531.5</v>
+        <v>1533.6</v>
       </c>
       <c r="G18" t="n">
-        <v>2.36</v>
+        <v>1.73</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.54</v>
+        <v>-6.55</v>
       </c>
       <c r="I18" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1185,26 +1185,26 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.8991</v>
+        <v>0.899</v>
       </c>
       <c r="E19" t="n">
-        <v>46.38</v>
+        <v>46.35</v>
       </c>
       <c r="F19" t="n">
         <v>1463</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.13</v>
+        <v>-1.16</v>
       </c>
       <c r="H19" t="n">
         <v>10.17</v>
       </c>
       <c r="I19" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1226,26 +1226,26 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.886</v>
+        <v>0.8827</v>
       </c>
       <c r="E20" t="n">
-        <v>46.16</v>
+        <v>46.08</v>
       </c>
       <c r="F20" t="n">
-        <v>1481</v>
+        <v>1477.5</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.34</v>
+        <v>-0.42</v>
       </c>
       <c r="H20" t="n">
-        <v>-6.76</v>
+        <v>-7.04</v>
       </c>
       <c r="I20" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1267,26 +1267,26 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8779</v>
+        <v>0.8803</v>
       </c>
       <c r="E21" t="n">
-        <v>45.68</v>
+        <v>45.85</v>
       </c>
       <c r="F21" t="n">
-        <v>1515.3</v>
+        <v>1517.6</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.09</v>
+        <v>-0.9</v>
       </c>
       <c r="H21" t="n">
-        <v>-9.460000000000001</v>
+        <v>-12.71</v>
       </c>
       <c r="I21" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1308,26 +1308,26 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7429</v>
       </c>
       <c r="E22" t="n">
-        <v>39</v>
+        <v>39.02</v>
       </c>
       <c r="F22" t="n">
         <v>1380.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.73</v>
+        <v>-4.66</v>
       </c>
       <c r="H22" t="n">
         <v>-2.14</v>
       </c>
       <c r="I22" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1349,26 +1349,26 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.7326</v>
+        <v>0.7284</v>
       </c>
       <c r="E23" t="n">
-        <v>38.4</v>
+        <v>38.19</v>
       </c>
       <c r="F23" t="n">
-        <v>1379.9</v>
+        <v>1379</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.25</v>
+        <v>-4.34</v>
       </c>
       <c r="H23" t="n">
-        <v>-6.5</v>
+        <v>-9.01</v>
       </c>
       <c r="I23" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1390,26 +1390,26 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6564</v>
+        <v>0.6552</v>
       </c>
       <c r="E24" t="n">
-        <v>34.53</v>
+        <v>34.42</v>
       </c>
       <c r="F24" t="n">
-        <v>1389.8</v>
+        <v>1392.8</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.42</v>
+        <v>-5.94</v>
       </c>
       <c r="H24" t="n">
-        <v>-12.65</v>
+        <v>-13.23</v>
       </c>
       <c r="I24" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1431,26 +1431,26 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.6494</v>
       </c>
       <c r="E25" t="n">
-        <v>33.25</v>
+        <v>34</v>
       </c>
       <c r="F25" t="n">
-        <v>1333.3</v>
+        <v>1338.8</v>
       </c>
       <c r="G25" t="n">
-        <v>-7.59</v>
+        <v>-7.13</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.86</v>
+        <v>-3.16</v>
       </c>
       <c r="I25" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1459,39 +1459,39 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6163999999999999</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>32.4</v>
+        <v>33.52</v>
       </c>
       <c r="F26" t="n">
-        <v>1384.2</v>
+        <v>1367.4</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.36</v>
+        <v>-6.08</v>
       </c>
       <c r="H26" t="n">
-        <v>-16.59</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1500,39 +1500,39 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.6161</v>
+        <v>0.5967</v>
       </c>
       <c r="E27" t="n">
-        <v>32.45</v>
+        <v>31.31</v>
       </c>
       <c r="F27" t="n">
-        <v>1367.4</v>
+        <v>1379.7</v>
       </c>
       <c r="G27" t="n">
-        <v>-6.06</v>
+        <v>-5.27</v>
       </c>
       <c r="H27" t="n">
-        <v>-9.220000000000001</v>
+        <v>-16.55</v>
       </c>
       <c r="I27" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -1554,26 +1554,26 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.5597</v>
+        <v>0.5604</v>
       </c>
       <c r="E28" t="n">
-        <v>28.55</v>
+        <v>28.73</v>
       </c>
       <c r="F28" t="n">
-        <v>1308</v>
+        <v>1307.1</v>
       </c>
       <c r="G28" t="n">
-        <v>-7.85</v>
+        <v>-7.98</v>
       </c>
       <c r="H28" t="n">
-        <v>-9.5</v>
+        <v>-9.15</v>
       </c>
       <c r="I28" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -1595,26 +1595,26 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.5426</v>
+        <v>0.5463</v>
       </c>
       <c r="E29" t="n">
-        <v>27.8</v>
+        <v>28.07</v>
       </c>
       <c r="F29" t="n">
-        <v>1312.7</v>
+        <v>1310.8</v>
       </c>
       <c r="G29" t="n">
-        <v>-9.699999999999999</v>
+        <v>-9.17</v>
       </c>
       <c r="H29" t="n">
-        <v>-8.68</v>
+        <v>-8.6</v>
       </c>
       <c r="I29" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -1623,39 +1623,39 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5258</v>
+        <v>0.5178</v>
       </c>
       <c r="E30" t="n">
-        <v>26.49</v>
+        <v>26.33</v>
       </c>
       <c r="F30" t="n">
-        <v>1258.2</v>
+        <v>1294</v>
       </c>
       <c r="G30" t="n">
-        <v>-11.44</v>
+        <v>-10.5</v>
       </c>
       <c r="H30" t="n">
-        <v>-13.96</v>
+        <v>-13.46</v>
       </c>
       <c r="I30" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -1664,39 +1664,39 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.5144</v>
+        <v>0.4989</v>
       </c>
       <c r="E31" t="n">
-        <v>25.99</v>
+        <v>24.85</v>
       </c>
       <c r="F31" t="n">
-        <v>1294</v>
+        <v>1257.3</v>
       </c>
       <c r="G31" t="n">
-        <v>-10.41</v>
+        <v>-11.66</v>
       </c>
       <c r="H31" t="n">
-        <v>-13.46</v>
+        <v>-15.61</v>
       </c>
       <c r="I31" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K31" t="n">

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5319</v>
+        <v>1.557</v>
       </c>
       <c r="E2" t="n">
-        <v>72.20999999999999</v>
+        <v>73.13</v>
       </c>
       <c r="F2" t="n">
-        <v>1754.9</v>
+        <v>1757.8</v>
       </c>
       <c r="G2" t="n">
-        <v>11.12</v>
+        <v>11.98</v>
       </c>
       <c r="H2" t="n">
-        <v>12.32</v>
+        <v>15.81</v>
       </c>
       <c r="I2" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -529,26 +529,26 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.4885</v>
+        <v>1.5013</v>
       </c>
       <c r="E3" t="n">
-        <v>70.77</v>
+        <v>71.37</v>
       </c>
       <c r="F3" t="n">
-        <v>1735.4</v>
+        <v>1737.9</v>
       </c>
       <c r="G3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="H3" t="n">
-        <v>15.4</v>
+        <v>17.4</v>
       </c>
       <c r="I3" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.4115</v>
+        <v>1.4162</v>
       </c>
       <c r="E4" t="n">
-        <v>68.20999999999999</v>
+        <v>68.45</v>
       </c>
       <c r="F4" t="n">
         <v>1660.9</v>
@@ -585,11 +585,11 @@
         <v>6.25</v>
       </c>
       <c r="I4" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -598,39 +598,39 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1610612743</v>
+        <v>1610612739</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.3876</v>
+        <v>1.387</v>
       </c>
       <c r="E5" t="n">
         <v>67.05</v>
       </c>
       <c r="F5" t="n">
-        <v>1599</v>
+        <v>1637.4</v>
       </c>
       <c r="G5" t="n">
-        <v>4.8</v>
+        <v>4.26</v>
       </c>
       <c r="H5" t="n">
-        <v>8.300000000000001</v>
+        <v>4.65</v>
       </c>
       <c r="I5" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -639,39 +639,39 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1610612739</v>
+        <v>1610612743</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.381</v>
+        <v>1.3807</v>
       </c>
       <c r="E6" t="n">
-        <v>66.73</v>
+        <v>66.77</v>
       </c>
       <c r="F6" t="n">
-        <v>1642.8</v>
+        <v>1599</v>
       </c>
       <c r="G6" t="n">
-        <v>3.69</v>
+        <v>4.8</v>
       </c>
       <c r="H6" t="n">
-        <v>2.96</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.3654</v>
+        <v>1.3679</v>
       </c>
       <c r="E7" t="n">
-        <v>66.45999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F7" t="n">
         <v>1647.3</v>
@@ -708,11 +708,11 @@
         <v>5.64</v>
       </c>
       <c r="I7" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -734,26 +734,26 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.3536</v>
+        <v>1.3293</v>
       </c>
       <c r="E8" t="n">
-        <v>65.7</v>
+        <v>64.64</v>
       </c>
       <c r="F8" t="n">
-        <v>1563.8</v>
+        <v>1569.2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.98</v>
+        <v>1.91</v>
       </c>
       <c r="H8" t="n">
-        <v>11.01</v>
+        <v>5.84</v>
       </c>
       <c r="I8" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -775,26 +775,26 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.2443</v>
+        <v>1.244</v>
       </c>
       <c r="E9" t="n">
-        <v>60.72</v>
+        <v>60.75</v>
       </c>
       <c r="F9" t="n">
-        <v>1679.7</v>
+        <v>1681.5</v>
       </c>
       <c r="G9" t="n">
-        <v>7.41</v>
+        <v>7.29</v>
       </c>
       <c r="H9" t="n">
-        <v>10.4</v>
+        <v>9.34</v>
       </c>
       <c r="I9" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -816,26 +816,26 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.2267</v>
+        <v>1.2248</v>
       </c>
       <c r="E10" t="n">
-        <v>60.75</v>
+        <v>60.78</v>
       </c>
       <c r="F10" t="n">
-        <v>1575.1</v>
+        <v>1579.1</v>
       </c>
       <c r="G10" t="n">
-        <v>4.69</v>
+        <v>3.91</v>
       </c>
       <c r="H10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="I10" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -844,39 +844,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1610612766</v>
+        <v>1610612745</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.2203</v>
+        <v>1.2185</v>
       </c>
       <c r="E11" t="n">
-        <v>60.39</v>
+        <v>60.54</v>
       </c>
       <c r="F11" t="n">
-        <v>1580.4</v>
+        <v>1584.8</v>
       </c>
       <c r="G11" t="n">
-        <v>3.62</v>
+        <v>4.5</v>
       </c>
       <c r="H11" t="n">
-        <v>10.53</v>
+        <v>6.9</v>
       </c>
       <c r="I11" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -885,39 +885,39 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1610612745</v>
+        <v>1610612766</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.2159</v>
+        <v>1.2049</v>
       </c>
       <c r="E12" t="n">
-        <v>60.4</v>
+        <v>59.83</v>
       </c>
       <c r="F12" t="n">
-        <v>1584.8</v>
+        <v>1583</v>
       </c>
       <c r="G12" t="n">
-        <v>4.5</v>
+        <v>3.87</v>
       </c>
       <c r="H12" t="n">
-        <v>6.9</v>
+        <v>12.06</v>
       </c>
       <c r="I12" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.1553</v>
+        <v>1.1477</v>
       </c>
       <c r="E13" t="n">
-        <v>57.77</v>
+        <v>57.55</v>
       </c>
       <c r="F13" t="n">
         <v>1521.6</v>
@@ -954,11 +954,11 @@
         <v>11.61</v>
       </c>
       <c r="I13" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -980,26 +980,26 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.1494</v>
+        <v>1.1249</v>
       </c>
       <c r="E14" t="n">
-        <v>57.67</v>
+        <v>56.64</v>
       </c>
       <c r="F14" t="n">
-        <v>1559.9</v>
+        <v>1555.4</v>
       </c>
       <c r="G14" t="n">
-        <v>2.18</v>
+        <v>1.7</v>
       </c>
       <c r="H14" t="n">
-        <v>5.77</v>
+        <v>2.75</v>
       </c>
       <c r="I14" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.06</v>
+        <v>1.0677</v>
       </c>
       <c r="E15" t="n">
-        <v>53.91</v>
+        <v>54.26</v>
       </c>
       <c r="F15" t="n">
         <v>1514</v>
@@ -1036,11 +1036,11 @@
         <v>3.16</v>
       </c>
       <c r="I15" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1049,39 +1049,39 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1610612756</v>
+        <v>1610612755</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.0358</v>
+        <v>1.0085</v>
       </c>
       <c r="E16" t="n">
-        <v>52.9</v>
+        <v>51.73</v>
       </c>
       <c r="F16" t="n">
-        <v>1510.5</v>
+        <v>1472.2</v>
       </c>
       <c r="G16" t="n">
-        <v>1.64</v>
+        <v>0.57</v>
       </c>
       <c r="H16" t="n">
-        <v>3.47</v>
+        <v>0.53</v>
       </c>
       <c r="I16" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1090,39 +1090,39 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1610612755</v>
+        <v>1610612756</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.0077</v>
+        <v>1.0053</v>
       </c>
       <c r="E17" t="n">
-        <v>51.68</v>
+        <v>51.49</v>
       </c>
       <c r="F17" t="n">
-        <v>1472.2</v>
+        <v>1508.1</v>
       </c>
       <c r="G17" t="n">
-        <v>0.57</v>
+        <v>1.19</v>
       </c>
       <c r="H17" t="n">
-        <v>0.53</v>
+        <v>0.18</v>
       </c>
       <c r="I17" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9724</v>
+        <v>0.9744</v>
       </c>
       <c r="E18" t="n">
-        <v>49.97</v>
+        <v>50.02</v>
       </c>
       <c r="F18" t="n">
         <v>1533.6</v>
@@ -1159,11 +1159,11 @@
         <v>-6.55</v>
       </c>
       <c r="I18" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1185,26 +1185,26 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.899</v>
+        <v>0.909</v>
       </c>
       <c r="E19" t="n">
-        <v>46.35</v>
+        <v>46.9</v>
       </c>
       <c r="F19" t="n">
-        <v>1463</v>
+        <v>1467.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.16</v>
+        <v>-0.73</v>
       </c>
       <c r="H19" t="n">
-        <v>10.17</v>
+        <v>10.51</v>
       </c>
       <c r="I19" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1226,26 +1226,26 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.8827</v>
+        <v>0.8865</v>
       </c>
       <c r="E20" t="n">
-        <v>46.08</v>
+        <v>46.28</v>
       </c>
       <c r="F20" t="n">
-        <v>1477.5</v>
+        <v>1475</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.42</v>
+        <v>-0.52</v>
       </c>
       <c r="H20" t="n">
-        <v>-7.04</v>
+        <v>-6.38</v>
       </c>
       <c r="I20" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8803</v>
+        <v>0.8854</v>
       </c>
       <c r="E21" t="n">
-        <v>45.85</v>
+        <v>46.09</v>
       </c>
       <c r="F21" t="n">
         <v>1517.6</v>
@@ -1282,11 +1282,11 @@
         <v>-12.71</v>
       </c>
       <c r="I21" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1308,26 +1308,26 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.7429</v>
+        <v>0.7571</v>
       </c>
       <c r="E22" t="n">
-        <v>39.02</v>
+        <v>39.65</v>
       </c>
       <c r="F22" t="n">
-        <v>1380.2</v>
+        <v>1375.7</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.66</v>
+        <v>-4.56</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.14</v>
+        <v>-5.19</v>
       </c>
       <c r="I22" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.7284</v>
+        <v>0.7343</v>
       </c>
       <c r="E23" t="n">
-        <v>38.19</v>
+        <v>38.45</v>
       </c>
       <c r="F23" t="n">
         <v>1379</v>
@@ -1364,11 +1364,11 @@
         <v>-9.01</v>
       </c>
       <c r="I23" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1377,39 +1377,39 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1610612749</v>
+        <v>1610612754</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6552</v>
+        <v>0.6672</v>
       </c>
       <c r="E24" t="n">
-        <v>34.42</v>
+        <v>34.82</v>
       </c>
       <c r="F24" t="n">
-        <v>1392.8</v>
+        <v>1338.8</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.94</v>
+        <v>-7.13</v>
       </c>
       <c r="H24" t="n">
-        <v>-13.23</v>
+        <v>-3.16</v>
       </c>
       <c r="I24" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1418,39 +1418,39 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1610612754</v>
+        <v>1610612742</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6494</v>
+        <v>0.636</v>
       </c>
       <c r="E25" t="n">
-        <v>34</v>
+        <v>33.54</v>
       </c>
       <c r="F25" t="n">
-        <v>1338.8</v>
+        <v>1367.4</v>
       </c>
       <c r="G25" t="n">
-        <v>-7.13</v>
+        <v>-6.08</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.16</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1459,39 +1459,39 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1610612742</v>
+        <v>1610612749</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.6227</v>
       </c>
       <c r="E26" t="n">
-        <v>33.52</v>
+        <v>32.56</v>
       </c>
       <c r="F26" t="n">
-        <v>1367.4</v>
+        <v>1392.8</v>
       </c>
       <c r="G26" t="n">
-        <v>-6.08</v>
+        <v>-5.94</v>
       </c>
       <c r="H26" t="n">
-        <v>-9.220000000000001</v>
+        <v>-13.23</v>
       </c>
       <c r="I26" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.5967</v>
+        <v>0.5935</v>
       </c>
       <c r="E27" t="n">
-        <v>31.31</v>
+        <v>31</v>
       </c>
       <c r="F27" t="n">
         <v>1379.7</v>
@@ -1528,11 +1528,11 @@
         <v>-16.55</v>
       </c>
       <c r="I27" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.5604</v>
+        <v>0.581</v>
       </c>
       <c r="E28" t="n">
-        <v>28.73</v>
+        <v>29.84</v>
       </c>
       <c r="F28" t="n">
         <v>1307.1</v>
@@ -1569,11 +1569,11 @@
         <v>-9.15</v>
       </c>
       <c r="I28" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.5463</v>
+        <v>0.5475</v>
       </c>
       <c r="E29" t="n">
-        <v>28.07</v>
+        <v>28.05</v>
       </c>
       <c r="F29" t="n">
         <v>1310.8</v>
@@ -1610,11 +1610,11 @@
         <v>-8.6</v>
       </c>
       <c r="I29" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5178</v>
+        <v>0.5203</v>
       </c>
       <c r="E30" t="n">
-        <v>26.33</v>
+        <v>26.41</v>
       </c>
       <c r="F30" t="n">
         <v>1294</v>
@@ -1651,11 +1651,11 @@
         <v>-13.46</v>
       </c>
       <c r="I30" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.4989</v>
+        <v>0.4992</v>
       </c>
       <c r="E31" t="n">
-        <v>24.85</v>
+        <v>24.83</v>
       </c>
       <c r="F31" t="n">
         <v>1257.3</v>
@@ -1692,11 +1692,11 @@
         <v>-15.61</v>
       </c>
       <c r="I31" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="K31" t="n">

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.557</v>
+        <v>1.5596</v>
       </c>
       <c r="E2" t="n">
-        <v>73.13</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="F2" t="n">
         <v>1757.8</v>
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.5013</v>
+        <v>1.505</v>
       </c>
       <c r="E3" t="n">
-        <v>71.37</v>
+        <v>71.55</v>
       </c>
       <c r="F3" t="n">
         <v>1737.9</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.4162</v>
+        <v>1.4192</v>
       </c>
       <c r="E4" t="n">
-        <v>68.45</v>
+        <v>68.58</v>
       </c>
       <c r="F4" t="n">
         <v>1660.9</v>
@@ -611,10 +611,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.387</v>
+        <v>1.3911</v>
       </c>
       <c r="E5" t="n">
-        <v>67.05</v>
+        <v>67.23</v>
       </c>
       <c r="F5" t="n">
         <v>1637.4</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.3807</v>
+        <v>1.3841</v>
       </c>
       <c r="E6" t="n">
-        <v>66.77</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="F6" t="n">
         <v>1599</v>
@@ -680,32 +680,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612752</v>
+        <v>1610612747</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.3679</v>
+        <v>1.335</v>
       </c>
       <c r="E7" t="n">
-        <v>66.59999999999999</v>
+        <v>64.87</v>
       </c>
       <c r="F7" t="n">
-        <v>1647.3</v>
+        <v>1569.2</v>
       </c>
       <c r="G7" t="n">
-        <v>6.42</v>
+        <v>1.91</v>
       </c>
       <c r="H7" t="n">
-        <v>5.64</v>
+        <v>5.84</v>
       </c>
       <c r="I7" t="n">
         <v>164</v>
@@ -721,32 +721,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1610612747</v>
+        <v>1610612752</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.3293</v>
+        <v>1.3099</v>
       </c>
       <c r="E8" t="n">
-        <v>64.64</v>
+        <v>64.25</v>
       </c>
       <c r="F8" t="n">
-        <v>1569.2</v>
+        <v>1647.3</v>
       </c>
       <c r="G8" t="n">
-        <v>1.91</v>
+        <v>6.42</v>
       </c>
       <c r="H8" t="n">
-        <v>5.84</v>
+        <v>5.64</v>
       </c>
       <c r="I8" t="n">
         <v>164</v>
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.244</v>
+        <v>1.2434</v>
       </c>
       <c r="E9" t="n">
-        <v>60.75</v>
+        <v>60.78</v>
       </c>
       <c r="F9" t="n">
         <v>1681.5</v>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.2248</v>
+        <v>1.2287</v>
       </c>
       <c r="E10" t="n">
-        <v>60.78</v>
+        <v>60.95</v>
       </c>
       <c r="F10" t="n">
         <v>1579.1</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.2185</v>
+        <v>1.2224</v>
       </c>
       <c r="E11" t="n">
-        <v>60.54</v>
+        <v>60.7</v>
       </c>
       <c r="F11" t="n">
         <v>1584.8</v>
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.2049</v>
+        <v>1.2065</v>
       </c>
       <c r="E12" t="n">
-        <v>59.83</v>
+        <v>59.91</v>
       </c>
       <c r="F12" t="n">
         <v>1583</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.1477</v>
+        <v>1.1511</v>
       </c>
       <c r="E13" t="n">
-        <v>57.55</v>
+        <v>57.69</v>
       </c>
       <c r="F13" t="n">
         <v>1521.6</v>
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.1249</v>
+        <v>1.1268</v>
       </c>
       <c r="E14" t="n">
-        <v>56.64</v>
+        <v>56.72</v>
       </c>
       <c r="F14" t="n">
         <v>1555.4</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.0677</v>
+        <v>1.0707</v>
       </c>
       <c r="E15" t="n">
-        <v>54.26</v>
+        <v>54.36</v>
       </c>
       <c r="F15" t="n">
         <v>1514</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.0085</v>
+        <v>1.0138</v>
       </c>
       <c r="E16" t="n">
-        <v>51.73</v>
+        <v>51.91</v>
       </c>
       <c r="F16" t="n">
         <v>1472.2</v>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.0053</v>
+        <v>1.0077</v>
       </c>
       <c r="E17" t="n">
-        <v>51.49</v>
+        <v>51.59</v>
       </c>
       <c r="F17" t="n">
         <v>1508.1</v>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9744</v>
+        <v>0.9759</v>
       </c>
       <c r="E18" t="n">
-        <v>50.02</v>
+        <v>50.07</v>
       </c>
       <c r="F18" t="n">
         <v>1533.6</v>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.909</v>
+        <v>0.9082</v>
       </c>
       <c r="E19" t="n">
-        <v>46.9</v>
+        <v>46.88</v>
       </c>
       <c r="F19" t="n">
         <v>1467.5</v>
@@ -1213,32 +1213,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1610612744</v>
+        <v>1610612753</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.8865</v>
+        <v>0.8872</v>
       </c>
       <c r="E20" t="n">
-        <v>46.28</v>
+        <v>46.15</v>
       </c>
       <c r="F20" t="n">
-        <v>1475</v>
+        <v>1517.6</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.52</v>
+        <v>-0.9</v>
       </c>
       <c r="H20" t="n">
-        <v>-6.38</v>
+        <v>-12.71</v>
       </c>
       <c r="I20" t="n">
         <v>164</v>
@@ -1254,32 +1254,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1610612753</v>
+        <v>1610612744</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8854</v>
+        <v>0.8872</v>
       </c>
       <c r="E21" t="n">
-        <v>46.09</v>
+        <v>46.3</v>
       </c>
       <c r="F21" t="n">
-        <v>1517.6</v>
+        <v>1475</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9</v>
+        <v>-0.52</v>
       </c>
       <c r="H21" t="n">
-        <v>-12.71</v>
+        <v>-6.38</v>
       </c>
       <c r="I21" t="n">
         <v>164</v>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.7571</v>
+        <v>0.7588</v>
       </c>
       <c r="E22" t="n">
-        <v>39.65</v>
+        <v>39.69</v>
       </c>
       <c r="F22" t="n">
         <v>1375.7</v>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.7343</v>
+        <v>0.7363</v>
       </c>
       <c r="E23" t="n">
-        <v>38.45</v>
+        <v>38.49</v>
       </c>
       <c r="F23" t="n">
         <v>1379</v>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6672</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>34.82</v>
+        <v>34.84</v>
       </c>
       <c r="F24" t="n">
         <v>1338.8</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.636</v>
+        <v>0.6312</v>
       </c>
       <c r="E25" t="n">
-        <v>33.54</v>
+        <v>33.26</v>
       </c>
       <c r="F25" t="n">
         <v>1367.4</v>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6227</v>
+        <v>0.6232</v>
       </c>
       <c r="E26" t="n">
-        <v>32.56</v>
+        <v>32.53</v>
       </c>
       <c r="F26" t="n">
         <v>1392.8</v>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.5935</v>
+        <v>0.6025</v>
       </c>
       <c r="E27" t="n">
-        <v>31</v>
+        <v>31.54</v>
       </c>
       <c r="F27" t="n">
         <v>1379.7</v>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.581</v>
+        <v>0.5805</v>
       </c>
       <c r="E28" t="n">
-        <v>29.84</v>
+        <v>29.83</v>
       </c>
       <c r="F28" t="n">
         <v>1307.1</v>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.5475</v>
+        <v>0.547</v>
       </c>
       <c r="E29" t="n">
-        <v>28.05</v>
+        <v>27.98</v>
       </c>
       <c r="F29" t="n">
         <v>1310.8</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5203</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>26.41</v>
+        <v>26.4</v>
       </c>
       <c r="F30" t="n">
         <v>1294</v>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.4992</v>
+        <v>0.4984</v>
       </c>
       <c r="E31" t="n">
-        <v>24.83</v>
+        <v>24.76</v>
       </c>
       <c r="F31" t="n">
         <v>1257.3</v>

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5596</v>
+        <v>1.5764</v>
       </c>
       <c r="E2" t="n">
-        <v>73.26000000000001</v>
+        <v>73.87</v>
       </c>
       <c r="F2" t="n">
         <v>1757.8</v>
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.505</v>
+        <v>1.5181</v>
       </c>
       <c r="E3" t="n">
-        <v>71.55</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="F3" t="n">
         <v>1737.9</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.4192</v>
+        <v>1.4324</v>
       </c>
       <c r="E4" t="n">
-        <v>68.58</v>
+        <v>69.09</v>
       </c>
       <c r="F4" t="n">
         <v>1660.9</v>
@@ -611,10 +611,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.3911</v>
+        <v>1.4053</v>
       </c>
       <c r="E5" t="n">
-        <v>67.23</v>
+        <v>67.73</v>
       </c>
       <c r="F5" t="n">
         <v>1637.4</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.3841</v>
+        <v>1.3992</v>
       </c>
       <c r="E6" t="n">
-        <v>66.93000000000001</v>
+        <v>67.47</v>
       </c>
       <c r="F6" t="n">
         <v>1599</v>
@@ -680,32 +680,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612747</v>
+        <v>1610612752</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.335</v>
+        <v>1.3211</v>
       </c>
       <c r="E7" t="n">
-        <v>64.87</v>
+        <v>64.69</v>
       </c>
       <c r="F7" t="n">
-        <v>1569.2</v>
+        <v>1647.3</v>
       </c>
       <c r="G7" t="n">
-        <v>1.91</v>
+        <v>6.42</v>
       </c>
       <c r="H7" t="n">
-        <v>5.84</v>
+        <v>5.64</v>
       </c>
       <c r="I7" t="n">
         <v>164</v>
@@ -721,32 +721,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1610612752</v>
+        <v>1610612765</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.3099</v>
+        <v>1.2504</v>
       </c>
       <c r="E8" t="n">
-        <v>64.25</v>
+        <v>61.02</v>
       </c>
       <c r="F8" t="n">
-        <v>1647.3</v>
+        <v>1681.5</v>
       </c>
       <c r="G8" t="n">
-        <v>6.42</v>
+        <v>7.29</v>
       </c>
       <c r="H8" t="n">
-        <v>5.64</v>
+        <v>9.34</v>
       </c>
       <c r="I8" t="n">
         <v>164</v>
@@ -762,32 +762,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1610612765</v>
+        <v>1610612750</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.2434</v>
+        <v>1.2414</v>
       </c>
       <c r="E9" t="n">
-        <v>60.78</v>
+        <v>61.5</v>
       </c>
       <c r="F9" t="n">
-        <v>1681.5</v>
+        <v>1579.1</v>
       </c>
       <c r="G9" t="n">
-        <v>7.29</v>
+        <v>3.91</v>
       </c>
       <c r="H9" t="n">
-        <v>9.34</v>
+        <v>1.41</v>
       </c>
       <c r="I9" t="n">
         <v>164</v>
@@ -803,32 +803,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.2287</v>
+        <v>1.2323</v>
       </c>
       <c r="E10" t="n">
-        <v>60.95</v>
+        <v>61.13</v>
       </c>
       <c r="F10" t="n">
-        <v>1579.1</v>
+        <v>1584.8</v>
       </c>
       <c r="G10" t="n">
-        <v>3.91</v>
+        <v>4.5</v>
       </c>
       <c r="H10" t="n">
-        <v>1.41</v>
+        <v>6.9</v>
       </c>
       <c r="I10" t="n">
         <v>164</v>
@@ -844,32 +844,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1610612745</v>
+        <v>1610612766</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.2224</v>
+        <v>1.2136</v>
       </c>
       <c r="E11" t="n">
-        <v>60.7</v>
+        <v>60.22</v>
       </c>
       <c r="F11" t="n">
-        <v>1584.8</v>
+        <v>1583</v>
       </c>
       <c r="G11" t="n">
-        <v>4.5</v>
+        <v>3.87</v>
       </c>
       <c r="H11" t="n">
-        <v>6.9</v>
+        <v>12.06</v>
       </c>
       <c r="I11" t="n">
         <v>164</v>
@@ -885,32 +885,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1610612766</v>
+        <v>1610612737</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.2065</v>
+        <v>1.1628</v>
       </c>
       <c r="E12" t="n">
-        <v>59.91</v>
+        <v>58.15</v>
       </c>
       <c r="F12" t="n">
-        <v>1583</v>
+        <v>1521.6</v>
       </c>
       <c r="G12" t="n">
-        <v>3.87</v>
+        <v>2.41</v>
       </c>
       <c r="H12" t="n">
-        <v>12.06</v>
+        <v>11.61</v>
       </c>
       <c r="I12" t="n">
         <v>164</v>
@@ -926,32 +926,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1610612737</v>
+        <v>1610612747</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.1511</v>
+        <v>1.1355</v>
       </c>
       <c r="E13" t="n">
-        <v>57.69</v>
+        <v>57.14</v>
       </c>
       <c r="F13" t="n">
-        <v>1521.6</v>
+        <v>1569.2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.41</v>
+        <v>1.91</v>
       </c>
       <c r="H13" t="n">
-        <v>11.61</v>
+        <v>5.84</v>
       </c>
       <c r="I13" t="n">
         <v>164</v>
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.1268</v>
+        <v>1.1339</v>
       </c>
       <c r="E14" t="n">
-        <v>56.72</v>
+        <v>57.03</v>
       </c>
       <c r="F14" t="n">
         <v>1555.4</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.0707</v>
+        <v>1.0794</v>
       </c>
       <c r="E15" t="n">
-        <v>54.36</v>
+        <v>54.72</v>
       </c>
       <c r="F15" t="n">
         <v>1514</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.0138</v>
+        <v>1.023</v>
       </c>
       <c r="E16" t="n">
-        <v>51.91</v>
+        <v>52.28</v>
       </c>
       <c r="F16" t="n">
         <v>1472.2</v>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.0077</v>
+        <v>1.0135</v>
       </c>
       <c r="E17" t="n">
-        <v>51.59</v>
+        <v>51.86</v>
       </c>
       <c r="F17" t="n">
         <v>1508.1</v>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9759</v>
+        <v>0.9836</v>
       </c>
       <c r="E18" t="n">
-        <v>50.07</v>
+        <v>50.39</v>
       </c>
       <c r="F18" t="n">
         <v>1533.6</v>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.9082</v>
+        <v>0.9466</v>
       </c>
       <c r="E19" t="n">
-        <v>46.88</v>
+        <v>48.71</v>
       </c>
       <c r="F19" t="n">
         <v>1467.5</v>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.8872</v>
+        <v>0.8913</v>
       </c>
       <c r="E20" t="n">
-        <v>46.15</v>
+        <v>46.31</v>
       </c>
       <c r="F20" t="n">
         <v>1517.6</v>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8872</v>
+        <v>0.8894</v>
       </c>
       <c r="E21" t="n">
-        <v>46.3</v>
+        <v>46.39</v>
       </c>
       <c r="F21" t="n">
         <v>1475</v>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.7588</v>
+        <v>0.7602</v>
       </c>
       <c r="E22" t="n">
-        <v>39.69</v>
+        <v>39.75</v>
       </c>
       <c r="F22" t="n">
         <v>1375.7</v>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.7363</v>
+        <v>0.7377</v>
       </c>
       <c r="E23" t="n">
-        <v>38.49</v>
+        <v>38.56</v>
       </c>
       <c r="F23" t="n">
         <v>1379</v>
@@ -1393,7 +1393,7 @@
         <v>0.6677999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>34.84</v>
+        <v>34.82</v>
       </c>
       <c r="F24" t="n">
         <v>1338.8</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6312</v>
+        <v>0.6291</v>
       </c>
       <c r="E25" t="n">
-        <v>33.26</v>
+        <v>33.2</v>
       </c>
       <c r="F25" t="n">
         <v>1367.4</v>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6232</v>
+        <v>0.6194</v>
       </c>
       <c r="E26" t="n">
-        <v>32.53</v>
+        <v>32.3</v>
       </c>
       <c r="F26" t="n">
         <v>1392.8</v>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.6025</v>
+        <v>0.6</v>
       </c>
       <c r="E27" t="n">
-        <v>31.54</v>
+        <v>31.38</v>
       </c>
       <c r="F27" t="n">
         <v>1379.7</v>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.5805</v>
+        <v>0.5772</v>
       </c>
       <c r="E28" t="n">
-        <v>29.83</v>
+        <v>29.63</v>
       </c>
       <c r="F28" t="n">
         <v>1307.1</v>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.547</v>
+        <v>0.5447</v>
       </c>
       <c r="E29" t="n">
-        <v>27.98</v>
+        <v>27.8</v>
       </c>
       <c r="F29" t="n">
         <v>1310.8</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.5178</v>
       </c>
       <c r="E30" t="n">
-        <v>26.4</v>
+        <v>26.21</v>
       </c>
       <c r="F30" t="n">
         <v>1294</v>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.4984</v>
+        <v>0.4967</v>
       </c>
       <c r="E31" t="n">
-        <v>24.76</v>
+        <v>24.56</v>
       </c>
       <c r="F31" t="n">
         <v>1257.3</v>

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5764</v>
+        <v>1.5755</v>
       </c>
       <c r="E2" t="n">
-        <v>73.87</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>1757.8</v>
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.5181</v>
+        <v>1.517</v>
       </c>
       <c r="E3" t="n">
-        <v>72.06999999999999</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>1737.9</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.4324</v>
+        <v>1.431</v>
       </c>
       <c r="E4" t="n">
-        <v>69.09</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="F4" t="n">
         <v>1660.9</v>
@@ -611,10 +611,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.4053</v>
+        <v>1.404</v>
       </c>
       <c r="E5" t="n">
-        <v>67.73</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="F5" t="n">
         <v>1637.4</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.3992</v>
+        <v>1.398</v>
       </c>
       <c r="E6" t="n">
-        <v>67.47</v>
+        <v>67.42</v>
       </c>
       <c r="F6" t="n">
         <v>1599</v>
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.3211</v>
+        <v>1.3196</v>
       </c>
       <c r="E7" t="n">
-        <v>64.69</v>
+        <v>64.63</v>
       </c>
       <c r="F7" t="n">
         <v>1647.3</v>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.2504</v>
+        <v>1.2483</v>
       </c>
       <c r="E8" t="n">
-        <v>61.02</v>
+        <v>60.93</v>
       </c>
       <c r="F8" t="n">
         <v>1681.5</v>
@@ -762,32 +762,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1610612750</v>
+        <v>1610612766</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.2414</v>
+        <v>1.2409</v>
       </c>
       <c r="E9" t="n">
-        <v>61.5</v>
+        <v>61.36</v>
       </c>
       <c r="F9" t="n">
-        <v>1579.1</v>
+        <v>1583</v>
       </c>
       <c r="G9" t="n">
-        <v>3.91</v>
+        <v>3.87</v>
       </c>
       <c r="H9" t="n">
-        <v>1.41</v>
+        <v>12.06</v>
       </c>
       <c r="I9" t="n">
         <v>164</v>
@@ -803,32 +803,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.2323</v>
+        <v>1.2402</v>
       </c>
       <c r="E10" t="n">
-        <v>61.13</v>
+        <v>61.44</v>
       </c>
       <c r="F10" t="n">
-        <v>1584.8</v>
+        <v>1579.1</v>
       </c>
       <c r="G10" t="n">
-        <v>4.5</v>
+        <v>3.91</v>
       </c>
       <c r="H10" t="n">
-        <v>6.9</v>
+        <v>1.41</v>
       </c>
       <c r="I10" t="n">
         <v>164</v>
@@ -844,32 +844,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1610612766</v>
+        <v>1610612745</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.2136</v>
+        <v>1.231</v>
       </c>
       <c r="E11" t="n">
-        <v>60.22</v>
+        <v>61.06</v>
       </c>
       <c r="F11" t="n">
-        <v>1583</v>
+        <v>1584.8</v>
       </c>
       <c r="G11" t="n">
-        <v>3.87</v>
+        <v>4.5</v>
       </c>
       <c r="H11" t="n">
-        <v>12.06</v>
+        <v>6.9</v>
       </c>
       <c r="I11" t="n">
         <v>164</v>
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.1628</v>
+        <v>1.1617</v>
       </c>
       <c r="E12" t="n">
-        <v>58.15</v>
+        <v>58.12</v>
       </c>
       <c r="F12" t="n">
         <v>1521.6</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.1355</v>
+        <v>1.1335</v>
       </c>
       <c r="E13" t="n">
-        <v>57.14</v>
+        <v>57.05</v>
       </c>
       <c r="F13" t="n">
         <v>1569.2</v>
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.1339</v>
+        <v>1.1326</v>
       </c>
       <c r="E14" t="n">
-        <v>57.03</v>
+        <v>56.97</v>
       </c>
       <c r="F14" t="n">
         <v>1555.4</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.0794</v>
+        <v>1.0777</v>
       </c>
       <c r="E15" t="n">
-        <v>54.72</v>
+        <v>54.65</v>
       </c>
       <c r="F15" t="n">
         <v>1514</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.023</v>
+        <v>1.0213</v>
       </c>
       <c r="E16" t="n">
-        <v>52.28</v>
+        <v>52.21</v>
       </c>
       <c r="F16" t="n">
         <v>1472.2</v>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.0135</v>
+        <v>1.0108</v>
       </c>
       <c r="E17" t="n">
-        <v>51.86</v>
+        <v>51.73</v>
       </c>
       <c r="F17" t="n">
         <v>1508.1</v>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9836</v>
+        <v>0.9807</v>
       </c>
       <c r="E18" t="n">
-        <v>50.39</v>
+        <v>50.27</v>
       </c>
       <c r="F18" t="n">
         <v>1533.6</v>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.9466</v>
+        <v>0.9457</v>
       </c>
       <c r="E19" t="n">
-        <v>48.71</v>
+        <v>48.67</v>
       </c>
       <c r="F19" t="n">
         <v>1467.5</v>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.8913</v>
+        <v>0.89</v>
       </c>
       <c r="E20" t="n">
-        <v>46.31</v>
+        <v>46.25</v>
       </c>
       <c r="F20" t="n">
         <v>1517.6</v>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8894</v>
+        <v>0.8875999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>46.39</v>
+        <v>46.32</v>
       </c>
       <c r="F21" t="n">
         <v>1475</v>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.7602</v>
+        <v>0.7591</v>
       </c>
       <c r="E22" t="n">
-        <v>39.75</v>
+        <v>39.71</v>
       </c>
       <c r="F22" t="n">
         <v>1375.7</v>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.7377</v>
+        <v>0.7356</v>
       </c>
       <c r="E23" t="n">
-        <v>38.56</v>
+        <v>38.47</v>
       </c>
       <c r="F23" t="n">
         <v>1379</v>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>34.82</v>
+        <v>35.51</v>
       </c>
       <c r="F24" t="n">
         <v>1338.8</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6291</v>
+        <v>0.6281</v>
       </c>
       <c r="E25" t="n">
-        <v>33.2</v>
+        <v>33.16</v>
       </c>
       <c r="F25" t="n">
         <v>1367.4</v>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6194</v>
+        <v>0.6185</v>
       </c>
       <c r="E26" t="n">
-        <v>32.3</v>
+        <v>32.25</v>
       </c>
       <c r="F26" t="n">
         <v>1392.8</v>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.6</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>31.38</v>
+        <v>31.31</v>
       </c>
       <c r="F27" t="n">
         <v>1379.7</v>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.5772</v>
+        <v>0.5757</v>
       </c>
       <c r="E28" t="n">
-        <v>29.63</v>
+        <v>29.57</v>
       </c>
       <c r="F28" t="n">
         <v>1307.1</v>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.5447</v>
+        <v>0.5438</v>
       </c>
       <c r="E29" t="n">
-        <v>27.8</v>
+        <v>27.75</v>
       </c>
       <c r="F29" t="n">
         <v>1310.8</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5178</v>
+        <v>0.5163</v>
       </c>
       <c r="E30" t="n">
-        <v>26.21</v>
+        <v>26.14</v>
       </c>
       <c r="F30" t="n">
         <v>1294</v>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.4967</v>
+        <v>0.4956</v>
       </c>
       <c r="E31" t="n">
-        <v>24.56</v>
+        <v>24.5</v>
       </c>
       <c r="F31" t="n">
         <v>1257.3</v>

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5755</v>
+        <v>1.5751</v>
       </c>
       <c r="E2" t="n">
         <v>73.81999999999999</v>
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.517</v>
+        <v>1.5165</v>
       </c>
       <c r="E3" t="n">
-        <v>72.01000000000001</v>
+        <v>72</v>
       </c>
       <c r="F3" t="n">
         <v>1737.9</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.431</v>
+        <v>1.4308</v>
       </c>
       <c r="E4" t="n">
-        <v>69.04000000000001</v>
+        <v>69.03</v>
       </c>
       <c r="F4" t="n">
         <v>1660.9</v>
@@ -611,10 +611,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.404</v>
+        <v>1.4037</v>
       </c>
       <c r="E5" t="n">
-        <v>67.68000000000001</v>
+        <v>67.67</v>
       </c>
       <c r="F5" t="n">
         <v>1637.4</v>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.398</v>
+        <v>1.3981</v>
       </c>
       <c r="E6" t="n">
         <v>67.42</v>
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.3196</v>
+        <v>1.3193</v>
       </c>
       <c r="E7" t="n">
-        <v>64.63</v>
+        <v>64.62</v>
       </c>
       <c r="F7" t="n">
         <v>1647.3</v>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.2483</v>
+        <v>1.2477</v>
       </c>
       <c r="E8" t="n">
-        <v>60.93</v>
+        <v>60.9</v>
       </c>
       <c r="F8" t="n">
         <v>1681.5</v>
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.2409</v>
+        <v>1.2402</v>
       </c>
       <c r="E9" t="n">
-        <v>61.36</v>
+        <v>61.33</v>
       </c>
       <c r="F9" t="n">
         <v>1583</v>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.2402</v>
+        <v>1.2399</v>
       </c>
       <c r="E10" t="n">
-        <v>61.44</v>
+        <v>61.43</v>
       </c>
       <c r="F10" t="n">
         <v>1579.1</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.231</v>
+        <v>1.2305</v>
       </c>
       <c r="E11" t="n">
-        <v>61.06</v>
+        <v>61.05</v>
       </c>
       <c r="F11" t="n">
         <v>1584.8</v>
@@ -901,7 +901,7 @@
         <v>1.1617</v>
       </c>
       <c r="E12" t="n">
-        <v>58.12</v>
+        <v>58.11</v>
       </c>
       <c r="F12" t="n">
         <v>1521.6</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.1335</v>
+        <v>1.1327</v>
       </c>
       <c r="E13" t="n">
-        <v>57.05</v>
+        <v>57.03</v>
       </c>
       <c r="F13" t="n">
         <v>1569.2</v>
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.1326</v>
+        <v>1.1322</v>
       </c>
       <c r="E14" t="n">
-        <v>56.97</v>
+        <v>56.94</v>
       </c>
       <c r="F14" t="n">
         <v>1555.4</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.0777</v>
+        <v>1.0772</v>
       </c>
       <c r="E15" t="n">
-        <v>54.65</v>
+        <v>54.62</v>
       </c>
       <c r="F15" t="n">
         <v>1514</v>
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.0213</v>
+        <v>1.0212</v>
       </c>
       <c r="E16" t="n">
         <v>52.21</v>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.0108</v>
+        <v>1.0103</v>
       </c>
       <c r="E17" t="n">
-        <v>51.73</v>
+        <v>51.71</v>
       </c>
       <c r="F17" t="n">
         <v>1508.1</v>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9807</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>50.27</v>
+        <v>50.24</v>
       </c>
       <c r="F18" t="n">
         <v>1533.6</v>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.9457</v>
+        <v>0.9447</v>
       </c>
       <c r="E19" t="n">
-        <v>48.67</v>
+        <v>48.62</v>
       </c>
       <c r="F19" t="n">
         <v>1467.5</v>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.89</v>
+        <v>0.8899</v>
       </c>
       <c r="E20" t="n">
-        <v>46.25</v>
+        <v>46.24</v>
       </c>
       <c r="F20" t="n">
         <v>1517.6</v>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.8873</v>
       </c>
       <c r="E21" t="n">
-        <v>46.32</v>
+        <v>46.29</v>
       </c>
       <c r="F21" t="n">
         <v>1475</v>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.7591</v>
+        <v>0.7587</v>
       </c>
       <c r="E22" t="n">
-        <v>39.71</v>
+        <v>39.68</v>
       </c>
       <c r="F22" t="n">
         <v>1375.7</v>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.7356</v>
+        <v>0.7346</v>
       </c>
       <c r="E23" t="n">
-        <v>38.47</v>
+        <v>38.4</v>
       </c>
       <c r="F23" t="n">
         <v>1379</v>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6958</v>
       </c>
       <c r="E24" t="n">
-        <v>35.51</v>
+        <v>36.24</v>
       </c>
       <c r="F24" t="n">
         <v>1338.8</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6281</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>33.16</v>
+        <v>33.13</v>
       </c>
       <c r="F25" t="n">
         <v>1367.4</v>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6185</v>
+        <v>0.6181</v>
       </c>
       <c r="E26" t="n">
-        <v>32.25</v>
+        <v>32.21</v>
       </c>
       <c r="F26" t="n">
         <v>1392.8</v>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.5978</v>
       </c>
       <c r="E27" t="n">
-        <v>31.31</v>
+        <v>31.27</v>
       </c>
       <c r="F27" t="n">
         <v>1379.7</v>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.5757</v>
+        <v>0.5752</v>
       </c>
       <c r="E28" t="n">
-        <v>29.57</v>
+        <v>29.53</v>
       </c>
       <c r="F28" t="n">
         <v>1307.1</v>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.5438</v>
+        <v>0.543</v>
       </c>
       <c r="E29" t="n">
-        <v>27.75</v>
+        <v>27.71</v>
       </c>
       <c r="F29" t="n">
         <v>1310.8</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5163</v>
+        <v>0.5151</v>
       </c>
       <c r="E30" t="n">
-        <v>26.14</v>
+        <v>26.08</v>
       </c>
       <c r="F30" t="n">
         <v>1294</v>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.4956</v>
+        <v>0.4951</v>
       </c>
       <c r="E31" t="n">
-        <v>24.5</v>
+        <v>24.47</v>
       </c>
       <c r="F31" t="n">
         <v>1257.3</v>

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5751</v>
+        <v>1.5791</v>
       </c>
       <c r="E2" t="n">
-        <v>73.81999999999999</v>
+        <v>73.81</v>
       </c>
       <c r="F2" t="n">
         <v>1757.8</v>
@@ -503,11 +503,11 @@
         <v>15.81</v>
       </c>
       <c r="I2" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -529,26 +529,26 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.5165</v>
+        <v>1.5128</v>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>71.7</v>
       </c>
       <c r="F3" t="n">
-        <v>1737.9</v>
+        <v>1742.5</v>
       </c>
       <c r="G3" t="n">
-        <v>8.91</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>17.4</v>
+        <v>15.43</v>
       </c>
       <c r="I3" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -570,26 +570,26 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.4308</v>
+        <v>1.4732</v>
       </c>
       <c r="E4" t="n">
-        <v>69.03</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1660.9</v>
+        <v>1665.9</v>
       </c>
       <c r="G4" t="n">
-        <v>7.21</v>
+        <v>7.7</v>
       </c>
       <c r="H4" t="n">
-        <v>6.25</v>
+        <v>9.76</v>
       </c>
       <c r="I4" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -598,39 +598,39 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1610612739</v>
+        <v>1610612752</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.4037</v>
+        <v>1.3984</v>
       </c>
       <c r="E5" t="n">
-        <v>67.67</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>1637.4</v>
+        <v>1648.9</v>
       </c>
       <c r="G5" t="n">
-        <v>4.26</v>
+        <v>7.31</v>
       </c>
       <c r="H5" t="n">
-        <v>4.65</v>
+        <v>8.16</v>
       </c>
       <c r="I5" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -652,26 +652,26 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.3981</v>
+        <v>1.3938</v>
       </c>
       <c r="E6" t="n">
-        <v>67.42</v>
+        <v>67.23</v>
       </c>
       <c r="F6" t="n">
-        <v>1599</v>
+        <v>1600.4</v>
       </c>
       <c r="G6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H6" t="n">
-        <v>8.300000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="I6" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -680,39 +680,39 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612752</v>
+        <v>1610612739</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.3193</v>
+        <v>1.3081</v>
       </c>
       <c r="E7" t="n">
-        <v>64.62</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>1647.3</v>
+        <v>1637.4</v>
       </c>
       <c r="G7" t="n">
-        <v>6.42</v>
+        <v>4.26</v>
       </c>
       <c r="H7" t="n">
-        <v>5.64</v>
+        <v>4.65</v>
       </c>
       <c r="I7" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -734,26 +734,26 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.2477</v>
+        <v>1.2798</v>
       </c>
       <c r="E8" t="n">
-        <v>60.9</v>
+        <v>62.14</v>
       </c>
       <c r="F8" t="n">
-        <v>1681.5</v>
+        <v>1683.5</v>
       </c>
       <c r="G8" t="n">
-        <v>7.29</v>
+        <v>7.66</v>
       </c>
       <c r="H8" t="n">
-        <v>9.34</v>
+        <v>12.91</v>
       </c>
       <c r="I8" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -775,26 +775,26 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.2402</v>
+        <v>1.2582</v>
       </c>
       <c r="E9" t="n">
-        <v>61.33</v>
+        <v>61.99</v>
       </c>
       <c r="F9" t="n">
-        <v>1583</v>
+        <v>1586.5</v>
       </c>
       <c r="G9" t="n">
-        <v>3.87</v>
+        <v>4.02</v>
       </c>
       <c r="H9" t="n">
-        <v>12.06</v>
+        <v>13.45</v>
       </c>
       <c r="I9" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -803,39 +803,39 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.2399</v>
+        <v>1.2567</v>
       </c>
       <c r="E10" t="n">
-        <v>61.43</v>
+        <v>62.15</v>
       </c>
       <c r="F10" t="n">
-        <v>1579.1</v>
+        <v>1585.8</v>
       </c>
       <c r="G10" t="n">
-        <v>3.91</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>1.41</v>
+        <v>9.69</v>
       </c>
       <c r="I10" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -844,39 +844,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.2305</v>
+        <v>1.2262</v>
       </c>
       <c r="E11" t="n">
-        <v>61.05</v>
+        <v>60.66</v>
       </c>
       <c r="F11" t="n">
-        <v>1584.8</v>
+        <v>1577</v>
       </c>
       <c r="G11" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="H11" t="n">
-        <v>6.9</v>
+        <v>2.06</v>
       </c>
       <c r="I11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -898,26 +898,26 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.1617</v>
+        <v>1.1879</v>
       </c>
       <c r="E12" t="n">
-        <v>58.11</v>
+        <v>59.2</v>
       </c>
       <c r="F12" t="n">
-        <v>1521.6</v>
+        <v>1529.8</v>
       </c>
       <c r="G12" t="n">
-        <v>2.41</v>
+        <v>2.84</v>
       </c>
       <c r="H12" t="n">
-        <v>11.61</v>
+        <v>12.4</v>
       </c>
       <c r="I12" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -926,39 +926,39 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1610612747</v>
+        <v>1610612746</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.1327</v>
+        <v>1.1341</v>
       </c>
       <c r="E13" t="n">
-        <v>57.03</v>
+        <v>57.1</v>
       </c>
       <c r="F13" t="n">
-        <v>1569.2</v>
+        <v>1555.4</v>
       </c>
       <c r="G13" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="H13" t="n">
-        <v>5.84</v>
+        <v>2.75</v>
       </c>
       <c r="I13" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -967,39 +967,39 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1610612746</v>
+        <v>1610612761</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.1322</v>
+        <v>1.0943</v>
       </c>
       <c r="E14" t="n">
-        <v>56.94</v>
+        <v>55.56</v>
       </c>
       <c r="F14" t="n">
-        <v>1555.4</v>
+        <v>1510.5</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7</v>
+        <v>2.49</v>
       </c>
       <c r="H14" t="n">
-        <v>2.75</v>
+        <v>6.06</v>
       </c>
       <c r="I14" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1008,39 +1008,39 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.0772</v>
+        <v>1.0287</v>
       </c>
       <c r="E15" t="n">
-        <v>54.62</v>
+        <v>52.63</v>
       </c>
       <c r="F15" t="n">
-        <v>1514</v>
+        <v>1478.3</v>
       </c>
       <c r="G15" t="n">
-        <v>1.53</v>
+        <v>-0.13</v>
       </c>
       <c r="H15" t="n">
-        <v>3.16</v>
+        <v>0.66</v>
       </c>
       <c r="I15" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1049,39 +1049,39 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1610612755</v>
+        <v>1610612747</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.0212</v>
+        <v>1.0233</v>
       </c>
       <c r="E16" t="n">
-        <v>52.21</v>
+        <v>52.27</v>
       </c>
       <c r="F16" t="n">
-        <v>1472.2</v>
+        <v>1569.2</v>
       </c>
       <c r="G16" t="n">
-        <v>0.57</v>
+        <v>1.91</v>
       </c>
       <c r="H16" t="n">
-        <v>0.53</v>
+        <v>5.84</v>
       </c>
       <c r="I16" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.0103</v>
+        <v>1.0138</v>
       </c>
       <c r="E17" t="n">
-        <v>51.71</v>
+        <v>52.08</v>
       </c>
       <c r="F17" t="n">
         <v>1508.1</v>
@@ -1118,11 +1118,11 @@
         <v>0.18</v>
       </c>
       <c r="I17" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1144,26 +1144,26 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.9949</v>
       </c>
       <c r="E18" t="n">
-        <v>50.24</v>
+        <v>50.89</v>
       </c>
       <c r="F18" t="n">
-        <v>1533.6</v>
+        <v>1528.7</v>
       </c>
       <c r="G18" t="n">
-        <v>1.73</v>
+        <v>2.21</v>
       </c>
       <c r="H18" t="n">
-        <v>-6.55</v>
+        <v>-6.17</v>
       </c>
       <c r="I18" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.9447</v>
+        <v>0.9488</v>
       </c>
       <c r="E19" t="n">
-        <v>48.62</v>
+        <v>48.83</v>
       </c>
       <c r="F19" t="n">
         <v>1467.5</v>
@@ -1200,11 +1200,11 @@
         <v>10.51</v>
       </c>
       <c r="I19" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1213,39 +1213,39 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1610612753</v>
+        <v>1610612744</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.8899</v>
+        <v>0.8902</v>
       </c>
       <c r="E20" t="n">
-        <v>46.24</v>
+        <v>46.56</v>
       </c>
       <c r="F20" t="n">
-        <v>1517.6</v>
+        <v>1475</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9</v>
+        <v>-0.52</v>
       </c>
       <c r="H20" t="n">
-        <v>-12.71</v>
+        <v>-6.38</v>
       </c>
       <c r="I20" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1254,39 +1254,39 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1610612744</v>
+        <v>1610612753</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8873</v>
+        <v>0.8888</v>
       </c>
       <c r="E21" t="n">
-        <v>46.29</v>
+        <v>46.39</v>
       </c>
       <c r="F21" t="n">
-        <v>1475</v>
+        <v>1509.4</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.52</v>
+        <v>-0.18</v>
       </c>
       <c r="H21" t="n">
-        <v>-6.38</v>
+        <v>-11.16</v>
       </c>
       <c r="I21" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1308,26 +1308,26 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.7587</v>
+        <v>0.7783</v>
       </c>
       <c r="E22" t="n">
-        <v>39.68</v>
+        <v>40.65</v>
       </c>
       <c r="F22" t="n">
-        <v>1375.7</v>
+        <v>1374.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.56</v>
+        <v>-4.34</v>
       </c>
       <c r="H22" t="n">
-        <v>-5.19</v>
+        <v>-6.06</v>
       </c>
       <c r="I22" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1349,26 +1349,26 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.7346</v>
+        <v>0.7066</v>
       </c>
       <c r="E23" t="n">
-        <v>38.4</v>
+        <v>37.08</v>
       </c>
       <c r="F23" t="n">
-        <v>1379</v>
+        <v>1375.1</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.34</v>
+        <v>-5.39</v>
       </c>
       <c r="H23" t="n">
-        <v>-9.01</v>
+        <v>-11.73</v>
       </c>
       <c r="I23" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1377,39 +1377,39 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1610612754</v>
+        <v>1610612749</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6958</v>
+        <v>0.6494</v>
       </c>
       <c r="E24" t="n">
-        <v>36.24</v>
+        <v>33.99</v>
       </c>
       <c r="F24" t="n">
-        <v>1338.8</v>
+        <v>1391.8</v>
       </c>
       <c r="G24" t="n">
-        <v>-7.13</v>
+        <v>-6.45</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.16</v>
+        <v>-14.41</v>
       </c>
       <c r="I24" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1418,39 +1418,39 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1610612742</v>
+        <v>1610612754</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.6368</v>
       </c>
       <c r="E25" t="n">
-        <v>33.13</v>
+        <v>33.26</v>
       </c>
       <c r="F25" t="n">
-        <v>1367.4</v>
+        <v>1342.6</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.08</v>
+        <v>-7.78</v>
       </c>
       <c r="H25" t="n">
-        <v>-9.220000000000001</v>
+        <v>-3.92</v>
       </c>
       <c r="I25" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1459,39 +1459,39 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1610612749</v>
+        <v>1610612742</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6181</v>
+        <v>0.6302</v>
       </c>
       <c r="E26" t="n">
-        <v>32.21</v>
+        <v>33.34</v>
       </c>
       <c r="F26" t="n">
-        <v>1392.8</v>
+        <v>1364.5</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.94</v>
+        <v>-5.96</v>
       </c>
       <c r="H26" t="n">
-        <v>-13.23</v>
+        <v>-11.05</v>
       </c>
       <c r="I26" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1513,26 +1513,26 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.5978</v>
+        <v>0.5962</v>
       </c>
       <c r="E27" t="n">
-        <v>31.27</v>
+        <v>31.28</v>
       </c>
       <c r="F27" t="n">
-        <v>1379.7</v>
+        <v>1378.1</v>
       </c>
       <c r="G27" t="n">
-        <v>-5.27</v>
+        <v>-6.03</v>
       </c>
       <c r="H27" t="n">
-        <v>-16.55</v>
+        <v>-18.27</v>
       </c>
       <c r="I27" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -1554,26 +1554,26 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.5752</v>
+        <v>0.5719</v>
       </c>
       <c r="E28" t="n">
-        <v>29.53</v>
+        <v>29.44</v>
       </c>
       <c r="F28" t="n">
-        <v>1307.1</v>
+        <v>1305.7</v>
       </c>
       <c r="G28" t="n">
-        <v>-7.98</v>
+        <v>-8.48</v>
       </c>
       <c r="H28" t="n">
-        <v>-9.15</v>
+        <v>-10.73</v>
       </c>
       <c r="I28" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -1595,26 +1595,26 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.543</v>
+        <v>0.5495</v>
       </c>
       <c r="E29" t="n">
-        <v>27.71</v>
+        <v>28.33</v>
       </c>
       <c r="F29" t="n">
-        <v>1310.8</v>
+        <v>1314.2</v>
       </c>
       <c r="G29" t="n">
-        <v>-9.17</v>
+        <v>-9.07</v>
       </c>
       <c r="H29" t="n">
-        <v>-8.6</v>
+        <v>-8.17</v>
       </c>
       <c r="I29" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -1623,39 +1623,39 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5151</v>
+        <v>0.5038</v>
       </c>
       <c r="E30" t="n">
-        <v>26.08</v>
+        <v>24.95</v>
       </c>
       <c r="F30" t="n">
-        <v>1294</v>
+        <v>1255.3</v>
       </c>
       <c r="G30" t="n">
-        <v>-10.5</v>
+        <v>-11.43</v>
       </c>
       <c r="H30" t="n">
-        <v>-13.46</v>
+        <v>-15.49</v>
       </c>
       <c r="I30" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -1664,39 +1664,39 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.4951</v>
+        <v>0.4861</v>
       </c>
       <c r="E31" t="n">
-        <v>24.47</v>
+        <v>24.2</v>
       </c>
       <c r="F31" t="n">
-        <v>1257.3</v>
+        <v>1291.5</v>
       </c>
       <c r="G31" t="n">
-        <v>-11.66</v>
+        <v>-10.73</v>
       </c>
       <c r="H31" t="n">
-        <v>-15.61</v>
+        <v>-15.17</v>
       </c>
       <c r="I31" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="K31" t="n">

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -61,6 +61,9 @@
     <t>New York Knicks</t>
   </si>
   <si>
+    <t>Denver Nuggets</t>
+  </si>
+  <si>
     <t>Cleveland Cavaliers</t>
   </si>
   <si>
@@ -76,18 +79,15 @@
     <t>Atlanta Hawks</t>
   </si>
   <si>
-    <t>Denver Nuggets</t>
-  </si>
-  <si>
     <t>LA Clippers</t>
   </si>
   <si>
+    <t>Toronto Raptors</t>
+  </si>
+  <si>
     <t>Minnesota Timberwolves</t>
   </si>
   <si>
-    <t>Toronto Raptors</t>
-  </si>
-  <si>
     <t>Phoenix Suns</t>
   </si>
   <si>
@@ -109,12 +109,12 @@
     <t>Orlando Magic</t>
   </si>
   <si>
+    <t>Dallas Mavericks</t>
+  </si>
+  <si>
     <t>New Orleans Pelicans</t>
   </si>
   <si>
-    <t>Dallas Mavericks</t>
-  </si>
-  <si>
     <t>Indiana Pacers</t>
   </si>
   <si>
@@ -151,6 +151,9 @@
     <t>NYK</t>
   </si>
   <si>
+    <t>DEN</t>
+  </si>
+  <si>
     <t>CLE</t>
   </si>
   <si>
@@ -166,18 +169,15 @@
     <t>ATL</t>
   </si>
   <si>
-    <t>DEN</t>
-  </si>
-  <si>
     <t>LAC</t>
   </si>
   <si>
+    <t>TOR</t>
+  </si>
+  <si>
     <t>MIN</t>
   </si>
   <si>
-    <t>TOR</t>
-  </si>
-  <si>
     <t>PHX</t>
   </si>
   <si>
@@ -199,10 +199,10 @@
     <t>ORL</t>
   </si>
   <si>
+    <t>DAL</t>
+  </si>
+  <si>
     <t>NOP</t>
-  </si>
-  <si>
-    <t>DAL</t>
   </si>
   <si>
     <t>IND</t>
@@ -636,10 +636,10 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>1.5887</v>
+        <v>1.5785</v>
       </c>
       <c r="E2">
-        <v>74.14</v>
+        <v>73.7</v>
       </c>
       <c r="F2">
         <v>1762.4</v>
@@ -671,10 +671,10 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>1.5231</v>
+        <v>1.5091</v>
       </c>
       <c r="E3">
-        <v>72.14</v>
+        <v>71.56</v>
       </c>
       <c r="F3">
         <v>1737.7</v>
@@ -706,10 +706,10 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>1.5088</v>
+        <v>1.4946</v>
       </c>
       <c r="E4">
-        <v>71.95999999999999</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="F4">
         <v>1669.3</v>
@@ -741,10 +741,10 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>1.4065</v>
+        <v>1.3912</v>
       </c>
       <c r="E5">
-        <v>68.09999999999999</v>
+        <v>67.48</v>
       </c>
       <c r="F5">
         <v>1651</v>
@@ -767,7 +767,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6">
-        <v>1610612739</v>
+        <v>1610612743</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
@@ -776,19 +776,19 @@
         <v>45</v>
       </c>
       <c r="D6">
-        <v>1.404</v>
+        <v>1.388</v>
       </c>
       <c r="E6">
-        <v>67.84999999999999</v>
+        <v>67.08</v>
       </c>
       <c r="F6">
-        <v>1640.2</v>
+        <v>1605.2</v>
       </c>
       <c r="G6">
-        <v>4.42</v>
+        <v>4.67</v>
       </c>
       <c r="H6">
-        <v>4.44</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="I6">
         <v>168</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7">
-        <v>1610612766</v>
+        <v>1610612739</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
@@ -811,19 +811,19 @@
         <v>46</v>
       </c>
       <c r="D7">
-        <v>1.2909</v>
+        <v>1.3876</v>
       </c>
       <c r="E7">
-        <v>63.23</v>
+        <v>67.2</v>
       </c>
       <c r="F7">
-        <v>1587.9</v>
+        <v>1640.2</v>
       </c>
       <c r="G7">
-        <v>4.05</v>
+        <v>4.42</v>
       </c>
       <c r="H7">
-        <v>15.96</v>
+        <v>4.44</v>
       </c>
       <c r="I7">
         <v>168</v>
@@ -837,7 +837,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8">
-        <v>1610612765</v>
+        <v>1610612766</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -846,19 +846,19 @@
         <v>47</v>
       </c>
       <c r="D8">
-        <v>1.2812</v>
+        <v>1.2817</v>
       </c>
       <c r="E8">
-        <v>62.15</v>
+        <v>62.84</v>
       </c>
       <c r="F8">
-        <v>1687.7</v>
+        <v>1587.9</v>
       </c>
       <c r="G8">
-        <v>6.87</v>
+        <v>4.05</v>
       </c>
       <c r="H8">
-        <v>10.07</v>
+        <v>15.96</v>
       </c>
       <c r="I8">
         <v>168</v>
@@ -872,7 +872,7 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9">
-        <v>1610612745</v>
+        <v>1610612765</v>
       </c>
       <c r="B9" t="s">
         <v>18</v>
@@ -881,19 +881,19 @@
         <v>48</v>
       </c>
       <c r="D9">
-        <v>1.2705</v>
+        <v>1.2718</v>
       </c>
       <c r="E9">
-        <v>62.72</v>
+        <v>61.8</v>
       </c>
       <c r="F9">
-        <v>1587.3</v>
+        <v>1687.7</v>
       </c>
       <c r="G9">
-        <v>4.75</v>
+        <v>6.87</v>
       </c>
       <c r="H9">
-        <v>10.72</v>
+        <v>10.07</v>
       </c>
       <c r="I9">
         <v>168</v>
@@ -907,7 +907,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10">
-        <v>1610612737</v>
+        <v>1610612745</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
@@ -916,19 +916,19 @@
         <v>49</v>
       </c>
       <c r="D10">
-        <v>1.1907</v>
+        <v>1.2572</v>
       </c>
       <c r="E10">
-        <v>59.46</v>
+        <v>62.18</v>
       </c>
       <c r="F10">
-        <v>1532.7</v>
+        <v>1587.3</v>
       </c>
       <c r="G10">
-        <v>2.19</v>
+        <v>4.75</v>
       </c>
       <c r="H10">
-        <v>10.02</v>
+        <v>10.72</v>
       </c>
       <c r="I10">
         <v>168</v>
@@ -942,7 +942,7 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11">
-        <v>1610612743</v>
+        <v>1610612737</v>
       </c>
       <c r="B11" t="s">
         <v>20</v>
@@ -951,19 +951,19 @@
         <v>50</v>
       </c>
       <c r="D11">
-        <v>1.1695</v>
+        <v>1.1745</v>
       </c>
       <c r="E11">
-        <v>58.46</v>
+        <v>58.77</v>
       </c>
       <c r="F11">
-        <v>1605.2</v>
+        <v>1532.7</v>
       </c>
       <c r="G11">
-        <v>4.67</v>
+        <v>2.19</v>
       </c>
       <c r="H11">
-        <v>8.619999999999999</v>
+        <v>10.02</v>
       </c>
       <c r="I11">
         <v>168</v>
@@ -986,10 +986,10 @@
         <v>51</v>
       </c>
       <c r="D12">
-        <v>1.1589</v>
+        <v>1.1468</v>
       </c>
       <c r="E12">
-        <v>58.21</v>
+        <v>57.76</v>
       </c>
       <c r="F12">
         <v>1550.8</v>
@@ -1012,7 +1012,7 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13">
-        <v>1610612750</v>
+        <v>1610612761</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
@@ -1021,19 +1021,19 @@
         <v>52</v>
       </c>
       <c r="D13">
-        <v>1.109</v>
+        <v>1.1074</v>
       </c>
       <c r="E13">
-        <v>55.93</v>
+        <v>56.1</v>
       </c>
       <c r="F13">
-        <v>1572.9</v>
+        <v>1515.2</v>
       </c>
       <c r="G13">
-        <v>3.37</v>
+        <v>1.54</v>
       </c>
       <c r="H13">
-        <v>-0.41</v>
+        <v>2.78</v>
       </c>
       <c r="I13">
         <v>168</v>
@@ -1047,7 +1047,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14">
-        <v>1610612761</v>
+        <v>1610612750</v>
       </c>
       <c r="B14" t="s">
         <v>23</v>
@@ -1056,19 +1056,19 @@
         <v>53</v>
       </c>
       <c r="D14">
-        <v>1.0965</v>
+        <v>1.0968</v>
       </c>
       <c r="E14">
-        <v>55.66</v>
+        <v>55.41</v>
       </c>
       <c r="F14">
-        <v>1515.2</v>
+        <v>1572.9</v>
       </c>
       <c r="G14">
-        <v>1.54</v>
+        <v>3.37</v>
       </c>
       <c r="H14">
-        <v>2.78</v>
+        <v>-0.41</v>
       </c>
       <c r="I14">
         <v>168</v>
@@ -1091,10 +1091,10 @@
         <v>54</v>
       </c>
       <c r="D15">
-        <v>1.0393</v>
+        <v>1.0281</v>
       </c>
       <c r="E15">
-        <v>53.23</v>
+        <v>52.71</v>
       </c>
       <c r="F15">
         <v>1504.6</v>
@@ -1126,10 +1126,10 @@
         <v>55</v>
       </c>
       <c r="D16">
-        <v>1.0331</v>
+        <v>1.0195</v>
       </c>
       <c r="E16">
-        <v>52.63</v>
+        <v>52.09</v>
       </c>
       <c r="F16">
         <v>1528.7</v>
@@ -1161,10 +1161,10 @@
         <v>56</v>
       </c>
       <c r="D17">
-        <v>1.0224</v>
+        <v>1.0052</v>
       </c>
       <c r="E17">
-        <v>52.27</v>
+        <v>51.61</v>
       </c>
       <c r="F17">
         <v>1474.2</v>
@@ -1196,10 +1196,10 @@
         <v>57</v>
       </c>
       <c r="D18">
-        <v>0.9722</v>
+        <v>0.9647</v>
       </c>
       <c r="E18">
-        <v>49.91</v>
+        <v>49.58</v>
       </c>
       <c r="F18">
         <v>1469.1</v>
@@ -1231,10 +1231,10 @@
         <v>58</v>
       </c>
       <c r="D19">
-        <v>0.9686</v>
+        <v>0.9548</v>
       </c>
       <c r="E19">
-        <v>50.05</v>
+        <v>49.51</v>
       </c>
       <c r="F19">
         <v>1472.7</v>
@@ -1266,10 +1266,10 @@
         <v>59</v>
       </c>
       <c r="D20">
-        <v>0.9543</v>
+        <v>0.9513</v>
       </c>
       <c r="E20">
-        <v>48.87</v>
+        <v>48.7</v>
       </c>
       <c r="F20">
         <v>1564.6</v>
@@ -1301,10 +1301,10 @@
         <v>60</v>
       </c>
       <c r="D21">
-        <v>0.9443</v>
+        <v>0.9357</v>
       </c>
       <c r="E21">
-        <v>48.85</v>
+        <v>48.54</v>
       </c>
       <c r="F21">
         <v>1513.1</v>
@@ -1327,7 +1327,7 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
-        <v>1610612740</v>
+        <v>1610612742</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
@@ -1336,19 +1336,19 @@
         <v>61</v>
       </c>
       <c r="D22">
-        <v>0.6928</v>
+        <v>0.6875</v>
       </c>
       <c r="E22">
-        <v>36.64</v>
+        <v>36.24</v>
       </c>
       <c r="F22">
-        <v>1372.7</v>
+        <v>1362.4</v>
       </c>
       <c r="G22">
-        <v>-4.36</v>
+        <v>-5.47</v>
       </c>
       <c r="H22">
-        <v>-6.44</v>
+        <v>-6.92</v>
       </c>
       <c r="I22">
         <v>168</v>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B23" t="s">
         <v>32</v>
@@ -1371,19 +1371,19 @@
         <v>62</v>
       </c>
       <c r="D23">
-        <v>0.6927</v>
+        <v>0.6728</v>
       </c>
       <c r="E23">
-        <v>36.45</v>
+        <v>35.63</v>
       </c>
       <c r="F23">
-        <v>1362.4</v>
+        <v>1372.7</v>
       </c>
       <c r="G23">
-        <v>-5.47</v>
+        <v>-4.36</v>
       </c>
       <c r="H23">
-        <v>-6.92</v>
+        <v>-6.44</v>
       </c>
       <c r="I23">
         <v>168</v>
@@ -1406,10 +1406,10 @@
         <v>63</v>
       </c>
       <c r="D24">
-        <v>0.6587</v>
+        <v>0.6574</v>
       </c>
       <c r="E24">
-        <v>34.41</v>
+        <v>34.36</v>
       </c>
       <c r="F24">
         <v>1341.3</v>
@@ -1441,10 +1441,10 @@
         <v>64</v>
       </c>
       <c r="D25">
-        <v>0.6309</v>
+        <v>0.63</v>
       </c>
       <c r="E25">
-        <v>33.24</v>
+        <v>33.26</v>
       </c>
       <c r="F25">
         <v>1373.1</v>
@@ -1476,10 +1476,10 @@
         <v>65</v>
       </c>
       <c r="D26">
-        <v>0.619</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="E26">
-        <v>32.18</v>
+        <v>32.22</v>
       </c>
       <c r="F26">
         <v>1388.4</v>
@@ -1511,7 +1511,7 @@
         <v>66</v>
       </c>
       <c r="D27">
-        <v>0.6042</v>
+        <v>0.6031</v>
       </c>
       <c r="E27">
         <v>31.47</v>
@@ -1546,10 +1546,10 @@
         <v>67</v>
       </c>
       <c r="D28">
-        <v>0.5779</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="E28">
-        <v>29.53</v>
+        <v>30.45</v>
       </c>
       <c r="F28">
         <v>1304.2</v>
@@ -1581,10 +1581,10 @@
         <v>68</v>
       </c>
       <c r="D29">
-        <v>0.5397</v>
+        <v>0.541</v>
       </c>
       <c r="E29">
-        <v>27.45</v>
+        <v>27.59</v>
       </c>
       <c r="F29">
         <v>1315.7</v>
@@ -1616,10 +1616,10 @@
         <v>69</v>
       </c>
       <c r="D30">
-        <v>0.5387</v>
+        <v>0.5367</v>
       </c>
       <c r="E30">
-        <v>26.9</v>
+        <v>26.82</v>
       </c>
       <c r="F30">
         <v>1254.6</v>
@@ -1651,10 +1651,10 @@
         <v>70</v>
       </c>
       <c r="D31">
-        <v>0.513</v>
+        <v>0.5133</v>
       </c>
       <c r="E31">
-        <v>25.88</v>
+        <v>25.97</v>
       </c>
       <c r="F31">
         <v>1288.6</v>

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -49,33 +49,33 @@
     <t>rank</t>
   </si>
   <si>
+    <t>San Antonio Spurs</t>
+  </si>
+  <si>
+    <t>Boston Celtics</t>
+  </si>
+  <si>
+    <t>New York Knicks</t>
+  </si>
+  <si>
+    <t>Detroit Pistons</t>
+  </si>
+  <si>
+    <t>Denver Nuggets</t>
+  </si>
+  <si>
     <t>Oklahoma City Thunder</t>
   </si>
   <si>
-    <t>San Antonio Spurs</t>
-  </si>
-  <si>
-    <t>Boston Celtics</t>
-  </si>
-  <si>
-    <t>New York Knicks</t>
-  </si>
-  <si>
-    <t>Denver Nuggets</t>
+    <t>Houston Rockets</t>
+  </si>
+  <si>
+    <t>Charlotte Hornets</t>
   </si>
   <si>
     <t>Cleveland Cavaliers</t>
   </si>
   <si>
-    <t>Charlotte Hornets</t>
-  </si>
-  <si>
-    <t>Detroit Pistons</t>
-  </si>
-  <si>
-    <t>Houston Rockets</t>
-  </si>
-  <si>
     <t>Atlanta Hawks</t>
   </si>
   <si>
@@ -88,42 +88,42 @@
     <t>Minnesota Timberwolves</t>
   </si>
   <si>
+    <t>Miami Heat</t>
+  </si>
+  <si>
+    <t>Los Angeles Lakers</t>
+  </si>
+  <si>
+    <t>Orlando Magic</t>
+  </si>
+  <si>
     <t>Phoenix Suns</t>
   </si>
   <si>
-    <t>Miami Heat</t>
+    <t>Portland Trail Blazers</t>
   </si>
   <si>
     <t>Philadelphia 76ers</t>
   </si>
   <si>
-    <t>Portland Trail Blazers</t>
-  </si>
-  <si>
     <t>Golden State Warriors</t>
   </si>
   <si>
-    <t>Los Angeles Lakers</t>
-  </si>
-  <si>
-    <t>Orlando Magic</t>
+    <t>Milwaukee Bucks</t>
   </si>
   <si>
     <t>Dallas Mavericks</t>
   </si>
   <si>
+    <t>Chicago Bulls</t>
+  </si>
+  <si>
+    <t>Indiana Pacers</t>
+  </si>
+  <si>
     <t>New Orleans Pelicans</t>
   </si>
   <si>
-    <t>Indiana Pacers</t>
-  </si>
-  <si>
-    <t>Chicago Bulls</t>
-  </si>
-  <si>
-    <t>Milwaukee Bucks</t>
-  </si>
-  <si>
     <t>Memphis Grizzlies</t>
   </si>
   <si>
@@ -139,33 +139,33 @@
     <t>Brooklyn Nets</t>
   </si>
   <si>
+    <t>SAS</t>
+  </si>
+  <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>NYK</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>DEN</t>
+  </si>
+  <si>
     <t>OKC</t>
   </si>
   <si>
-    <t>SAS</t>
-  </si>
-  <si>
-    <t>BOS</t>
-  </si>
-  <si>
-    <t>NYK</t>
-  </si>
-  <si>
-    <t>DEN</t>
+    <t>HOU</t>
+  </si>
+  <si>
+    <t>CHA</t>
   </si>
   <si>
     <t>CLE</t>
   </si>
   <si>
-    <t>CHA</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>HOU</t>
-  </si>
-  <si>
     <t>ATL</t>
   </si>
   <si>
@@ -178,42 +178,42 @@
     <t>MIN</t>
   </si>
   <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>ORL</t>
+  </si>
+  <si>
     <t>PHX</t>
   </si>
   <si>
-    <t>MIA</t>
+    <t>POR</t>
   </si>
   <si>
     <t>PHI</t>
   </si>
   <si>
-    <t>POR</t>
-  </si>
-  <si>
     <t>GSW</t>
   </si>
   <si>
-    <t>LAL</t>
-  </si>
-  <si>
-    <t>ORL</t>
+    <t>MIL</t>
   </si>
   <si>
     <t>DAL</t>
   </si>
   <si>
+    <t>CHI</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
     <t>NOP</t>
   </si>
   <si>
-    <t>IND</t>
-  </si>
-  <si>
-    <t>CHI</t>
-  </si>
-  <si>
-    <t>MIL</t>
-  </si>
-  <si>
     <t>MEM</t>
   </si>
   <si>
@@ -229,7 +229,7 @@
     <t>BKN</t>
   </si>
   <si>
-    <t>2026-04-07</t>
+    <t>2026-04-10</t>
   </si>
 </sst>
 </file>
@@ -627,7 +627,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2">
-        <v>1610612760</v>
+        <v>1610612759</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -636,22 +636,22 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>1.5785</v>
+        <v>1.5199</v>
       </c>
       <c r="E2">
-        <v>73.7</v>
+        <v>72.14</v>
       </c>
       <c r="F2">
-        <v>1762.4</v>
+        <v>1738.9</v>
       </c>
       <c r="G2">
-        <v>12.1</v>
+        <v>8.67</v>
       </c>
       <c r="H2">
-        <v>18.44</v>
+        <v>14.29</v>
       </c>
       <c r="I2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J2" t="s">
         <v>71</v>
@@ -662,7 +662,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3">
-        <v>1610612759</v>
+        <v>1610612738</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -671,22 +671,22 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>1.5091</v>
+        <v>1.4971</v>
       </c>
       <c r="E3">
-        <v>71.56</v>
+        <v>71.61</v>
       </c>
       <c r="F3">
-        <v>1737.7</v>
+        <v>1674</v>
       </c>
       <c r="G3">
-        <v>8.56</v>
+        <v>7.17</v>
       </c>
       <c r="H3">
-        <v>15.7</v>
+        <v>8.17</v>
       </c>
       <c r="I3">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J3" t="s">
         <v>71</v>
@@ -697,7 +697,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4">
-        <v>1610612738</v>
+        <v>1610612752</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -706,22 +706,22 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>1.4946</v>
+        <v>1.4179</v>
       </c>
       <c r="E4">
-        <v>71.34999999999999</v>
+        <v>68.64</v>
       </c>
       <c r="F4">
-        <v>1669.3</v>
+        <v>1653.7</v>
       </c>
       <c r="G4">
-        <v>7.59</v>
+        <v>6.79</v>
       </c>
       <c r="H4">
-        <v>10.22</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J4" t="s">
         <v>71</v>
@@ -732,7 +732,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5">
-        <v>1610612752</v>
+        <v>1610612765</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -741,22 +741,22 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>1.3912</v>
+        <v>1.4111</v>
       </c>
       <c r="E5">
-        <v>67.48</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="F5">
-        <v>1651</v>
+        <v>1680.7</v>
       </c>
       <c r="G5">
-        <v>6.81</v>
+        <v>7.8</v>
       </c>
       <c r="H5">
-        <v>7.62</v>
+        <v>11.6</v>
       </c>
       <c r="I5">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J5" t="s">
         <v>71</v>
@@ -776,22 +776,22 @@
         <v>45</v>
       </c>
       <c r="D6">
-        <v>1.388</v>
+        <v>1.4084</v>
       </c>
       <c r="E6">
-        <v>67.08</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="F6">
-        <v>1605.2</v>
+        <v>1606.6</v>
       </c>
       <c r="G6">
-        <v>4.67</v>
+        <v>4.89</v>
       </c>
       <c r="H6">
-        <v>8.619999999999999</v>
+        <v>7.25</v>
       </c>
       <c r="I6">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J6" t="s">
         <v>71</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7">
-        <v>1610612739</v>
+        <v>1610612760</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
@@ -811,22 +811,22 @@
         <v>46</v>
       </c>
       <c r="D7">
-        <v>1.3876</v>
+        <v>1.3217</v>
       </c>
       <c r="E7">
-        <v>67.2</v>
+        <v>62.13</v>
       </c>
       <c r="F7">
-        <v>1640.2</v>
+        <v>1769.5</v>
       </c>
       <c r="G7">
-        <v>4.42</v>
+        <v>12.28</v>
       </c>
       <c r="H7">
-        <v>4.44</v>
+        <v>21.17</v>
       </c>
       <c r="I7">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J7" t="s">
         <v>71</v>
@@ -837,7 +837,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8">
-        <v>1610612766</v>
+        <v>1610612745</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -846,22 +846,22 @@
         <v>47</v>
       </c>
       <c r="D8">
-        <v>1.2817</v>
+        <v>1.291</v>
       </c>
       <c r="E8">
-        <v>62.84</v>
+        <v>63.48</v>
       </c>
       <c r="F8">
-        <v>1587.9</v>
+        <v>1593.7</v>
       </c>
       <c r="G8">
-        <v>4.05</v>
+        <v>4.92</v>
       </c>
       <c r="H8">
-        <v>15.96</v>
+        <v>11.9</v>
       </c>
       <c r="I8">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J8" t="s">
         <v>71</v>
@@ -872,7 +872,7 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9">
-        <v>1610612765</v>
+        <v>1610612766</v>
       </c>
       <c r="B9" t="s">
         <v>18</v>
@@ -881,22 +881,22 @@
         <v>48</v>
       </c>
       <c r="D9">
-        <v>1.2718</v>
+        <v>1.2804</v>
       </c>
       <c r="E9">
-        <v>61.8</v>
+        <v>62.97</v>
       </c>
       <c r="F9">
-        <v>1687.7</v>
+        <v>1593.1</v>
       </c>
       <c r="G9">
-        <v>6.87</v>
+        <v>3.38</v>
       </c>
       <c r="H9">
-        <v>10.07</v>
+        <v>12.18</v>
       </c>
       <c r="I9">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J9" t="s">
         <v>71</v>
@@ -907,7 +907,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10">
-        <v>1610612745</v>
+        <v>1610612739</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
@@ -916,22 +916,22 @@
         <v>49</v>
       </c>
       <c r="D10">
-        <v>1.2572</v>
+        <v>1.2606</v>
       </c>
       <c r="E10">
-        <v>62.18</v>
+        <v>62.22</v>
       </c>
       <c r="F10">
-        <v>1587.3</v>
+        <v>1642.2</v>
       </c>
       <c r="G10">
-        <v>4.75</v>
+        <v>4.35</v>
       </c>
       <c r="H10">
-        <v>10.72</v>
+        <v>4.4</v>
       </c>
       <c r="I10">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J10" t="s">
         <v>71</v>
@@ -951,22 +951,22 @@
         <v>50</v>
       </c>
       <c r="D11">
-        <v>1.1745</v>
+        <v>1.1879</v>
       </c>
       <c r="E11">
-        <v>58.77</v>
+        <v>59.22</v>
       </c>
       <c r="F11">
-        <v>1532.7</v>
+        <v>1530</v>
       </c>
       <c r="G11">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="H11">
-        <v>10.02</v>
+        <v>8.25</v>
       </c>
       <c r="I11">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J11" t="s">
         <v>71</v>
@@ -986,22 +986,22 @@
         <v>51</v>
       </c>
       <c r="D12">
-        <v>1.1468</v>
+        <v>1.1739</v>
       </c>
       <c r="E12">
-        <v>57.76</v>
+        <v>58.74</v>
       </c>
       <c r="F12">
-        <v>1550.8</v>
+        <v>1554.7</v>
       </c>
       <c r="G12">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="H12">
-        <v>6.36</v>
+        <v>7.24</v>
       </c>
       <c r="I12">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J12" t="s">
         <v>71</v>
@@ -1021,22 +1021,22 @@
         <v>52</v>
       </c>
       <c r="D13">
-        <v>1.1074</v>
+        <v>1.1493</v>
       </c>
       <c r="E13">
-        <v>56.1</v>
+        <v>57.74</v>
       </c>
       <c r="F13">
-        <v>1515.2</v>
+        <v>1518.4</v>
       </c>
       <c r="G13">
-        <v>1.54</v>
+        <v>2.5</v>
       </c>
       <c r="H13">
-        <v>2.78</v>
+        <v>5.48</v>
       </c>
       <c r="I13">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J13" t="s">
         <v>71</v>
@@ -1056,22 +1056,22 @@
         <v>53</v>
       </c>
       <c r="D14">
-        <v>1.0968</v>
+        <v>1.12</v>
       </c>
       <c r="E14">
-        <v>55.41</v>
+        <v>56.33</v>
       </c>
       <c r="F14">
-        <v>1572.9</v>
+        <v>1570</v>
       </c>
       <c r="G14">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="H14">
-        <v>-0.41</v>
+        <v>-0.2</v>
       </c>
       <c r="I14">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J14" t="s">
         <v>71</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15">
-        <v>1610612756</v>
+        <v>1610612748</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
@@ -1091,22 +1091,22 @@
         <v>54</v>
       </c>
       <c r="D15">
-        <v>1.0281</v>
+        <v>1.0243</v>
       </c>
       <c r="E15">
-        <v>52.71</v>
+        <v>52.05</v>
       </c>
       <c r="F15">
-        <v>1504.6</v>
+        <v>1524.1</v>
       </c>
       <c r="G15">
-        <v>1.69</v>
+        <v>1.33</v>
       </c>
       <c r="H15">
-        <v>2.41</v>
+        <v>-7.87</v>
       </c>
       <c r="I15">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J15" t="s">
         <v>71</v>
@@ -1117,7 +1117,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16">
-        <v>1610612748</v>
+        <v>1610612747</v>
       </c>
       <c r="B16" t="s">
         <v>25</v>
@@ -1126,22 +1126,22 @@
         <v>55</v>
       </c>
       <c r="D16">
-        <v>1.0195</v>
+        <v>1.0139</v>
       </c>
       <c r="E16">
-        <v>52.09</v>
+        <v>51.79</v>
       </c>
       <c r="F16">
-        <v>1528.7</v>
+        <v>1554.9</v>
       </c>
       <c r="G16">
-        <v>2.21</v>
+        <v>1.94</v>
       </c>
       <c r="H16">
-        <v>-6.17</v>
+        <v>1.76</v>
       </c>
       <c r="I16">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J16" t="s">
         <v>71</v>
@@ -1152,7 +1152,7 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B17" t="s">
         <v>26</v>
@@ -1161,22 +1161,22 @@
         <v>56</v>
       </c>
       <c r="D17">
-        <v>1.0052</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="E17">
-        <v>51.61</v>
+        <v>50.58</v>
       </c>
       <c r="F17">
-        <v>1474.2</v>
+        <v>1520.1</v>
       </c>
       <c r="G17">
-        <v>-0.03</v>
+        <v>0.19</v>
       </c>
       <c r="H17">
-        <v>-0.74</v>
+        <v>-4.66</v>
       </c>
       <c r="I17">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J17" t="s">
         <v>71</v>
@@ -1187,7 +1187,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>1610612757</v>
+        <v>1610612756</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -1196,22 +1196,22 @@
         <v>57</v>
       </c>
       <c r="D18">
-        <v>0.9647</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="E18">
-        <v>49.58</v>
+        <v>50.34</v>
       </c>
       <c r="F18">
-        <v>1469.1</v>
+        <v>1502.5</v>
       </c>
       <c r="G18">
-        <v>-1.1</v>
+        <v>1.48</v>
       </c>
       <c r="H18">
-        <v>10.79</v>
+        <v>3.6</v>
       </c>
       <c r="I18">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J18" t="s">
         <v>71</v>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19">
-        <v>1610612744</v>
+        <v>1610612757</v>
       </c>
       <c r="B19" t="s">
         <v>28</v>
@@ -1231,22 +1231,22 @@
         <v>58</v>
       </c>
       <c r="D19">
-        <v>0.9548</v>
+        <v>0.9734</v>
       </c>
       <c r="E19">
-        <v>49.51</v>
+        <v>50.03</v>
       </c>
       <c r="F19">
-        <v>1472.7</v>
+        <v>1467.7</v>
       </c>
       <c r="G19">
-        <v>-0.48</v>
+        <v>-1.4</v>
       </c>
       <c r="H19">
-        <v>-6.25</v>
+        <v>7.99</v>
       </c>
       <c r="I19">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J19" t="s">
         <v>71</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20">
-        <v>1610612747</v>
+        <v>1610612755</v>
       </c>
       <c r="B20" t="s">
         <v>29</v>
@@ -1266,22 +1266,22 @@
         <v>59</v>
       </c>
       <c r="D20">
-        <v>0.9513</v>
+        <v>0.9695</v>
       </c>
       <c r="E20">
-        <v>48.7</v>
+        <v>50.01</v>
       </c>
       <c r="F20">
-        <v>1564.6</v>
+        <v>1473</v>
       </c>
       <c r="G20">
-        <v>2.03</v>
+        <v>-0.1</v>
       </c>
       <c r="H20">
-        <v>5.11</v>
+        <v>1.12</v>
       </c>
       <c r="I20">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J20" t="s">
         <v>71</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21">
-        <v>1610612753</v>
+        <v>1610612744</v>
       </c>
       <c r="B21" t="s">
         <v>30</v>
@@ -1301,22 +1301,22 @@
         <v>60</v>
       </c>
       <c r="D21">
-        <v>0.9357</v>
+        <v>0.9641</v>
       </c>
       <c r="E21">
-        <v>48.54</v>
+        <v>49.73</v>
       </c>
       <c r="F21">
-        <v>1513.1</v>
+        <v>1471.1</v>
       </c>
       <c r="G21">
-        <v>0.06</v>
+        <v>-0.7</v>
       </c>
       <c r="H21">
-        <v>-7.5</v>
+        <v>-6.04</v>
       </c>
       <c r="I21">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J21" t="s">
         <v>71</v>
@@ -1327,7 +1327,7 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
-        <v>1610612742</v>
+        <v>1610612749</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
@@ -1336,22 +1336,22 @@
         <v>61</v>
       </c>
       <c r="D22">
-        <v>0.6875</v>
+        <v>0.672</v>
       </c>
       <c r="E22">
-        <v>36.24</v>
+        <v>35.17</v>
       </c>
       <c r="F22">
-        <v>1362.4</v>
+        <v>1389</v>
       </c>
       <c r="G22">
-        <v>-5.47</v>
+        <v>-6.7</v>
       </c>
       <c r="H22">
-        <v>-6.92</v>
+        <v>-14.66</v>
       </c>
       <c r="I22">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J22" t="s">
         <v>71</v>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23">
-        <v>1610612740</v>
+        <v>1610612742</v>
       </c>
       <c r="B23" t="s">
         <v>32</v>
@@ -1371,22 +1371,22 @@
         <v>62</v>
       </c>
       <c r="D23">
-        <v>0.6728</v>
+        <v>0.6702</v>
       </c>
       <c r="E23">
-        <v>35.63</v>
+        <v>35.41</v>
       </c>
       <c r="F23">
-        <v>1372.7</v>
+        <v>1364.5</v>
       </c>
       <c r="G23">
-        <v>-4.36</v>
+        <v>-5.73</v>
       </c>
       <c r="H23">
-        <v>-6.44</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="I23">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J23" t="s">
         <v>71</v>
@@ -1397,7 +1397,7 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24">
-        <v>1610612754</v>
+        <v>1610612741</v>
       </c>
       <c r="B24" t="s">
         <v>33</v>
@@ -1406,22 +1406,22 @@
         <v>63</v>
       </c>
       <c r="D24">
-        <v>0.6574</v>
+        <v>0.6559</v>
       </c>
       <c r="E24">
-        <v>34.36</v>
+        <v>34.66</v>
       </c>
       <c r="F24">
-        <v>1341.3</v>
+        <v>1373.8</v>
       </c>
       <c r="G24">
-        <v>-7.5</v>
+        <v>-4.07</v>
       </c>
       <c r="H24">
-        <v>-3.45</v>
+        <v>-7.79</v>
       </c>
       <c r="I24">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J24" t="s">
         <v>71</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25">
-        <v>1610612741</v>
+        <v>1610612754</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
@@ -1441,22 +1441,22 @@
         <v>64</v>
       </c>
       <c r="D25">
-        <v>0.63</v>
+        <v>0.6556</v>
       </c>
       <c r="E25">
-        <v>33.26</v>
+        <v>34.3</v>
       </c>
       <c r="F25">
-        <v>1373.1</v>
+        <v>1338.4</v>
       </c>
       <c r="G25">
-        <v>-4.9</v>
+        <v>-6.85</v>
       </c>
       <c r="H25">
-        <v>-11.65</v>
+        <v>2.19</v>
       </c>
       <c r="I25">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J25" t="s">
         <v>71</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26">
-        <v>1610612749</v>
+        <v>1610612740</v>
       </c>
       <c r="B26" t="s">
         <v>35</v>
@@ -1476,22 +1476,22 @@
         <v>65</v>
       </c>
       <c r="D26">
-        <v>0.6183999999999999</v>
+        <v>0.6514</v>
       </c>
       <c r="E26">
-        <v>32.22</v>
+        <v>34.41</v>
       </c>
       <c r="F26">
-        <v>1388.4</v>
+        <v>1370.9</v>
       </c>
       <c r="G26">
-        <v>-5.5</v>
+        <v>-3.89</v>
       </c>
       <c r="H26">
-        <v>-14.06</v>
+        <v>-6.13</v>
       </c>
       <c r="I26">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J26" t="s">
         <v>71</v>
@@ -1511,22 +1511,22 @@
         <v>66</v>
       </c>
       <c r="D27">
-        <v>0.6031</v>
+        <v>0.5896</v>
       </c>
       <c r="E27">
-        <v>31.47</v>
+        <v>30.8</v>
       </c>
       <c r="F27">
-        <v>1371.2</v>
+        <v>1369.3</v>
       </c>
       <c r="G27">
-        <v>-5.97</v>
+        <v>-6</v>
       </c>
       <c r="H27">
-        <v>-19.74</v>
+        <v>-19.96</v>
       </c>
       <c r="I27">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J27" t="s">
         <v>71</v>
@@ -1546,22 +1546,22 @@
         <v>67</v>
       </c>
       <c r="D28">
-        <v>0.5953000000000001</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="E28">
-        <v>30.45</v>
+        <v>29.95</v>
       </c>
       <c r="F28">
-        <v>1304.2</v>
+        <v>1303.5</v>
       </c>
       <c r="G28">
-        <v>-8.869999999999999</v>
+        <v>-8.66</v>
       </c>
       <c r="H28">
-        <v>-13.68</v>
+        <v>-12.2</v>
       </c>
       <c r="I28">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J28" t="s">
         <v>71</v>
@@ -1581,22 +1581,22 @@
         <v>68</v>
       </c>
       <c r="D29">
-        <v>0.541</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="E29">
-        <v>27.59</v>
+        <v>27.68</v>
       </c>
       <c r="F29">
-        <v>1315.7</v>
+        <v>1312.9</v>
       </c>
       <c r="G29">
-        <v>-9.609999999999999</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="H29">
-        <v>-11.58</v>
+        <v>-12.05</v>
       </c>
       <c r="I29">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J29" t="s">
         <v>71</v>
@@ -1616,22 +1616,22 @@
         <v>69</v>
       </c>
       <c r="D30">
-        <v>0.5367</v>
+        <v>0.5189</v>
       </c>
       <c r="E30">
-        <v>26.82</v>
+        <v>25.99</v>
       </c>
       <c r="F30">
-        <v>1254.6</v>
+        <v>1251.3</v>
       </c>
       <c r="G30">
-        <v>-11.35</v>
+        <v>-11.54</v>
       </c>
       <c r="H30">
-        <v>-15.6</v>
+        <v>-15.71</v>
       </c>
       <c r="I30">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J30" t="s">
         <v>71</v>
@@ -1651,22 +1651,22 @@
         <v>70</v>
       </c>
       <c r="D31">
-        <v>0.5133</v>
+        <v>0.5172</v>
       </c>
       <c r="E31">
-        <v>25.97</v>
+        <v>26.23</v>
       </c>
       <c r="F31">
-        <v>1288.6</v>
+        <v>1290.9</v>
       </c>
       <c r="G31">
-        <v>-10</v>
+        <v>-10.5</v>
       </c>
       <c r="H31">
-        <v>-13.37</v>
+        <v>-11.49</v>
       </c>
       <c r="I31">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J31" t="s">
         <v>71</v>

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -49,64 +49,73 @@
     <t>rank</t>
   </si>
   <si>
+    <t>Detroit Pistons</t>
+  </si>
+  <si>
     <t>San Antonio Spurs</t>
   </si>
   <si>
+    <t>Denver Nuggets</t>
+  </si>
+  <si>
+    <t>Charlotte Hornets</t>
+  </si>
+  <si>
     <t>Boston Celtics</t>
   </si>
   <si>
+    <t>Oklahoma City Thunder</t>
+  </si>
+  <si>
+    <t>Toronto Raptors</t>
+  </si>
+  <si>
+    <t>LA Clippers</t>
+  </si>
+  <si>
     <t>New York Knicks</t>
   </si>
   <si>
-    <t>Detroit Pistons</t>
-  </si>
-  <si>
-    <t>Denver Nuggets</t>
-  </si>
-  <si>
-    <t>Oklahoma City Thunder</t>
+    <t>Atlanta Hawks</t>
+  </si>
+  <si>
+    <t>Miami Heat</t>
+  </si>
+  <si>
+    <t>Cleveland Cavaliers</t>
+  </si>
+  <si>
+    <t>Phoenix Suns</t>
   </si>
   <si>
     <t>Houston Rockets</t>
   </si>
   <si>
-    <t>Charlotte Hornets</t>
-  </si>
-  <si>
-    <t>Cleveland Cavaliers</t>
-  </si>
-  <si>
-    <t>Atlanta Hawks</t>
-  </si>
-  <si>
-    <t>LA Clippers</t>
-  </si>
-  <si>
-    <t>Toronto Raptors</t>
+    <t>Golden State Warriors</t>
+  </si>
+  <si>
+    <t>Los Angeles Lakers</t>
+  </si>
+  <si>
+    <t>Portland Trail Blazers</t>
+  </si>
+  <si>
+    <t>Orlando Magic</t>
+  </si>
+  <si>
+    <t>Philadelphia 76ers</t>
   </si>
   <si>
     <t>Minnesota Timberwolves</t>
   </si>
   <si>
-    <t>Miami Heat</t>
-  </si>
-  <si>
-    <t>Los Angeles Lakers</t>
-  </si>
-  <si>
-    <t>Orlando Magic</t>
-  </si>
-  <si>
-    <t>Phoenix Suns</t>
-  </si>
-  <si>
-    <t>Portland Trail Blazers</t>
-  </si>
-  <si>
-    <t>Philadelphia 76ers</t>
-  </si>
-  <si>
-    <t>Golden State Warriors</t>
+    <t>Chicago Bulls</t>
+  </si>
+  <si>
+    <t>Indiana Pacers</t>
+  </si>
+  <si>
+    <t>New Orleans Pelicans</t>
   </si>
   <si>
     <t>Milwaukee Bucks</t>
@@ -115,21 +124,12 @@
     <t>Dallas Mavericks</t>
   </si>
   <si>
-    <t>Chicago Bulls</t>
-  </si>
-  <si>
-    <t>Indiana Pacers</t>
-  </si>
-  <si>
-    <t>New Orleans Pelicans</t>
+    <t>Utah Jazz</t>
   </si>
   <si>
     <t>Memphis Grizzlies</t>
   </si>
   <si>
-    <t>Utah Jazz</t>
-  </si>
-  <si>
     <t>Sacramento Kings</t>
   </si>
   <si>
@@ -139,64 +139,73 @@
     <t>Brooklyn Nets</t>
   </si>
   <si>
+    <t>DET</t>
+  </si>
+  <si>
     <t>SAS</t>
   </si>
   <si>
+    <t>DEN</t>
+  </si>
+  <si>
+    <t>CHA</t>
+  </si>
+  <si>
     <t>BOS</t>
   </si>
   <si>
+    <t>OKC</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>LAC</t>
+  </si>
+  <si>
     <t>NYK</t>
   </si>
   <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>DEN</t>
-  </si>
-  <si>
-    <t>OKC</t>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t>PHX</t>
   </si>
   <si>
     <t>HOU</t>
   </si>
   <si>
-    <t>CHA</t>
-  </si>
-  <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>ATL</t>
-  </si>
-  <si>
-    <t>LAC</t>
-  </si>
-  <si>
-    <t>TOR</t>
+    <t>GSW</t>
+  </si>
+  <si>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>POR</t>
+  </si>
+  <si>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>PHI</t>
   </si>
   <si>
     <t>MIN</t>
   </si>
   <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>LAL</t>
-  </si>
-  <si>
-    <t>ORL</t>
-  </si>
-  <si>
-    <t>PHX</t>
-  </si>
-  <si>
-    <t>POR</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>GSW</t>
+    <t>CHI</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>NOP</t>
   </si>
   <si>
     <t>MIL</t>
@@ -205,21 +214,12 @@
     <t>DAL</t>
   </si>
   <si>
-    <t>CHI</t>
-  </si>
-  <si>
-    <t>IND</t>
-  </si>
-  <si>
-    <t>NOP</t>
+    <t>UTA</t>
   </si>
   <si>
     <t>MEM</t>
   </si>
   <si>
-    <t>UTA</t>
-  </si>
-  <si>
     <t>SAC</t>
   </si>
   <si>
@@ -229,7 +229,7 @@
     <t>BKN</t>
   </si>
   <si>
-    <t>2026-04-10</t>
+    <t>2026-04-13</t>
   </si>
 </sst>
 </file>
@@ -627,7 +627,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2">
-        <v>1610612759</v>
+        <v>1610612765</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -636,22 +636,22 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>1.5199</v>
+        <v>1.4585</v>
       </c>
       <c r="E2">
-        <v>72.14</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="F2">
-        <v>1738.9</v>
+        <v>1687.7</v>
       </c>
       <c r="G2">
-        <v>8.67</v>
+        <v>7.92</v>
       </c>
       <c r="H2">
-        <v>14.29</v>
+        <v>13.43</v>
       </c>
       <c r="I2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J2" t="s">
         <v>71</v>
@@ -662,7 +662,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3">
-        <v>1610612738</v>
+        <v>1610612759</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -671,22 +671,22 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>1.4971</v>
+        <v>1.4534</v>
       </c>
       <c r="E3">
-        <v>71.61</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="F3">
-        <v>1674</v>
+        <v>1740.7</v>
       </c>
       <c r="G3">
-        <v>7.17</v>
+        <v>8.23</v>
       </c>
       <c r="H3">
-        <v>8.17</v>
+        <v>13.34</v>
       </c>
       <c r="I3">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J3" t="s">
         <v>71</v>
@@ -697,7 +697,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4">
-        <v>1610612752</v>
+        <v>1610612743</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -706,22 +706,22 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>1.4179</v>
+        <v>1.3569</v>
       </c>
       <c r="E4">
-        <v>68.64</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F4">
-        <v>1653.7</v>
+        <v>1617</v>
       </c>
       <c r="G4">
-        <v>6.79</v>
+        <v>5.1</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>9.65</v>
       </c>
       <c r="I4">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J4" t="s">
         <v>71</v>
@@ -732,7 +732,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5">
-        <v>1610612765</v>
+        <v>1610612766</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -741,22 +741,22 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>1.4111</v>
+        <v>1.3334</v>
       </c>
       <c r="E5">
-        <v>67.79000000000001</v>
+        <v>65.16</v>
       </c>
       <c r="F5">
-        <v>1680.7</v>
+        <v>1585.1</v>
       </c>
       <c r="G5">
-        <v>7.8</v>
+        <v>3.48</v>
       </c>
       <c r="H5">
-        <v>11.6</v>
+        <v>7.63</v>
       </c>
       <c r="I5">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J5" t="s">
         <v>71</v>
@@ -767,7 +767,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6">
-        <v>1610612743</v>
+        <v>1610612738</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
@@ -776,22 +776,22 @@
         <v>45</v>
       </c>
       <c r="D6">
-        <v>1.4084</v>
+        <v>1.294</v>
       </c>
       <c r="E6">
-        <v>67.84999999999999</v>
+        <v>63.29</v>
       </c>
       <c r="F6">
-        <v>1606.6</v>
+        <v>1672.1</v>
       </c>
       <c r="G6">
-        <v>4.89</v>
+        <v>7.6</v>
       </c>
       <c r="H6">
-        <v>7.25</v>
+        <v>11.58</v>
       </c>
       <c r="I6">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J6" t="s">
         <v>71</v>
@@ -811,22 +811,22 @@
         <v>46</v>
       </c>
       <c r="D7">
-        <v>1.3217</v>
+        <v>1.2904</v>
       </c>
       <c r="E7">
-        <v>62.13</v>
+        <v>61.7</v>
       </c>
       <c r="F7">
-        <v>1769.5</v>
+        <v>1764.1</v>
       </c>
       <c r="G7">
-        <v>12.28</v>
+        <v>10.65</v>
       </c>
       <c r="H7">
-        <v>21.17</v>
+        <v>11.73</v>
       </c>
       <c r="I7">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J7" t="s">
         <v>71</v>
@@ -837,7 +837,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8">
-        <v>1610612745</v>
+        <v>1610612761</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -846,22 +846,22 @@
         <v>47</v>
       </c>
       <c r="D8">
-        <v>1.291</v>
+        <v>1.2653</v>
       </c>
       <c r="E8">
-        <v>63.48</v>
+        <v>62.25</v>
       </c>
       <c r="F8">
-        <v>1593.7</v>
+        <v>1519.1</v>
       </c>
       <c r="G8">
-        <v>4.92</v>
+        <v>2.84</v>
       </c>
       <c r="H8">
-        <v>11.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I8">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J8" t="s">
         <v>71</v>
@@ -872,7 +872,7 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9">
-        <v>1610612766</v>
+        <v>1610612746</v>
       </c>
       <c r="B9" t="s">
         <v>18</v>
@@ -881,22 +881,22 @@
         <v>48</v>
       </c>
       <c r="D9">
-        <v>1.2804</v>
+        <v>1.2405</v>
       </c>
       <c r="E9">
-        <v>62.97</v>
+        <v>61.33</v>
       </c>
       <c r="F9">
-        <v>1593.1</v>
+        <v>1546.1</v>
       </c>
       <c r="G9">
-        <v>3.38</v>
+        <v>1.89</v>
       </c>
       <c r="H9">
-        <v>12.18</v>
+        <v>5.42</v>
       </c>
       <c r="I9">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J9" t="s">
         <v>71</v>
@@ -907,7 +907,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10">
-        <v>1610612739</v>
+        <v>1610612752</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
@@ -916,22 +916,22 @@
         <v>49</v>
       </c>
       <c r="D10">
-        <v>1.2606</v>
+        <v>1.2078</v>
       </c>
       <c r="E10">
-        <v>62.22</v>
+        <v>59.81</v>
       </c>
       <c r="F10">
-        <v>1642.2</v>
+        <v>1659.5</v>
       </c>
       <c r="G10">
-        <v>4.35</v>
+        <v>6.58</v>
       </c>
       <c r="H10">
-        <v>4.4</v>
+        <v>5.41</v>
       </c>
       <c r="I10">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J10" t="s">
         <v>71</v>
@@ -951,22 +951,22 @@
         <v>50</v>
       </c>
       <c r="D11">
-        <v>1.1879</v>
+        <v>1.206</v>
       </c>
       <c r="E11">
-        <v>59.22</v>
+        <v>59.83</v>
       </c>
       <c r="F11">
-        <v>1530</v>
+        <v>1535.4</v>
       </c>
       <c r="G11">
-        <v>2.09</v>
+        <v>1.76</v>
       </c>
       <c r="H11">
-        <v>8.25</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="I11">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J11" t="s">
         <v>71</v>
@@ -977,7 +977,7 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12">
-        <v>1610612746</v>
+        <v>1610612748</v>
       </c>
       <c r="B12" t="s">
         <v>21</v>
@@ -986,22 +986,22 @@
         <v>51</v>
       </c>
       <c r="D12">
-        <v>1.1739</v>
+        <v>1.1452</v>
       </c>
       <c r="E12">
-        <v>58.74</v>
+        <v>57.16</v>
       </c>
       <c r="F12">
-        <v>1554.7</v>
+        <v>1522.6</v>
       </c>
       <c r="G12">
-        <v>1.9</v>
+        <v>2.47</v>
       </c>
       <c r="H12">
-        <v>7.24</v>
+        <v>-1.4</v>
       </c>
       <c r="I12">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J12" t="s">
         <v>71</v>
@@ -1012,7 +1012,7 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13">
-        <v>1610612761</v>
+        <v>1610612739</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
@@ -1021,22 +1021,22 @@
         <v>52</v>
       </c>
       <c r="D13">
-        <v>1.1493</v>
+        <v>1.1318</v>
       </c>
       <c r="E13">
-        <v>57.74</v>
+        <v>56.71</v>
       </c>
       <c r="F13">
-        <v>1518.4</v>
+        <v>1636.7</v>
       </c>
       <c r="G13">
-        <v>2.5</v>
+        <v>4.26</v>
       </c>
       <c r="H13">
-        <v>5.48</v>
+        <v>2.49</v>
       </c>
       <c r="I13">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J13" t="s">
         <v>71</v>
@@ -1047,7 +1047,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14">
-        <v>1610612750</v>
+        <v>1610612756</v>
       </c>
       <c r="B14" t="s">
         <v>23</v>
@@ -1056,22 +1056,22 @@
         <v>53</v>
       </c>
       <c r="D14">
-        <v>1.12</v>
+        <v>1.1195</v>
       </c>
       <c r="E14">
-        <v>56.33</v>
+        <v>56.35</v>
       </c>
       <c r="F14">
-        <v>1570</v>
+        <v>1499.2</v>
       </c>
       <c r="G14">
-        <v>3.35</v>
+        <v>1.68</v>
       </c>
       <c r="H14">
-        <v>-0.2</v>
+        <v>4.11</v>
       </c>
       <c r="I14">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J14" t="s">
         <v>71</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15">
-        <v>1610612748</v>
+        <v>1610612745</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
@@ -1091,22 +1091,22 @@
         <v>54</v>
       </c>
       <c r="D15">
-        <v>1.0243</v>
+        <v>1.1142</v>
       </c>
       <c r="E15">
-        <v>52.05</v>
+        <v>55.54</v>
       </c>
       <c r="F15">
-        <v>1524.1</v>
+        <v>1591.5</v>
       </c>
       <c r="G15">
-        <v>1.33</v>
+        <v>5.28</v>
       </c>
       <c r="H15">
-        <v>-7.87</v>
+        <v>14.7</v>
       </c>
       <c r="I15">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J15" t="s">
         <v>71</v>
@@ -1117,7 +1117,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16">
-        <v>1610612747</v>
+        <v>1610612744</v>
       </c>
       <c r="B16" t="s">
         <v>25</v>
@@ -1126,22 +1126,22 @@
         <v>55</v>
       </c>
       <c r="D16">
-        <v>1.0139</v>
+        <v>1.0815</v>
       </c>
       <c r="E16">
-        <v>51.79</v>
+        <v>54.41</v>
       </c>
       <c r="F16">
-        <v>1554.9</v>
+        <v>1465</v>
       </c>
       <c r="G16">
-        <v>1.94</v>
+        <v>-0.58</v>
       </c>
       <c r="H16">
-        <v>1.76</v>
+        <v>-4.18</v>
       </c>
       <c r="I16">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J16" t="s">
         <v>71</v>
@@ -1152,7 +1152,7 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>1610612753</v>
+        <v>1610612747</v>
       </c>
       <c r="B17" t="s">
         <v>26</v>
@@ -1161,22 +1161,22 @@
         <v>56</v>
       </c>
       <c r="D17">
-        <v>0.9814000000000001</v>
+        <v>1.0792</v>
       </c>
       <c r="E17">
-        <v>50.58</v>
+        <v>54.6</v>
       </c>
       <c r="F17">
-        <v>1520.1</v>
+        <v>1563.1</v>
       </c>
       <c r="G17">
-        <v>0.19</v>
+        <v>2.88</v>
       </c>
       <c r="H17">
-        <v>-4.66</v>
+        <v>5.75</v>
       </c>
       <c r="I17">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J17" t="s">
         <v>71</v>
@@ -1187,7 +1187,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>1610612756</v>
+        <v>1610612757</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -1196,22 +1196,22 @@
         <v>57</v>
       </c>
       <c r="D18">
-        <v>0.9782999999999999</v>
+        <v>1.072</v>
       </c>
       <c r="E18">
-        <v>50.34</v>
+        <v>54.1</v>
       </c>
       <c r="F18">
-        <v>1502.5</v>
+        <v>1471.6</v>
       </c>
       <c r="G18">
-        <v>1.48</v>
+        <v>-0.76</v>
       </c>
       <c r="H18">
-        <v>3.6</v>
+        <v>9.57</v>
       </c>
       <c r="I18">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J18" t="s">
         <v>71</v>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19">
-        <v>1610612757</v>
+        <v>1610612753</v>
       </c>
       <c r="B19" t="s">
         <v>28</v>
@@ -1231,22 +1231,22 @@
         <v>58</v>
       </c>
       <c r="D19">
-        <v>0.9734</v>
+        <v>1.0706</v>
       </c>
       <c r="E19">
-        <v>50.03</v>
+        <v>54.18</v>
       </c>
       <c r="F19">
-        <v>1467.7</v>
+        <v>1527</v>
       </c>
       <c r="G19">
-        <v>-1.4</v>
+        <v>0.14</v>
       </c>
       <c r="H19">
-        <v>7.99</v>
+        <v>-1.71</v>
       </c>
       <c r="I19">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J19" t="s">
         <v>71</v>
@@ -1266,22 +1266,22 @@
         <v>59</v>
       </c>
       <c r="D20">
-        <v>0.9695</v>
+        <v>1.0679</v>
       </c>
       <c r="E20">
-        <v>50.01</v>
+        <v>54.06</v>
       </c>
       <c r="F20">
-        <v>1473</v>
+        <v>1473.1</v>
       </c>
       <c r="G20">
-        <v>-0.1</v>
+        <v>0.72</v>
       </c>
       <c r="H20">
-        <v>1.12</v>
+        <v>2.26</v>
       </c>
       <c r="I20">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J20" t="s">
         <v>71</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21">
-        <v>1610612744</v>
+        <v>1610612750</v>
       </c>
       <c r="B21" t="s">
         <v>30</v>
@@ -1301,22 +1301,22 @@
         <v>60</v>
       </c>
       <c r="D21">
-        <v>0.9641</v>
+        <v>1.0364</v>
       </c>
       <c r="E21">
-        <v>49.73</v>
+        <v>52.46</v>
       </c>
       <c r="F21">
-        <v>1471.1</v>
+        <v>1570.4</v>
       </c>
       <c r="G21">
-        <v>-0.7</v>
+        <v>3.77</v>
       </c>
       <c r="H21">
-        <v>-6.04</v>
+        <v>-0.58</v>
       </c>
       <c r="I21">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J21" t="s">
         <v>71</v>
@@ -1327,7 +1327,7 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
-        <v>1610612749</v>
+        <v>1610612741</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
@@ -1336,22 +1336,22 @@
         <v>61</v>
       </c>
       <c r="D22">
-        <v>0.672</v>
+        <v>0.6761</v>
       </c>
       <c r="E22">
-        <v>35.17</v>
+        <v>35.55</v>
       </c>
       <c r="F22">
-        <v>1389</v>
+        <v>1371.5</v>
       </c>
       <c r="G22">
-        <v>-6.7</v>
+        <v>-4.88</v>
       </c>
       <c r="H22">
-        <v>-14.66</v>
+        <v>-12.12</v>
       </c>
       <c r="I22">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J22" t="s">
         <v>71</v>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23">
-        <v>1610612742</v>
+        <v>1610612754</v>
       </c>
       <c r="B23" t="s">
         <v>32</v>
@@ -1371,22 +1371,22 @@
         <v>62</v>
       </c>
       <c r="D23">
-        <v>0.6702</v>
+        <v>0.6706</v>
       </c>
       <c r="E23">
-        <v>35.41</v>
+        <v>35.21</v>
       </c>
       <c r="F23">
-        <v>1364.5</v>
+        <v>1339.6</v>
       </c>
       <c r="G23">
-        <v>-5.73</v>
+        <v>-7.43</v>
       </c>
       <c r="H23">
-        <v>-8.470000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="I23">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J23" t="s">
         <v>71</v>
@@ -1397,7 +1397,7 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24">
-        <v>1610612741</v>
+        <v>1610612740</v>
       </c>
       <c r="B24" t="s">
         <v>33</v>
@@ -1406,22 +1406,22 @@
         <v>63</v>
       </c>
       <c r="D24">
-        <v>0.6559</v>
+        <v>0.6354</v>
       </c>
       <c r="E24">
-        <v>34.66</v>
+        <v>33.5</v>
       </c>
       <c r="F24">
-        <v>1373.8</v>
+        <v>1371.2</v>
       </c>
       <c r="G24">
-        <v>-4.07</v>
+        <v>-4.59</v>
       </c>
       <c r="H24">
-        <v>-7.79</v>
+        <v>-11.5</v>
       </c>
       <c r="I24">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J24" t="s">
         <v>71</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25">
-        <v>1610612754</v>
+        <v>1610612749</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
@@ -1441,22 +1441,22 @@
         <v>64</v>
       </c>
       <c r="D25">
-        <v>0.6556</v>
+        <v>0.6344</v>
       </c>
       <c r="E25">
-        <v>34.3</v>
+        <v>33.29</v>
       </c>
       <c r="F25">
-        <v>1338.4</v>
+        <v>1388.8</v>
       </c>
       <c r="G25">
-        <v>-6.85</v>
+        <v>-6.46</v>
       </c>
       <c r="H25">
-        <v>2.19</v>
+        <v>-13.09</v>
       </c>
       <c r="I25">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J25" t="s">
         <v>71</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26">
-        <v>1610612740</v>
+        <v>1610612742</v>
       </c>
       <c r="B26" t="s">
         <v>35</v>
@@ -1476,22 +1476,22 @@
         <v>65</v>
       </c>
       <c r="D26">
-        <v>0.6514</v>
+        <v>0.6075</v>
       </c>
       <c r="E26">
-        <v>34.41</v>
+        <v>32.21</v>
       </c>
       <c r="F26">
-        <v>1370.9</v>
+        <v>1362.8</v>
       </c>
       <c r="G26">
-        <v>-3.89</v>
+        <v>-5.24</v>
       </c>
       <c r="H26">
-        <v>-6.13</v>
+        <v>-5.8</v>
       </c>
       <c r="I26">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J26" t="s">
         <v>71</v>
@@ -1502,7 +1502,7 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27">
-        <v>1610612763</v>
+        <v>1610612762</v>
       </c>
       <c r="B27" t="s">
         <v>36</v>
@@ -1511,22 +1511,22 @@
         <v>66</v>
       </c>
       <c r="D27">
-        <v>0.5896</v>
+        <v>0.6037</v>
       </c>
       <c r="E27">
-        <v>30.8</v>
+        <v>31.13</v>
       </c>
       <c r="F27">
-        <v>1369.3</v>
+        <v>1306.2</v>
       </c>
       <c r="G27">
-        <v>-6</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="H27">
-        <v>-19.96</v>
+        <v>-13.15</v>
       </c>
       <c r="I27">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J27" t="s">
         <v>71</v>
@@ -1537,7 +1537,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28">
-        <v>1610612762</v>
+        <v>1610612763</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
@@ -1546,22 +1546,22 @@
         <v>67</v>
       </c>
       <c r="D28">
-        <v>0.5842000000000001</v>
+        <v>0.6014</v>
       </c>
       <c r="E28">
-        <v>29.95</v>
+        <v>31.59</v>
       </c>
       <c r="F28">
-        <v>1303.5</v>
+        <v>1363.7</v>
       </c>
       <c r="G28">
-        <v>-8.66</v>
+        <v>-6.83</v>
       </c>
       <c r="H28">
-        <v>-12.2</v>
+        <v>-19.87</v>
       </c>
       <c r="I28">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J28" t="s">
         <v>71</v>
@@ -1581,22 +1581,22 @@
         <v>68</v>
       </c>
       <c r="D29">
-        <v>0.5407999999999999</v>
+        <v>0.5319</v>
       </c>
       <c r="E29">
-        <v>27.68</v>
+        <v>27.47</v>
       </c>
       <c r="F29">
-        <v>1312.9</v>
+        <v>1314.3</v>
       </c>
       <c r="G29">
-        <v>-9.279999999999999</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="H29">
-        <v>-12.05</v>
+        <v>-8.25</v>
       </c>
       <c r="I29">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J29" t="s">
         <v>71</v>
@@ -1616,22 +1616,22 @@
         <v>69</v>
       </c>
       <c r="D30">
-        <v>0.5189</v>
+        <v>0.526</v>
       </c>
       <c r="E30">
-        <v>25.99</v>
+        <v>26.57</v>
       </c>
       <c r="F30">
-        <v>1251.3</v>
+        <v>1248.5</v>
       </c>
       <c r="G30">
-        <v>-11.54</v>
+        <v>-11.82</v>
       </c>
       <c r="H30">
-        <v>-15.71</v>
+        <v>-14.92</v>
       </c>
       <c r="I30">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J30" t="s">
         <v>71</v>
@@ -1651,22 +1651,22 @@
         <v>70</v>
       </c>
       <c r="D31">
-        <v>0.5172</v>
+        <v>0.4884</v>
       </c>
       <c r="E31">
-        <v>26.23</v>
+        <v>24.78</v>
       </c>
       <c r="F31">
-        <v>1290.9</v>
+        <v>1286.6</v>
       </c>
       <c r="G31">
-        <v>-10.5</v>
+        <v>-10.84</v>
       </c>
       <c r="H31">
-        <v>-11.49</v>
+        <v>-14.6</v>
       </c>
       <c r="I31">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J31" t="s">
         <v>71</v>

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -49,87 +49,87 @@
     <t>rank</t>
   </si>
   <si>
+    <t>Boston Celtics</t>
+  </si>
+  <si>
+    <t>New York Knicks</t>
+  </si>
+  <si>
+    <t>Denver Nuggets</t>
+  </si>
+  <si>
+    <t>Cleveland Cavaliers</t>
+  </si>
+  <si>
     <t>Detroit Pistons</t>
   </si>
   <si>
     <t>San Antonio Spurs</t>
   </si>
   <si>
-    <t>Denver Nuggets</t>
+    <t>Oklahoma City Thunder</t>
+  </si>
+  <si>
+    <t>Houston Rockets</t>
+  </si>
+  <si>
+    <t>Atlanta Hawks</t>
   </si>
   <si>
     <t>Charlotte Hornets</t>
   </si>
   <si>
-    <t>Boston Celtics</t>
-  </si>
-  <si>
-    <t>Oklahoma City Thunder</t>
-  </si>
-  <si>
     <t>Toronto Raptors</t>
   </si>
   <si>
+    <t>Minnesota Timberwolves</t>
+  </si>
+  <si>
     <t>LA Clippers</t>
   </si>
   <si>
-    <t>New York Knicks</t>
-  </si>
-  <si>
-    <t>Atlanta Hawks</t>
+    <t>Los Angeles Lakers</t>
+  </si>
+  <si>
+    <t>Phoenix Suns</t>
+  </si>
+  <si>
+    <t>Portland Trail Blazers</t>
   </si>
   <si>
     <t>Miami Heat</t>
   </si>
   <si>
-    <t>Cleveland Cavaliers</t>
-  </si>
-  <si>
-    <t>Phoenix Suns</t>
-  </si>
-  <si>
-    <t>Houston Rockets</t>
+    <t>Orlando Magic</t>
+  </si>
+  <si>
+    <t>Philadelphia 76ers</t>
   </si>
   <si>
     <t>Golden State Warriors</t>
   </si>
   <si>
-    <t>Los Angeles Lakers</t>
-  </si>
-  <si>
-    <t>Portland Trail Blazers</t>
-  </si>
-  <si>
-    <t>Orlando Magic</t>
-  </si>
-  <si>
-    <t>Philadelphia 76ers</t>
-  </si>
-  <si>
-    <t>Minnesota Timberwolves</t>
+    <t>Indiana Pacers</t>
   </si>
   <si>
     <t>Chicago Bulls</t>
   </si>
   <si>
-    <t>Indiana Pacers</t>
+    <t>Milwaukee Bucks</t>
+  </si>
+  <si>
+    <t>Dallas Mavericks</t>
   </si>
   <si>
     <t>New Orleans Pelicans</t>
   </si>
   <si>
-    <t>Milwaukee Bucks</t>
-  </si>
-  <si>
-    <t>Dallas Mavericks</t>
+    <t>Memphis Grizzlies</t>
   </si>
   <si>
     <t>Utah Jazz</t>
   </si>
   <si>
-    <t>Memphis Grizzlies</t>
-  </si>
-  <si>
     <t>Sacramento Kings</t>
   </si>
   <si>
@@ -139,87 +139,87 @@
     <t>Brooklyn Nets</t>
   </si>
   <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>NYK</t>
+  </si>
+  <si>
+    <t>DEN</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
     <t>DET</t>
   </si>
   <si>
     <t>SAS</t>
   </si>
   <si>
-    <t>DEN</t>
+    <t>OKC</t>
+  </si>
+  <si>
+    <t>HOU</t>
+  </si>
+  <si>
+    <t>ATL</t>
   </si>
   <si>
     <t>CHA</t>
   </si>
   <si>
-    <t>BOS</t>
-  </si>
-  <si>
-    <t>OKC</t>
-  </si>
-  <si>
     <t>TOR</t>
   </si>
   <si>
+    <t>MIN</t>
+  </si>
+  <si>
     <t>LAC</t>
   </si>
   <si>
-    <t>NYK</t>
-  </si>
-  <si>
-    <t>ATL</t>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>PHX</t>
+  </si>
+  <si>
+    <t>POR</t>
   </si>
   <si>
     <t>MIA</t>
   </si>
   <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>PHX</t>
-  </si>
-  <si>
-    <t>HOU</t>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>PHI</t>
   </si>
   <si>
     <t>GSW</t>
   </si>
   <si>
-    <t>LAL</t>
-  </si>
-  <si>
-    <t>POR</t>
-  </si>
-  <si>
-    <t>ORL</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>MIN</t>
+    <t>IND</t>
   </si>
   <si>
     <t>CHI</t>
   </si>
   <si>
-    <t>IND</t>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>DAL</t>
   </si>
   <si>
     <t>NOP</t>
   </si>
   <si>
-    <t>MIL</t>
-  </si>
-  <si>
-    <t>DAL</t>
+    <t>MEM</t>
   </si>
   <si>
     <t>UTA</t>
   </si>
   <si>
-    <t>MEM</t>
-  </si>
-  <si>
     <t>SAC</t>
   </si>
   <si>
@@ -229,7 +229,7 @@
     <t>BKN</t>
   </si>
   <si>
-    <t>2026-04-13</t>
+    <t>2026-04-18</t>
   </si>
 </sst>
 </file>
@@ -627,7 +627,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2">
-        <v>1610612765</v>
+        <v>1610612738</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -636,22 +636,22 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>1.4585</v>
+        <v>1.4641</v>
       </c>
       <c r="E2">
-        <v>69.95999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="F2">
-        <v>1687.7</v>
+        <v>1672.1</v>
       </c>
       <c r="G2">
-        <v>7.92</v>
+        <v>7.6</v>
       </c>
       <c r="H2">
-        <v>13.43</v>
+        <v>11.58</v>
       </c>
       <c r="I2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J2" t="s">
         <v>71</v>
@@ -662,7 +662,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3">
-        <v>1610612759</v>
+        <v>1610612752</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -671,22 +671,22 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>1.4534</v>
+        <v>1.4253</v>
       </c>
       <c r="E3">
-        <v>69.70999999999999</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="F3">
-        <v>1740.7</v>
+        <v>1659.5</v>
       </c>
       <c r="G3">
-        <v>8.23</v>
+        <v>6.58</v>
       </c>
       <c r="H3">
-        <v>13.34</v>
+        <v>5.41</v>
       </c>
       <c r="I3">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J3" t="s">
         <v>71</v>
@@ -706,10 +706,10 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>1.3569</v>
+        <v>1.4218</v>
       </c>
       <c r="E4">
-        <v>66.09999999999999</v>
+        <v>68.52</v>
       </c>
       <c r="F4">
         <v>1617</v>
@@ -721,7 +721,7 @@
         <v>9.65</v>
       </c>
       <c r="I4">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J4" t="s">
         <v>71</v>
@@ -732,7 +732,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5">
-        <v>1610612766</v>
+        <v>1610612739</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -741,22 +741,22 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>1.3334</v>
+        <v>1.3981</v>
       </c>
       <c r="E5">
-        <v>65.16</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="F5">
-        <v>1585.1</v>
+        <v>1636.7</v>
       </c>
       <c r="G5">
-        <v>3.48</v>
+        <v>4.26</v>
       </c>
       <c r="H5">
-        <v>7.63</v>
+        <v>2.49</v>
       </c>
       <c r="I5">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J5" t="s">
         <v>71</v>
@@ -767,7 +767,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6">
-        <v>1610612738</v>
+        <v>1610612765</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
@@ -776,22 +776,22 @@
         <v>45</v>
       </c>
       <c r="D6">
-        <v>1.294</v>
+        <v>1.3876</v>
       </c>
       <c r="E6">
-        <v>63.29</v>
+        <v>66.64</v>
       </c>
       <c r="F6">
-        <v>1672.1</v>
+        <v>1687.7</v>
       </c>
       <c r="G6">
-        <v>7.6</v>
+        <v>7.92</v>
       </c>
       <c r="H6">
-        <v>11.58</v>
+        <v>13.43</v>
       </c>
       <c r="I6">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J6" t="s">
         <v>71</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7">
-        <v>1610612760</v>
+        <v>1610612759</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
@@ -811,22 +811,22 @@
         <v>46</v>
       </c>
       <c r="D7">
-        <v>1.2904</v>
+        <v>1.3842</v>
       </c>
       <c r="E7">
-        <v>61.7</v>
+        <v>66.44</v>
       </c>
       <c r="F7">
-        <v>1764.1</v>
+        <v>1740.7</v>
       </c>
       <c r="G7">
-        <v>10.65</v>
+        <v>8.23</v>
       </c>
       <c r="H7">
-        <v>11.73</v>
+        <v>13.34</v>
       </c>
       <c r="I7">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J7" t="s">
         <v>71</v>
@@ -837,7 +837,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8">
-        <v>1610612761</v>
+        <v>1610612760</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -846,22 +846,22 @@
         <v>47</v>
       </c>
       <c r="D8">
-        <v>1.2653</v>
+        <v>1.2771</v>
       </c>
       <c r="E8">
-        <v>62.25</v>
+        <v>60.85</v>
       </c>
       <c r="F8">
-        <v>1519.1</v>
+        <v>1764.1</v>
       </c>
       <c r="G8">
-        <v>2.84</v>
+        <v>10.65</v>
       </c>
       <c r="H8">
-        <v>8.300000000000001</v>
+        <v>11.73</v>
       </c>
       <c r="I8">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J8" t="s">
         <v>71</v>
@@ -872,7 +872,7 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9">
-        <v>1610612746</v>
+        <v>1610612745</v>
       </c>
       <c r="B9" t="s">
         <v>18</v>
@@ -881,22 +881,22 @@
         <v>48</v>
       </c>
       <c r="D9">
-        <v>1.2405</v>
+        <v>1.2246</v>
       </c>
       <c r="E9">
-        <v>61.33</v>
+        <v>60.45</v>
       </c>
       <c r="F9">
-        <v>1546.1</v>
+        <v>1591.5</v>
       </c>
       <c r="G9">
-        <v>1.89</v>
+        <v>5.28</v>
       </c>
       <c r="H9">
-        <v>5.42</v>
+        <v>14.7</v>
       </c>
       <c r="I9">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J9" t="s">
         <v>71</v>
@@ -907,7 +907,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10">
-        <v>1610612752</v>
+        <v>1610612737</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
@@ -916,22 +916,22 @@
         <v>49</v>
       </c>
       <c r="D10">
-        <v>1.2078</v>
+        <v>1.2015</v>
       </c>
       <c r="E10">
-        <v>59.81</v>
+        <v>59.7</v>
       </c>
       <c r="F10">
-        <v>1659.5</v>
+        <v>1535.4</v>
       </c>
       <c r="G10">
-        <v>6.58</v>
+        <v>1.76</v>
       </c>
       <c r="H10">
-        <v>5.41</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="I10">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J10" t="s">
         <v>71</v>
@@ -942,7 +942,7 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11">
-        <v>1610612737</v>
+        <v>1610612766</v>
       </c>
       <c r="B11" t="s">
         <v>20</v>
@@ -951,22 +951,22 @@
         <v>50</v>
       </c>
       <c r="D11">
-        <v>1.206</v>
+        <v>1.1981</v>
       </c>
       <c r="E11">
-        <v>59.83</v>
+        <v>59.54</v>
       </c>
       <c r="F11">
-        <v>1535.4</v>
+        <v>1595.9</v>
       </c>
       <c r="G11">
-        <v>1.76</v>
+        <v>2.43</v>
       </c>
       <c r="H11">
-        <v>8.720000000000001</v>
+        <v>-0.17</v>
       </c>
       <c r="I11">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J11" t="s">
         <v>71</v>
@@ -977,7 +977,7 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12">
-        <v>1610612748</v>
+        <v>1610612761</v>
       </c>
       <c r="B12" t="s">
         <v>21</v>
@@ -986,22 +986,22 @@
         <v>51</v>
       </c>
       <c r="D12">
-        <v>1.1452</v>
+        <v>1.1764</v>
       </c>
       <c r="E12">
-        <v>57.16</v>
+        <v>58.64</v>
       </c>
       <c r="F12">
-        <v>1522.6</v>
+        <v>1519.1</v>
       </c>
       <c r="G12">
-        <v>2.47</v>
+        <v>2.84</v>
       </c>
       <c r="H12">
-        <v>-1.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I12">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J12" t="s">
         <v>71</v>
@@ -1012,7 +1012,7 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13">
-        <v>1610612739</v>
+        <v>1610612750</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
@@ -1021,22 +1021,22 @@
         <v>52</v>
       </c>
       <c r="D13">
-        <v>1.1318</v>
+        <v>1.1602</v>
       </c>
       <c r="E13">
-        <v>56.71</v>
+        <v>57.87</v>
       </c>
       <c r="F13">
-        <v>1636.7</v>
+        <v>1570.4</v>
       </c>
       <c r="G13">
-        <v>4.26</v>
+        <v>3.77</v>
       </c>
       <c r="H13">
-        <v>2.49</v>
+        <v>-0.58</v>
       </c>
       <c r="I13">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J13" t="s">
         <v>71</v>
@@ -1047,7 +1047,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14">
-        <v>1610612756</v>
+        <v>1610612746</v>
       </c>
       <c r="B14" t="s">
         <v>23</v>
@@ -1056,22 +1056,22 @@
         <v>53</v>
       </c>
       <c r="D14">
-        <v>1.1195</v>
+        <v>1.1287</v>
       </c>
       <c r="E14">
-        <v>56.35</v>
+        <v>56.85</v>
       </c>
       <c r="F14">
-        <v>1499.2</v>
+        <v>1547.6</v>
       </c>
       <c r="G14">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="H14">
-        <v>4.11</v>
+        <v>1.77</v>
       </c>
       <c r="I14">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J14" t="s">
         <v>71</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15">
-        <v>1610612745</v>
+        <v>1610612747</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
@@ -1091,22 +1091,22 @@
         <v>54</v>
       </c>
       <c r="D15">
-        <v>1.1142</v>
+        <v>1.0906</v>
       </c>
       <c r="E15">
-        <v>55.54</v>
+        <v>55.12</v>
       </c>
       <c r="F15">
-        <v>1591.5</v>
+        <v>1563.1</v>
       </c>
       <c r="G15">
-        <v>5.28</v>
+        <v>2.88</v>
       </c>
       <c r="H15">
-        <v>14.7</v>
+        <v>5.75</v>
       </c>
       <c r="I15">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J15" t="s">
         <v>71</v>
@@ -1117,7 +1117,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16">
-        <v>1610612744</v>
+        <v>1610612756</v>
       </c>
       <c r="B16" t="s">
         <v>25</v>
@@ -1126,22 +1126,22 @@
         <v>55</v>
       </c>
       <c r="D16">
-        <v>1.0815</v>
+        <v>1.0591</v>
       </c>
       <c r="E16">
-        <v>54.41</v>
+        <v>53.83</v>
       </c>
       <c r="F16">
-        <v>1465</v>
+        <v>1507</v>
       </c>
       <c r="G16">
-        <v>-0.58</v>
+        <v>1.76</v>
       </c>
       <c r="H16">
-        <v>-4.18</v>
+        <v>3.82</v>
       </c>
       <c r="I16">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J16" t="s">
         <v>71</v>
@@ -1152,7 +1152,7 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>1610612747</v>
+        <v>1610612757</v>
       </c>
       <c r="B17" t="s">
         <v>26</v>
@@ -1161,22 +1161,22 @@
         <v>56</v>
       </c>
       <c r="D17">
-        <v>1.0792</v>
+        <v>1.0352</v>
       </c>
       <c r="E17">
-        <v>54.6</v>
+        <v>52.56</v>
       </c>
       <c r="F17">
-        <v>1563.1</v>
+        <v>1472.6</v>
       </c>
       <c r="G17">
-        <v>2.88</v>
+        <v>-0.85</v>
       </c>
       <c r="H17">
-        <v>5.75</v>
+        <v>10.8</v>
       </c>
       <c r="I17">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J17" t="s">
         <v>71</v>
@@ -1187,7 +1187,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>1610612757</v>
+        <v>1610612748</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -1196,22 +1196,22 @@
         <v>57</v>
       </c>
       <c r="D18">
-        <v>1.072</v>
+        <v>1.0322</v>
       </c>
       <c r="E18">
-        <v>54.1</v>
+        <v>52.53</v>
       </c>
       <c r="F18">
-        <v>1471.6</v>
+        <v>1527.6</v>
       </c>
       <c r="G18">
-        <v>-0.76</v>
+        <v>2.05</v>
       </c>
       <c r="H18">
-        <v>9.57</v>
+        <v>0.27</v>
       </c>
       <c r="I18">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J18" t="s">
         <v>71</v>
@@ -1231,22 +1231,22 @@
         <v>58</v>
       </c>
       <c r="D19">
-        <v>1.0706</v>
+        <v>1.0092</v>
       </c>
       <c r="E19">
-        <v>54.18</v>
+        <v>51.59</v>
       </c>
       <c r="F19">
-        <v>1527</v>
+        <v>1518.6</v>
       </c>
       <c r="G19">
-        <v>0.14</v>
+        <v>0.8</v>
       </c>
       <c r="H19">
-        <v>-1.71</v>
+        <v>0.27</v>
       </c>
       <c r="I19">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J19" t="s">
         <v>71</v>
@@ -1266,22 +1266,22 @@
         <v>59</v>
       </c>
       <c r="D20">
-        <v>1.0679</v>
+        <v>1.0089</v>
       </c>
       <c r="E20">
-        <v>54.06</v>
+        <v>51.65</v>
       </c>
       <c r="F20">
-        <v>1473.1</v>
+        <v>1475.3</v>
       </c>
       <c r="G20">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="H20">
-        <v>2.26</v>
+        <v>5.35</v>
       </c>
       <c r="I20">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J20" t="s">
         <v>71</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21">
-        <v>1610612750</v>
+        <v>1610612744</v>
       </c>
       <c r="B21" t="s">
         <v>30</v>
@@ -1301,22 +1301,22 @@
         <v>60</v>
       </c>
       <c r="D21">
-        <v>1.0364</v>
+        <v>0.9917</v>
       </c>
       <c r="E21">
-        <v>52.46</v>
+        <v>50.85</v>
       </c>
       <c r="F21">
-        <v>1570.4</v>
+        <v>1471.6</v>
       </c>
       <c r="G21">
-        <v>3.77</v>
+        <v>-0.99</v>
       </c>
       <c r="H21">
-        <v>-0.58</v>
+        <v>-5.81</v>
       </c>
       <c r="I21">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J21" t="s">
         <v>71</v>
@@ -1327,7 +1327,7 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
-        <v>1610612741</v>
+        <v>1610612754</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
@@ -1336,22 +1336,22 @@
         <v>61</v>
       </c>
       <c r="D22">
-        <v>0.6761</v>
+        <v>0.6596</v>
       </c>
       <c r="E22">
-        <v>35.55</v>
+        <v>34.69</v>
       </c>
       <c r="F22">
-        <v>1371.5</v>
+        <v>1339.6</v>
       </c>
       <c r="G22">
-        <v>-4.88</v>
+        <v>-7.43</v>
       </c>
       <c r="H22">
-        <v>-12.12</v>
+        <v>0.59</v>
       </c>
       <c r="I22">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J22" t="s">
         <v>71</v>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23">
-        <v>1610612754</v>
+        <v>1610612741</v>
       </c>
       <c r="B23" t="s">
         <v>32</v>
@@ -1371,22 +1371,22 @@
         <v>62</v>
       </c>
       <c r="D23">
-        <v>0.6706</v>
+        <v>0.655</v>
       </c>
       <c r="E23">
-        <v>35.21</v>
+        <v>34.71</v>
       </c>
       <c r="F23">
-        <v>1339.6</v>
+        <v>1371.5</v>
       </c>
       <c r="G23">
-        <v>-7.43</v>
+        <v>-4.88</v>
       </c>
       <c r="H23">
-        <v>0.59</v>
+        <v>-12.12</v>
       </c>
       <c r="I23">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J23" t="s">
         <v>71</v>
@@ -1397,7 +1397,7 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24">
-        <v>1610612740</v>
+        <v>1610612749</v>
       </c>
       <c r="B24" t="s">
         <v>33</v>
@@ -1406,22 +1406,22 @@
         <v>63</v>
       </c>
       <c r="D24">
-        <v>0.6354</v>
+        <v>0.6362</v>
       </c>
       <c r="E24">
-        <v>33.5</v>
+        <v>33.49</v>
       </c>
       <c r="F24">
-        <v>1371.2</v>
+        <v>1388.8</v>
       </c>
       <c r="G24">
-        <v>-4.59</v>
+        <v>-6.46</v>
       </c>
       <c r="H24">
-        <v>-11.5</v>
+        <v>-13.09</v>
       </c>
       <c r="I24">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J24" t="s">
         <v>71</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25">
-        <v>1610612749</v>
+        <v>1610612742</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
@@ -1441,22 +1441,22 @@
         <v>64</v>
       </c>
       <c r="D25">
-        <v>0.6344</v>
+        <v>0.6143</v>
       </c>
       <c r="E25">
-        <v>33.29</v>
+        <v>32.67</v>
       </c>
       <c r="F25">
-        <v>1388.8</v>
+        <v>1362.8</v>
       </c>
       <c r="G25">
-        <v>-6.46</v>
+        <v>-5.24</v>
       </c>
       <c r="H25">
-        <v>-13.09</v>
+        <v>-5.8</v>
       </c>
       <c r="I25">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J25" t="s">
         <v>71</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B26" t="s">
         <v>35</v>
@@ -1476,22 +1476,22 @@
         <v>65</v>
       </c>
       <c r="D26">
-        <v>0.6075</v>
+        <v>0.6089</v>
       </c>
       <c r="E26">
-        <v>32.21</v>
+        <v>32.23</v>
       </c>
       <c r="F26">
-        <v>1362.8</v>
+        <v>1371.2</v>
       </c>
       <c r="G26">
-        <v>-5.24</v>
+        <v>-4.59</v>
       </c>
       <c r="H26">
-        <v>-5.8</v>
+        <v>-11.5</v>
       </c>
       <c r="I26">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J26" t="s">
         <v>71</v>
@@ -1502,7 +1502,7 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27">
-        <v>1610612762</v>
+        <v>1610612763</v>
       </c>
       <c r="B27" t="s">
         <v>36</v>
@@ -1511,22 +1511,22 @@
         <v>66</v>
       </c>
       <c r="D27">
-        <v>0.6037</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="E27">
-        <v>31.13</v>
+        <v>31.2</v>
       </c>
       <c r="F27">
-        <v>1306.2</v>
+        <v>1363.7</v>
       </c>
       <c r="G27">
-        <v>-8.449999999999999</v>
+        <v>-6.83</v>
       </c>
       <c r="H27">
-        <v>-13.15</v>
+        <v>-19.87</v>
       </c>
       <c r="I27">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J27" t="s">
         <v>71</v>
@@ -1537,7 +1537,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28">
-        <v>1610612763</v>
+        <v>1610612762</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
@@ -1546,22 +1546,22 @@
         <v>67</v>
       </c>
       <c r="D28">
-        <v>0.6014</v>
+        <v>0.5907</v>
       </c>
       <c r="E28">
-        <v>31.59</v>
+        <v>30.57</v>
       </c>
       <c r="F28">
-        <v>1363.7</v>
+        <v>1306.2</v>
       </c>
       <c r="G28">
-        <v>-6.83</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="H28">
-        <v>-19.87</v>
+        <v>-13.15</v>
       </c>
       <c r="I28">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J28" t="s">
         <v>71</v>
@@ -1581,10 +1581,10 @@
         <v>68</v>
       </c>
       <c r="D29">
-        <v>0.5319</v>
+        <v>0.541</v>
       </c>
       <c r="E29">
-        <v>27.47</v>
+        <v>28</v>
       </c>
       <c r="F29">
         <v>1314.3</v>
@@ -1596,7 +1596,7 @@
         <v>-8.25</v>
       </c>
       <c r="I29">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J29" t="s">
         <v>71</v>
@@ -1616,10 +1616,10 @@
         <v>69</v>
       </c>
       <c r="D30">
-        <v>0.526</v>
+        <v>0.5266</v>
       </c>
       <c r="E30">
-        <v>26.57</v>
+        <v>26.53</v>
       </c>
       <c r="F30">
         <v>1248.5</v>
@@ -1631,7 +1631,7 @@
         <v>-14.92</v>
       </c>
       <c r="I30">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J30" t="s">
         <v>71</v>
@@ -1651,10 +1651,10 @@
         <v>70</v>
       </c>
       <c r="D31">
-        <v>0.4884</v>
+        <v>0.5016</v>
       </c>
       <c r="E31">
-        <v>24.78</v>
+        <v>25.48</v>
       </c>
       <c r="F31">
         <v>1286.6</v>
@@ -1666,7 +1666,7 @@
         <v>-14.6</v>
       </c>
       <c r="I31">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J31" t="s">
         <v>71</v>

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -79,12 +79,12 @@
     <t>Charlotte Hornets</t>
   </si>
   <si>
+    <t>Minnesota Timberwolves</t>
+  </si>
+  <si>
     <t>Toronto Raptors</t>
   </si>
   <si>
-    <t>Minnesota Timberwolves</t>
-  </si>
-  <si>
     <t>LA Clippers</t>
   </si>
   <si>
@@ -94,21 +94,21 @@
     <t>Phoenix Suns</t>
   </si>
   <si>
+    <t>Miami Heat</t>
+  </si>
+  <si>
+    <t>Philadelphia 76ers</t>
+  </si>
+  <si>
+    <t>Orlando Magic</t>
+  </si>
+  <si>
+    <t>Golden State Warriors</t>
+  </si>
+  <si>
     <t>Portland Trail Blazers</t>
   </si>
   <si>
-    <t>Miami Heat</t>
-  </si>
-  <si>
-    <t>Orlando Magic</t>
-  </si>
-  <si>
-    <t>Philadelphia 76ers</t>
-  </si>
-  <si>
-    <t>Golden State Warriors</t>
-  </si>
-  <si>
     <t>Indiana Pacers</t>
   </si>
   <si>
@@ -169,12 +169,12 @@
     <t>CHA</t>
   </si>
   <si>
+    <t>MIN</t>
+  </si>
+  <si>
     <t>TOR</t>
   </si>
   <si>
-    <t>MIN</t>
-  </si>
-  <si>
     <t>LAC</t>
   </si>
   <si>
@@ -184,19 +184,19 @@
     <t>PHX</t>
   </si>
   <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>GSW</t>
+  </si>
+  <si>
     <t>POR</t>
-  </si>
-  <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>ORL</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>GSW</t>
   </si>
   <si>
     <t>IND</t>
@@ -636,10 +636,10 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>1.4641</v>
+        <v>1.4675</v>
       </c>
       <c r="E2">
-        <v>70.3</v>
+        <v>70.44</v>
       </c>
       <c r="F2">
         <v>1672.1</v>
@@ -671,10 +671,10 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>1.4253</v>
+        <v>1.4289</v>
       </c>
       <c r="E3">
-        <v>68.84999999999999</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="F3">
         <v>1659.5</v>
@@ -706,10 +706,10 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>1.4218</v>
+        <v>1.4253</v>
       </c>
       <c r="E4">
-        <v>68.52</v>
+        <v>68.64</v>
       </c>
       <c r="F4">
         <v>1617</v>
@@ -741,10 +741,10 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>1.3981</v>
+        <v>1.4011</v>
       </c>
       <c r="E5">
-        <v>67.68000000000001</v>
+        <v>67.78</v>
       </c>
       <c r="F5">
         <v>1636.7</v>
@@ -776,10 +776,10 @@
         <v>45</v>
       </c>
       <c r="D6">
-        <v>1.3876</v>
+        <v>1.3895</v>
       </c>
       <c r="E6">
-        <v>66.64</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="F6">
         <v>1687.7</v>
@@ -811,10 +811,10 @@
         <v>46</v>
       </c>
       <c r="D7">
-        <v>1.3842</v>
+        <v>1.3888</v>
       </c>
       <c r="E7">
-        <v>66.44</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="F7">
         <v>1740.7</v>
@@ -846,10 +846,10 @@
         <v>47</v>
       </c>
       <c r="D8">
-        <v>1.2771</v>
+        <v>1.2795</v>
       </c>
       <c r="E8">
-        <v>60.85</v>
+        <v>60.94</v>
       </c>
       <c r="F8">
         <v>1764.1</v>
@@ -881,10 +881,10 @@
         <v>48</v>
       </c>
       <c r="D9">
-        <v>1.2246</v>
+        <v>1.2275</v>
       </c>
       <c r="E9">
-        <v>60.45</v>
+        <v>60.58</v>
       </c>
       <c r="F9">
         <v>1591.5</v>
@@ -916,10 +916,10 @@
         <v>49</v>
       </c>
       <c r="D10">
-        <v>1.2015</v>
+        <v>1.2051</v>
       </c>
       <c r="E10">
-        <v>59.7</v>
+        <v>59.86</v>
       </c>
       <c r="F10">
         <v>1535.4</v>
@@ -951,10 +951,10 @@
         <v>50</v>
       </c>
       <c r="D11">
-        <v>1.1981</v>
+        <v>1.2045</v>
       </c>
       <c r="E11">
-        <v>59.54</v>
+        <v>59.81</v>
       </c>
       <c r="F11">
         <v>1595.9</v>
@@ -977,7 +977,7 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12">
-        <v>1610612761</v>
+        <v>1610612750</v>
       </c>
       <c r="B12" t="s">
         <v>21</v>
@@ -986,19 +986,19 @@
         <v>51</v>
       </c>
       <c r="D12">
-        <v>1.1764</v>
+        <v>1.1626</v>
       </c>
       <c r="E12">
-        <v>58.64</v>
+        <v>58</v>
       </c>
       <c r="F12">
-        <v>1519.1</v>
+        <v>1570.4</v>
       </c>
       <c r="G12">
-        <v>2.84</v>
+        <v>3.77</v>
       </c>
       <c r="H12">
-        <v>8.300000000000001</v>
+        <v>-0.58</v>
       </c>
       <c r="I12">
         <v>179</v>
@@ -1012,7 +1012,7 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13">
-        <v>1610612750</v>
+        <v>1610612761</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
@@ -1021,19 +1021,19 @@
         <v>52</v>
       </c>
       <c r="D13">
-        <v>1.1602</v>
+        <v>1.1585</v>
       </c>
       <c r="E13">
-        <v>57.87</v>
+        <v>57.95</v>
       </c>
       <c r="F13">
-        <v>1570.4</v>
+        <v>1519.1</v>
       </c>
       <c r="G13">
-        <v>3.77</v>
+        <v>2.84</v>
       </c>
       <c r="H13">
-        <v>-0.58</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I13">
         <v>179</v>
@@ -1056,10 +1056,10 @@
         <v>53</v>
       </c>
       <c r="D14">
-        <v>1.1287</v>
+        <v>1.1279</v>
       </c>
       <c r="E14">
-        <v>56.85</v>
+        <v>56.83</v>
       </c>
       <c r="F14">
         <v>1547.6</v>
@@ -1091,10 +1091,10 @@
         <v>54</v>
       </c>
       <c r="D15">
-        <v>1.0906</v>
+        <v>1.0934</v>
       </c>
       <c r="E15">
-        <v>55.12</v>
+        <v>55.24</v>
       </c>
       <c r="F15">
         <v>1563.1</v>
@@ -1126,10 +1126,10 @@
         <v>55</v>
       </c>
       <c r="D16">
-        <v>1.0591</v>
+        <v>1.0599</v>
       </c>
       <c r="E16">
-        <v>53.83</v>
+        <v>53.86</v>
       </c>
       <c r="F16">
         <v>1507</v>
@@ -1152,7 +1152,7 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>1610612757</v>
+        <v>1610612748</v>
       </c>
       <c r="B17" t="s">
         <v>26</v>
@@ -1164,16 +1164,16 @@
         <v>1.0352</v>
       </c>
       <c r="E17">
-        <v>52.56</v>
+        <v>52.65</v>
       </c>
       <c r="F17">
-        <v>1472.6</v>
+        <v>1527.6</v>
       </c>
       <c r="G17">
-        <v>-0.85</v>
+        <v>2.05</v>
       </c>
       <c r="H17">
-        <v>10.8</v>
+        <v>0.27</v>
       </c>
       <c r="I17">
         <v>179</v>
@@ -1187,7 +1187,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>1610612748</v>
+        <v>1610612755</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -1196,19 +1196,19 @@
         <v>57</v>
       </c>
       <c r="D18">
-        <v>1.0322</v>
+        <v>1.0131</v>
       </c>
       <c r="E18">
-        <v>52.53</v>
+        <v>51.82</v>
       </c>
       <c r="F18">
-        <v>1527.6</v>
+        <v>1475.3</v>
       </c>
       <c r="G18">
-        <v>2.05</v>
+        <v>0.7</v>
       </c>
       <c r="H18">
-        <v>0.27</v>
+        <v>5.35</v>
       </c>
       <c r="I18">
         <v>179</v>
@@ -1231,10 +1231,10 @@
         <v>58</v>
       </c>
       <c r="D19">
-        <v>1.0092</v>
+        <v>1.0032</v>
       </c>
       <c r="E19">
-        <v>51.59</v>
+        <v>51.32</v>
       </c>
       <c r="F19">
         <v>1518.6</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20">
-        <v>1610612755</v>
+        <v>1610612744</v>
       </c>
       <c r="B20" t="s">
         <v>29</v>
@@ -1266,19 +1266,19 @@
         <v>59</v>
       </c>
       <c r="D20">
-        <v>1.0089</v>
+        <v>0.9966</v>
       </c>
       <c r="E20">
-        <v>51.65</v>
+        <v>51.07</v>
       </c>
       <c r="F20">
-        <v>1475.3</v>
+        <v>1471.6</v>
       </c>
       <c r="G20">
-        <v>0.7</v>
+        <v>-0.99</v>
       </c>
       <c r="H20">
-        <v>5.35</v>
+        <v>-5.81</v>
       </c>
       <c r="I20">
         <v>179</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21">
-        <v>1610612744</v>
+        <v>1610612757</v>
       </c>
       <c r="B21" t="s">
         <v>30</v>
@@ -1301,19 +1301,19 @@
         <v>60</v>
       </c>
       <c r="D21">
-        <v>0.9917</v>
+        <v>0.9897</v>
       </c>
       <c r="E21">
-        <v>50.85</v>
+        <v>50.61</v>
       </c>
       <c r="F21">
-        <v>1471.6</v>
+        <v>1472.6</v>
       </c>
       <c r="G21">
-        <v>-0.99</v>
+        <v>-0.85</v>
       </c>
       <c r="H21">
-        <v>-5.81</v>
+        <v>10.8</v>
       </c>
       <c r="I21">
         <v>179</v>
@@ -1336,10 +1336,10 @@
         <v>61</v>
       </c>
       <c r="D22">
-        <v>0.6596</v>
+        <v>0.6613</v>
       </c>
       <c r="E22">
-        <v>34.69</v>
+        <v>34.76</v>
       </c>
       <c r="F22">
         <v>1339.6</v>
@@ -1371,10 +1371,10 @@
         <v>62</v>
       </c>
       <c r="D23">
-        <v>0.655</v>
+        <v>0.6573</v>
       </c>
       <c r="E23">
-        <v>34.71</v>
+        <v>34.81</v>
       </c>
       <c r="F23">
         <v>1371.5</v>
@@ -1406,10 +1406,10 @@
         <v>63</v>
       </c>
       <c r="D24">
-        <v>0.6362</v>
+        <v>0.6378</v>
       </c>
       <c r="E24">
-        <v>33.49</v>
+        <v>33.55</v>
       </c>
       <c r="F24">
         <v>1388.8</v>
@@ -1441,10 +1441,10 @@
         <v>64</v>
       </c>
       <c r="D25">
-        <v>0.6143</v>
+        <v>0.6158</v>
       </c>
       <c r="E25">
-        <v>32.67</v>
+        <v>32.72</v>
       </c>
       <c r="F25">
         <v>1362.8</v>
@@ -1476,10 +1476,10 @@
         <v>65</v>
       </c>
       <c r="D26">
-        <v>0.6089</v>
+        <v>0.6098</v>
       </c>
       <c r="E26">
-        <v>32.23</v>
+        <v>32.26</v>
       </c>
       <c r="F26">
         <v>1371.2</v>
@@ -1511,10 +1511,10 @@
         <v>66</v>
       </c>
       <c r="D27">
-        <v>0.5911999999999999</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="E27">
-        <v>31.2</v>
+        <v>31.29</v>
       </c>
       <c r="F27">
         <v>1363.7</v>
@@ -1546,10 +1546,10 @@
         <v>67</v>
       </c>
       <c r="D28">
-        <v>0.5907</v>
+        <v>0.5928</v>
       </c>
       <c r="E28">
-        <v>30.57</v>
+        <v>30.66</v>
       </c>
       <c r="F28">
         <v>1306.2</v>
@@ -1581,10 +1581,10 @@
         <v>68</v>
       </c>
       <c r="D29">
-        <v>0.541</v>
+        <v>0.5429</v>
       </c>
       <c r="E29">
-        <v>28</v>
+        <v>28.07</v>
       </c>
       <c r="F29">
         <v>1314.3</v>
@@ -1616,10 +1616,10 @@
         <v>69</v>
       </c>
       <c r="D30">
-        <v>0.5266</v>
+        <v>0.5279</v>
       </c>
       <c r="E30">
-        <v>26.53</v>
+        <v>26.58</v>
       </c>
       <c r="F30">
         <v>1248.5</v>
@@ -1651,10 +1651,10 @@
         <v>70</v>
       </c>
       <c r="D31">
-        <v>0.5016</v>
+        <v>0.5031</v>
       </c>
       <c r="E31">
-        <v>25.48</v>
+        <v>25.53</v>
       </c>
       <c r="F31">
         <v>1286.6</v>

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -49,66 +49,66 @@
     <t>rank</t>
   </si>
   <si>
+    <t>Oklahoma City Thunder</t>
+  </si>
+  <si>
     <t>Boston Celtics</t>
   </si>
   <si>
+    <t>San Antonio Spurs</t>
+  </si>
+  <si>
+    <t>Denver Nuggets</t>
+  </si>
+  <si>
+    <t>Detroit Pistons</t>
+  </si>
+  <si>
+    <t>Cleveland Cavaliers</t>
+  </si>
+  <si>
     <t>New York Knicks</t>
   </si>
   <si>
-    <t>Denver Nuggets</t>
-  </si>
-  <si>
-    <t>Cleveland Cavaliers</t>
-  </si>
-  <si>
-    <t>Detroit Pistons</t>
-  </si>
-  <si>
-    <t>San Antonio Spurs</t>
-  </si>
-  <si>
-    <t>Oklahoma City Thunder</t>
-  </si>
-  <si>
     <t>Houston Rockets</t>
   </si>
   <si>
+    <t>Minnesota Timberwolves</t>
+  </si>
+  <si>
+    <t>Charlotte Hornets</t>
+  </si>
+  <si>
     <t>Atlanta Hawks</t>
   </si>
   <si>
-    <t>Charlotte Hornets</t>
-  </si>
-  <si>
-    <t>Minnesota Timberwolves</t>
-  </si>
-  <si>
     <t>Toronto Raptors</t>
   </si>
   <si>
+    <t>Los Angeles Lakers</t>
+  </si>
+  <si>
     <t>LA Clippers</t>
   </si>
   <si>
-    <t>Los Angeles Lakers</t>
+    <t>Orlando Magic</t>
+  </si>
+  <si>
+    <t>Miami Heat</t>
   </si>
   <si>
     <t>Phoenix Suns</t>
   </si>
   <si>
-    <t>Miami Heat</t>
+    <t>Portland Trail Blazers</t>
   </si>
   <si>
     <t>Philadelphia 76ers</t>
   </si>
   <si>
-    <t>Orlando Magic</t>
-  </si>
-  <si>
     <t>Golden State Warriors</t>
   </si>
   <si>
-    <t>Portland Trail Blazers</t>
-  </si>
-  <si>
     <t>Indiana Pacers</t>
   </si>
   <si>
@@ -118,18 +118,18 @@
     <t>Milwaukee Bucks</t>
   </si>
   <si>
+    <t>New Orleans Pelicans</t>
+  </si>
+  <si>
     <t>Dallas Mavericks</t>
   </si>
   <si>
-    <t>New Orleans Pelicans</t>
+    <t>Utah Jazz</t>
   </si>
   <si>
     <t>Memphis Grizzlies</t>
   </si>
   <si>
-    <t>Utah Jazz</t>
-  </si>
-  <si>
     <t>Sacramento Kings</t>
   </si>
   <si>
@@ -139,66 +139,66 @@
     <t>Brooklyn Nets</t>
   </si>
   <si>
+    <t>OKC</t>
+  </si>
+  <si>
     <t>BOS</t>
   </si>
   <si>
+    <t>SAS</t>
+  </si>
+  <si>
+    <t>DEN</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
     <t>NYK</t>
   </si>
   <si>
-    <t>DEN</t>
-  </si>
-  <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>SAS</t>
-  </si>
-  <si>
-    <t>OKC</t>
-  </si>
-  <si>
     <t>HOU</t>
   </si>
   <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>CHA</t>
+  </si>
+  <si>
     <t>ATL</t>
   </si>
   <si>
-    <t>CHA</t>
-  </si>
-  <si>
-    <t>MIN</t>
-  </si>
-  <si>
     <t>TOR</t>
   </si>
   <si>
+    <t>LAL</t>
+  </si>
+  <si>
     <t>LAC</t>
   </si>
   <si>
-    <t>LAL</t>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>MIA</t>
   </si>
   <si>
     <t>PHX</t>
   </si>
   <si>
-    <t>MIA</t>
+    <t>POR</t>
   </si>
   <si>
     <t>PHI</t>
   </si>
   <si>
-    <t>ORL</t>
-  </si>
-  <si>
     <t>GSW</t>
   </si>
   <si>
-    <t>POR</t>
-  </si>
-  <si>
     <t>IND</t>
   </si>
   <si>
@@ -208,18 +208,18 @@
     <t>MIL</t>
   </si>
   <si>
+    <t>NOP</t>
+  </si>
+  <si>
     <t>DAL</t>
   </si>
   <si>
-    <t>NOP</t>
+    <t>UTA</t>
   </si>
   <si>
     <t>MEM</t>
   </si>
   <si>
-    <t>UTA</t>
-  </si>
-  <si>
     <t>SAC</t>
   </si>
   <si>
@@ -229,7 +229,7 @@
     <t>BKN</t>
   </si>
   <si>
-    <t>2026-04-18</t>
+    <t>2026-04-22</t>
   </si>
 </sst>
 </file>
@@ -627,7 +627,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2">
-        <v>1610612738</v>
+        <v>1610612760</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -636,22 +636,22 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>1.4675</v>
+        <v>1.576</v>
       </c>
       <c r="E2">
-        <v>70.44</v>
+        <v>73.59</v>
       </c>
       <c r="F2">
-        <v>1672.1</v>
+        <v>1749.1</v>
       </c>
       <c r="G2">
-        <v>7.6</v>
+        <v>12.19</v>
       </c>
       <c r="H2">
-        <v>11.58</v>
+        <v>14.13</v>
       </c>
       <c r="I2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J2" t="s">
         <v>71</v>
@@ -662,7 +662,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3">
-        <v>1610612752</v>
+        <v>1610612738</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -671,22 +671,22 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>1.4289</v>
+        <v>1.5056</v>
       </c>
       <c r="E3">
-        <v>68.98999999999999</v>
+        <v>71.67</v>
       </c>
       <c r="F3">
-        <v>1659.5</v>
+        <v>1680.2</v>
       </c>
       <c r="G3">
-        <v>6.58</v>
+        <v>7.28</v>
       </c>
       <c r="H3">
-        <v>5.41</v>
+        <v>11.91</v>
       </c>
       <c r="I3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J3" t="s">
         <v>71</v>
@@ -697,7 +697,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4">
-        <v>1610612743</v>
+        <v>1610612759</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -706,22 +706,22 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>1.4253</v>
+        <v>1.4824</v>
       </c>
       <c r="E4">
-        <v>68.64</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="F4">
-        <v>1617</v>
+        <v>1737.4</v>
       </c>
       <c r="G4">
-        <v>5.1</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="H4">
-        <v>9.65</v>
+        <v>10.02</v>
       </c>
       <c r="I4">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J4" t="s">
         <v>71</v>
@@ -732,7 +732,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5">
-        <v>1610612739</v>
+        <v>1610612743</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -741,22 +741,22 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>1.4011</v>
+        <v>1.4007</v>
       </c>
       <c r="E5">
-        <v>67.78</v>
+        <v>67.44</v>
       </c>
       <c r="F5">
-        <v>1636.7</v>
+        <v>1628.8</v>
       </c>
       <c r="G5">
-        <v>4.26</v>
+        <v>4.83</v>
       </c>
       <c r="H5">
-        <v>2.49</v>
+        <v>8.18</v>
       </c>
       <c r="I5">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J5" t="s">
         <v>71</v>
@@ -776,22 +776,22 @@
         <v>45</v>
       </c>
       <c r="D6">
-        <v>1.3895</v>
+        <v>1.3999</v>
       </c>
       <c r="E6">
-        <v>66.73999999999999</v>
+        <v>67.09</v>
       </c>
       <c r="F6">
-        <v>1687.7</v>
+        <v>1688.7</v>
       </c>
       <c r="G6">
-        <v>7.92</v>
+        <v>7.19</v>
       </c>
       <c r="H6">
-        <v>13.43</v>
+        <v>11.64</v>
       </c>
       <c r="I6">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J6" t="s">
         <v>71</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7">
-        <v>1610612759</v>
+        <v>1610612739</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
@@ -811,22 +811,22 @@
         <v>46</v>
       </c>
       <c r="D7">
-        <v>1.3888</v>
+        <v>1.3897</v>
       </c>
       <c r="E7">
-        <v>66.65000000000001</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="F7">
-        <v>1740.7</v>
+        <v>1642.1</v>
       </c>
       <c r="G7">
-        <v>8.23</v>
+        <v>4.43</v>
       </c>
       <c r="H7">
-        <v>13.34</v>
+        <v>5.69</v>
       </c>
       <c r="I7">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J7" t="s">
         <v>71</v>
@@ -837,7 +837,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8">
-        <v>1610612760</v>
+        <v>1610612752</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -846,22 +846,22 @@
         <v>47</v>
       </c>
       <c r="D8">
-        <v>1.2795</v>
+        <v>1.382</v>
       </c>
       <c r="E8">
-        <v>60.94</v>
+        <v>66.91</v>
       </c>
       <c r="F8">
-        <v>1764.1</v>
+        <v>1657.3</v>
       </c>
       <c r="G8">
-        <v>10.65</v>
+        <v>6.55</v>
       </c>
       <c r="H8">
-        <v>11.73</v>
+        <v>3.19</v>
       </c>
       <c r="I8">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J8" t="s">
         <v>71</v>
@@ -881,22 +881,22 @@
         <v>48</v>
       </c>
       <c r="D9">
-        <v>1.2275</v>
+        <v>1.2452</v>
       </c>
       <c r="E9">
-        <v>60.58</v>
+        <v>61.55</v>
       </c>
       <c r="F9">
-        <v>1591.5</v>
+        <v>1587</v>
       </c>
       <c r="G9">
-        <v>5.28</v>
+        <v>4.22</v>
       </c>
       <c r="H9">
-        <v>14.7</v>
+        <v>10.52</v>
       </c>
       <c r="I9">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J9" t="s">
         <v>71</v>
@@ -907,7 +907,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10">
-        <v>1610612737</v>
+        <v>1610612750</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
@@ -916,22 +916,22 @@
         <v>49</v>
       </c>
       <c r="D10">
-        <v>1.2051</v>
+        <v>1.1813</v>
       </c>
       <c r="E10">
-        <v>59.86</v>
+        <v>58.84</v>
       </c>
       <c r="F10">
-        <v>1535.4</v>
+        <v>1565.3</v>
       </c>
       <c r="G10">
-        <v>1.76</v>
+        <v>3.52</v>
       </c>
       <c r="H10">
-        <v>8.720000000000001</v>
+        <v>-1.83</v>
       </c>
       <c r="I10">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J10" t="s">
         <v>71</v>
@@ -951,10 +951,10 @@
         <v>50</v>
       </c>
       <c r="D11">
-        <v>1.2045</v>
+        <v>1.1723</v>
       </c>
       <c r="E11">
-        <v>59.81</v>
+        <v>58.46</v>
       </c>
       <c r="F11">
         <v>1595.9</v>
@@ -966,7 +966,7 @@
         <v>-0.17</v>
       </c>
       <c r="I11">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J11" t="s">
         <v>71</v>
@@ -977,7 +977,7 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12">
-        <v>1610612750</v>
+        <v>1610612737</v>
       </c>
       <c r="B12" t="s">
         <v>21</v>
@@ -986,22 +986,22 @@
         <v>51</v>
       </c>
       <c r="D12">
-        <v>1.1626</v>
+        <v>1.1277</v>
       </c>
       <c r="E12">
-        <v>58</v>
+        <v>56.82</v>
       </c>
       <c r="F12">
-        <v>1570.4</v>
+        <v>1526</v>
       </c>
       <c r="G12">
-        <v>3.77</v>
+        <v>2.02</v>
       </c>
       <c r="H12">
-        <v>-0.58</v>
+        <v>4.49</v>
       </c>
       <c r="I12">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J12" t="s">
         <v>71</v>
@@ -1021,22 +1021,22 @@
         <v>52</v>
       </c>
       <c r="D13">
-        <v>1.1585</v>
+        <v>1.1151</v>
       </c>
       <c r="E13">
-        <v>57.95</v>
+        <v>56.23</v>
       </c>
       <c r="F13">
-        <v>1519.1</v>
+        <v>1515.6</v>
       </c>
       <c r="G13">
-        <v>2.84</v>
+        <v>1.92</v>
       </c>
       <c r="H13">
-        <v>8.300000000000001</v>
+        <v>7.11</v>
       </c>
       <c r="I13">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J13" t="s">
         <v>71</v>
@@ -1047,7 +1047,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14">
-        <v>1610612746</v>
+        <v>1610612747</v>
       </c>
       <c r="B14" t="s">
         <v>23</v>
@@ -1056,22 +1056,22 @@
         <v>53</v>
       </c>
       <c r="D14">
-        <v>1.1279</v>
+        <v>1.1022</v>
       </c>
       <c r="E14">
-        <v>56.83</v>
+        <v>55.57</v>
       </c>
       <c r="F14">
-        <v>1547.6</v>
+        <v>1570.6</v>
       </c>
       <c r="G14">
-        <v>1.77</v>
+        <v>3.05</v>
       </c>
       <c r="H14">
-        <v>1.77</v>
+        <v>7.93</v>
       </c>
       <c r="I14">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J14" t="s">
         <v>71</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15">
-        <v>1610612747</v>
+        <v>1610612746</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
@@ -1091,22 +1091,22 @@
         <v>54</v>
       </c>
       <c r="D15">
-        <v>1.0934</v>
+        <v>1.0979</v>
       </c>
       <c r="E15">
-        <v>55.24</v>
+        <v>55.66</v>
       </c>
       <c r="F15">
-        <v>1563.1</v>
+        <v>1547.6</v>
       </c>
       <c r="G15">
-        <v>2.88</v>
+        <v>1.77</v>
       </c>
       <c r="H15">
-        <v>5.75</v>
+        <v>1.77</v>
       </c>
       <c r="I15">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J15" t="s">
         <v>71</v>
@@ -1117,7 +1117,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16">
-        <v>1610612756</v>
+        <v>1610612753</v>
       </c>
       <c r="B16" t="s">
         <v>25</v>
@@ -1126,22 +1126,22 @@
         <v>55</v>
       </c>
       <c r="D16">
-        <v>1.0599</v>
+        <v>1.0212</v>
       </c>
       <c r="E16">
-        <v>53.86</v>
+        <v>52.14</v>
       </c>
       <c r="F16">
-        <v>1507</v>
+        <v>1535.8</v>
       </c>
       <c r="G16">
-        <v>1.76</v>
+        <v>0.8</v>
       </c>
       <c r="H16">
-        <v>3.82</v>
+        <v>5.82</v>
       </c>
       <c r="I16">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J16" t="s">
         <v>71</v>
@@ -1161,10 +1161,10 @@
         <v>56</v>
       </c>
       <c r="D17">
-        <v>1.0352</v>
+        <v>1.0048</v>
       </c>
       <c r="E17">
-        <v>52.65</v>
+        <v>51.6</v>
       </c>
       <c r="F17">
         <v>1527.6</v>
@@ -1176,7 +1176,7 @@
         <v>0.27</v>
       </c>
       <c r="I17">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J17" t="s">
         <v>71</v>
@@ -1187,7 +1187,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>1610612755</v>
+        <v>1610612756</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -1196,22 +1196,22 @@
         <v>57</v>
       </c>
       <c r="D18">
-        <v>1.0131</v>
+        <v>0.9956</v>
       </c>
       <c r="E18">
-        <v>51.82</v>
+        <v>51.3</v>
       </c>
       <c r="F18">
-        <v>1475.3</v>
+        <v>1513</v>
       </c>
       <c r="G18">
-        <v>0.7</v>
+        <v>0.52</v>
       </c>
       <c r="H18">
-        <v>5.35</v>
+        <v>-2.7</v>
       </c>
       <c r="I18">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J18" t="s">
         <v>71</v>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19">
-        <v>1610612753</v>
+        <v>1610612757</v>
       </c>
       <c r="B19" t="s">
         <v>28</v>
@@ -1231,22 +1231,22 @@
         <v>58</v>
       </c>
       <c r="D19">
-        <v>1.0032</v>
+        <v>0.9695</v>
       </c>
       <c r="E19">
-        <v>51.32</v>
+        <v>50.11</v>
       </c>
       <c r="F19">
-        <v>1518.6</v>
+        <v>1477</v>
       </c>
       <c r="G19">
-        <v>0.8</v>
+        <v>-0.91</v>
       </c>
       <c r="H19">
-        <v>0.27</v>
+        <v>4.28</v>
       </c>
       <c r="I19">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J19" t="s">
         <v>71</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20">
-        <v>1610612744</v>
+        <v>1610612755</v>
       </c>
       <c r="B20" t="s">
         <v>29</v>
@@ -1266,22 +1266,22 @@
         <v>59</v>
       </c>
       <c r="D20">
-        <v>0.9966</v>
+        <v>0.9597</v>
       </c>
       <c r="E20">
-        <v>51.07</v>
+        <v>49.61</v>
       </c>
       <c r="F20">
-        <v>1471.6</v>
+        <v>1475.6</v>
       </c>
       <c r="G20">
-        <v>-0.99</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H20">
-        <v>-5.81</v>
+        <v>1.85</v>
       </c>
       <c r="I20">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J20" t="s">
         <v>71</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21">
-        <v>1610612757</v>
+        <v>1610612744</v>
       </c>
       <c r="B21" t="s">
         <v>30</v>
@@ -1301,22 +1301,22 @@
         <v>60</v>
       </c>
       <c r="D21">
-        <v>0.9897</v>
+        <v>0.9587</v>
       </c>
       <c r="E21">
-        <v>50.61</v>
+        <v>49.65</v>
       </c>
       <c r="F21">
-        <v>1472.6</v>
+        <v>1471.6</v>
       </c>
       <c r="G21">
-        <v>-0.85</v>
+        <v>-0.99</v>
       </c>
       <c r="H21">
-        <v>10.8</v>
+        <v>-5.81</v>
       </c>
       <c r="I21">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J21" t="s">
         <v>71</v>
@@ -1336,10 +1336,10 @@
         <v>61</v>
       </c>
       <c r="D22">
-        <v>0.6613</v>
+        <v>0.6558</v>
       </c>
       <c r="E22">
-        <v>34.76</v>
+        <v>34.45</v>
       </c>
       <c r="F22">
         <v>1339.6</v>
@@ -1351,7 +1351,7 @@
         <v>0.59</v>
       </c>
       <c r="I22">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J22" t="s">
         <v>71</v>
@@ -1371,10 +1371,10 @@
         <v>62</v>
       </c>
       <c r="D23">
-        <v>0.6573</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="E23">
-        <v>34.81</v>
+        <v>34.32</v>
       </c>
       <c r="F23">
         <v>1371.5</v>
@@ -1386,7 +1386,7 @@
         <v>-12.12</v>
       </c>
       <c r="I23">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J23" t="s">
         <v>71</v>
@@ -1406,10 +1406,10 @@
         <v>63</v>
       </c>
       <c r="D24">
-        <v>0.6378</v>
+        <v>0.632</v>
       </c>
       <c r="E24">
-        <v>33.55</v>
+        <v>33.28</v>
       </c>
       <c r="F24">
         <v>1388.8</v>
@@ -1421,7 +1421,7 @@
         <v>-13.09</v>
       </c>
       <c r="I24">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J24" t="s">
         <v>71</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
@@ -1441,22 +1441,22 @@
         <v>64</v>
       </c>
       <c r="D25">
-        <v>0.6158</v>
+        <v>0.62</v>
       </c>
       <c r="E25">
-        <v>32.72</v>
+        <v>32.91</v>
       </c>
       <c r="F25">
-        <v>1362.8</v>
+        <v>1371.2</v>
       </c>
       <c r="G25">
-        <v>-5.24</v>
+        <v>-4.59</v>
       </c>
       <c r="H25">
-        <v>-5.8</v>
+        <v>-11.5</v>
       </c>
       <c r="I25">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J25" t="s">
         <v>71</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26">
-        <v>1610612740</v>
+        <v>1610612742</v>
       </c>
       <c r="B26" t="s">
         <v>35</v>
@@ -1476,22 +1476,22 @@
         <v>65</v>
       </c>
       <c r="D26">
-        <v>0.6098</v>
+        <v>0.6105</v>
       </c>
       <c r="E26">
-        <v>32.26</v>
+        <v>32.48</v>
       </c>
       <c r="F26">
-        <v>1371.2</v>
+        <v>1362.8</v>
       </c>
       <c r="G26">
-        <v>-4.59</v>
+        <v>-5.24</v>
       </c>
       <c r="H26">
-        <v>-11.5</v>
+        <v>-5.8</v>
       </c>
       <c r="I26">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J26" t="s">
         <v>71</v>
@@ -1502,7 +1502,7 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27">
-        <v>1610612763</v>
+        <v>1610612762</v>
       </c>
       <c r="B27" t="s">
         <v>36</v>
@@ -1511,22 +1511,22 @@
         <v>66</v>
       </c>
       <c r="D27">
-        <v>0.5931999999999999</v>
+        <v>0.5878</v>
       </c>
       <c r="E27">
-        <v>31.29</v>
+        <v>30.25</v>
       </c>
       <c r="F27">
-        <v>1363.7</v>
+        <v>1306.2</v>
       </c>
       <c r="G27">
-        <v>-6.83</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="H27">
-        <v>-19.87</v>
+        <v>-13.15</v>
       </c>
       <c r="I27">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J27" t="s">
         <v>71</v>
@@ -1537,7 +1537,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28">
-        <v>1610612762</v>
+        <v>1610612763</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
@@ -1546,22 +1546,22 @@
         <v>67</v>
       </c>
       <c r="D28">
-        <v>0.5928</v>
+        <v>0.5873</v>
       </c>
       <c r="E28">
-        <v>30.66</v>
+        <v>30.97</v>
       </c>
       <c r="F28">
-        <v>1306.2</v>
+        <v>1363.7</v>
       </c>
       <c r="G28">
-        <v>-8.449999999999999</v>
+        <v>-6.83</v>
       </c>
       <c r="H28">
-        <v>-13.15</v>
+        <v>-19.87</v>
       </c>
       <c r="I28">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J28" t="s">
         <v>71</v>
@@ -1581,10 +1581,10 @@
         <v>68</v>
       </c>
       <c r="D29">
-        <v>0.5429</v>
+        <v>0.5448</v>
       </c>
       <c r="E29">
-        <v>28.07</v>
+        <v>27.99</v>
       </c>
       <c r="F29">
         <v>1314.3</v>
@@ -1596,7 +1596,7 @@
         <v>-8.25</v>
       </c>
       <c r="I29">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J29" t="s">
         <v>71</v>
@@ -1616,10 +1616,10 @@
         <v>69</v>
       </c>
       <c r="D30">
-        <v>0.5279</v>
+        <v>0.5233</v>
       </c>
       <c r="E30">
-        <v>26.58</v>
+        <v>26.21</v>
       </c>
       <c r="F30">
         <v>1248.5</v>
@@ -1631,7 +1631,7 @@
         <v>-14.92</v>
       </c>
       <c r="I30">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J30" t="s">
         <v>71</v>
@@ -1651,10 +1651,10 @@
         <v>70</v>
       </c>
       <c r="D31">
-        <v>0.5031</v>
+        <v>0.5023</v>
       </c>
       <c r="E31">
-        <v>25.53</v>
+        <v>25.39</v>
       </c>
       <c r="F31">
         <v>1286.6</v>
@@ -1666,7 +1666,7 @@
         <v>-14.6</v>
       </c>
       <c r="I31">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J31" t="s">
         <v>71</v>

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -61,12 +61,12 @@
     <t>Denver Nuggets</t>
   </si>
   <si>
+    <t>Cleveland Cavaliers</t>
+  </si>
+  <si>
     <t>Detroit Pistons</t>
   </si>
   <si>
-    <t>Cleveland Cavaliers</t>
-  </si>
-  <si>
     <t>New York Knicks</t>
   </si>
   <si>
@@ -103,18 +103,18 @@
     <t>Portland Trail Blazers</t>
   </si>
   <si>
+    <t>Golden State Warriors</t>
+  </si>
+  <si>
     <t>Philadelphia 76ers</t>
   </si>
   <si>
-    <t>Golden State Warriors</t>
+    <t>Chicago Bulls</t>
   </si>
   <si>
     <t>Indiana Pacers</t>
   </si>
   <si>
-    <t>Chicago Bulls</t>
-  </si>
-  <si>
     <t>Milwaukee Bucks</t>
   </si>
   <si>
@@ -151,12 +151,12 @@
     <t>DEN</t>
   </si>
   <si>
+    <t>CLE</t>
+  </si>
+  <si>
     <t>DET</t>
   </si>
   <si>
-    <t>CLE</t>
-  </si>
-  <si>
     <t>NYK</t>
   </si>
   <si>
@@ -193,18 +193,18 @@
     <t>POR</t>
   </si>
   <si>
+    <t>GSW</t>
+  </si>
+  <si>
     <t>PHI</t>
   </si>
   <si>
-    <t>GSW</t>
+    <t>CHI</t>
   </si>
   <si>
     <t>IND</t>
   </si>
   <si>
-    <t>CHI</t>
-  </si>
-  <si>
     <t>MIL</t>
   </si>
   <si>
@@ -229,7 +229,7 @@
     <t>BKN</t>
   </si>
   <si>
-    <t>2026-04-22</t>
+    <t>2026-04-23</t>
   </si>
 </sst>
 </file>
@@ -636,22 +636,22 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>1.576</v>
+        <v>1.582</v>
       </c>
       <c r="E2">
-        <v>73.59</v>
+        <v>73.83</v>
       </c>
       <c r="F2">
-        <v>1749.1</v>
+        <v>1755.5</v>
       </c>
       <c r="G2">
-        <v>12.19</v>
+        <v>11.76</v>
       </c>
       <c r="H2">
-        <v>14.13</v>
+        <v>15.42</v>
       </c>
       <c r="I2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J2" t="s">
         <v>71</v>
@@ -671,22 +671,22 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>1.5056</v>
+        <v>1.5081</v>
       </c>
       <c r="E3">
-        <v>71.67</v>
+        <v>71.77</v>
       </c>
       <c r="F3">
         <v>1680.2</v>
       </c>
       <c r="G3">
-        <v>7.28</v>
+        <v>7.34</v>
       </c>
       <c r="H3">
         <v>11.91</v>
       </c>
       <c r="I3">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J3" t="s">
         <v>71</v>
@@ -706,10 +706,10 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>1.4824</v>
+        <v>1.482</v>
       </c>
       <c r="E4">
-        <v>70.31999999999999</v>
+        <v>70.37</v>
       </c>
       <c r="F4">
         <v>1737.4</v>
@@ -721,7 +721,7 @@
         <v>10.02</v>
       </c>
       <c r="I4">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J4" t="s">
         <v>71</v>
@@ -741,7 +741,7 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>1.4007</v>
+        <v>1.4001</v>
       </c>
       <c r="E5">
         <v>67.44</v>
@@ -756,7 +756,7 @@
         <v>8.18</v>
       </c>
       <c r="I5">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J5" t="s">
         <v>71</v>
@@ -767,7 +767,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6">
-        <v>1610612765</v>
+        <v>1610612739</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
@@ -776,22 +776,22 @@
         <v>45</v>
       </c>
       <c r="D6">
-        <v>1.3999</v>
+        <v>1.3933</v>
       </c>
       <c r="E6">
-        <v>67.09</v>
+        <v>67.33</v>
       </c>
       <c r="F6">
-        <v>1688.7</v>
+        <v>1642.1</v>
       </c>
       <c r="G6">
-        <v>7.19</v>
+        <v>4.44</v>
       </c>
       <c r="H6">
-        <v>11.64</v>
+        <v>5.69</v>
       </c>
       <c r="I6">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J6" t="s">
         <v>71</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7">
-        <v>1610612739</v>
+        <v>1610612765</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
@@ -811,22 +811,22 @@
         <v>46</v>
       </c>
       <c r="D7">
-        <v>1.3897</v>
+        <v>1.3888</v>
       </c>
       <c r="E7">
-        <v>67.20999999999999</v>
+        <v>66.58</v>
       </c>
       <c r="F7">
-        <v>1642.1</v>
+        <v>1675</v>
       </c>
       <c r="G7">
-        <v>4.43</v>
+        <v>7.65</v>
       </c>
       <c r="H7">
-        <v>5.69</v>
+        <v>11.2</v>
       </c>
       <c r="I7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J7" t="s">
         <v>71</v>
@@ -846,22 +846,22 @@
         <v>47</v>
       </c>
       <c r="D8">
-        <v>1.382</v>
+        <v>1.3833</v>
       </c>
       <c r="E8">
-        <v>66.91</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="F8">
         <v>1657.3</v>
       </c>
       <c r="G8">
-        <v>6.55</v>
+        <v>6.57</v>
       </c>
       <c r="H8">
         <v>3.19</v>
       </c>
       <c r="I8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J8" t="s">
         <v>71</v>
@@ -881,10 +881,10 @@
         <v>48</v>
       </c>
       <c r="D9">
-        <v>1.2452</v>
+        <v>1.2476</v>
       </c>
       <c r="E9">
-        <v>61.55</v>
+        <v>61.62</v>
       </c>
       <c r="F9">
         <v>1587</v>
@@ -896,7 +896,7 @@
         <v>10.52</v>
       </c>
       <c r="I9">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J9" t="s">
         <v>71</v>
@@ -916,10 +916,10 @@
         <v>49</v>
       </c>
       <c r="D10">
-        <v>1.1813</v>
+        <v>1.183</v>
       </c>
       <c r="E10">
-        <v>58.84</v>
+        <v>58.96</v>
       </c>
       <c r="F10">
         <v>1565.3</v>
@@ -931,7 +931,7 @@
         <v>-1.83</v>
       </c>
       <c r="I10">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J10" t="s">
         <v>71</v>
@@ -951,10 +951,10 @@
         <v>50</v>
       </c>
       <c r="D11">
-        <v>1.1723</v>
+        <v>1.1705</v>
       </c>
       <c r="E11">
-        <v>58.46</v>
+        <v>58.45</v>
       </c>
       <c r="F11">
         <v>1595.9</v>
@@ -966,7 +966,7 @@
         <v>-0.17</v>
       </c>
       <c r="I11">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J11" t="s">
         <v>71</v>
@@ -986,22 +986,22 @@
         <v>51</v>
       </c>
       <c r="D12">
-        <v>1.1277</v>
+        <v>1.1299</v>
       </c>
       <c r="E12">
-        <v>56.82</v>
+        <v>56.91</v>
       </c>
       <c r="F12">
         <v>1526</v>
       </c>
       <c r="G12">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="H12">
         <v>4.49</v>
       </c>
       <c r="I12">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J12" t="s">
         <v>71</v>
@@ -1021,22 +1021,22 @@
         <v>52</v>
       </c>
       <c r="D13">
-        <v>1.1151</v>
+        <v>1.1168</v>
       </c>
       <c r="E13">
-        <v>56.23</v>
+        <v>56.31</v>
       </c>
       <c r="F13">
         <v>1515.6</v>
       </c>
       <c r="G13">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="H13">
         <v>7.11</v>
       </c>
       <c r="I13">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J13" t="s">
         <v>71</v>
@@ -1056,10 +1056,10 @@
         <v>53</v>
       </c>
       <c r="D14">
-        <v>1.1022</v>
+        <v>1.1002</v>
       </c>
       <c r="E14">
-        <v>55.57</v>
+        <v>55.51</v>
       </c>
       <c r="F14">
         <v>1570.6</v>
@@ -1071,7 +1071,7 @@
         <v>7.93</v>
       </c>
       <c r="I14">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J14" t="s">
         <v>71</v>
@@ -1091,7 +1091,7 @@
         <v>54</v>
       </c>
       <c r="D15">
-        <v>1.0979</v>
+        <v>1.0983</v>
       </c>
       <c r="E15">
         <v>55.66</v>
@@ -1106,7 +1106,7 @@
         <v>1.77</v>
       </c>
       <c r="I15">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J15" t="s">
         <v>71</v>
@@ -1126,22 +1126,22 @@
         <v>55</v>
       </c>
       <c r="D16">
-        <v>1.0212</v>
+        <v>1.0127</v>
       </c>
       <c r="E16">
-        <v>52.14</v>
+        <v>51.91</v>
       </c>
       <c r="F16">
-        <v>1535.8</v>
+        <v>1549.6</v>
       </c>
       <c r="G16">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="H16">
-        <v>5.82</v>
+        <v>4.13</v>
       </c>
       <c r="I16">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J16" t="s">
         <v>71</v>
@@ -1161,10 +1161,10 @@
         <v>56</v>
       </c>
       <c r="D17">
-        <v>1.0048</v>
+        <v>1.0025</v>
       </c>
       <c r="E17">
-        <v>51.6</v>
+        <v>51.48</v>
       </c>
       <c r="F17">
         <v>1527.6</v>
@@ -1176,7 +1176,7 @@
         <v>0.27</v>
       </c>
       <c r="I17">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J17" t="s">
         <v>71</v>
@@ -1196,22 +1196,22 @@
         <v>57</v>
       </c>
       <c r="D18">
-        <v>0.9956</v>
+        <v>0.9745</v>
       </c>
       <c r="E18">
-        <v>51.3</v>
+        <v>50.43</v>
       </c>
       <c r="F18">
-        <v>1513</v>
+        <v>1506.7</v>
       </c>
       <c r="G18">
-        <v>0.52</v>
+        <v>0.67</v>
       </c>
       <c r="H18">
-        <v>-2.7</v>
+        <v>-5.68</v>
       </c>
       <c r="I18">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J18" t="s">
         <v>71</v>
@@ -1231,10 +1231,10 @@
         <v>58</v>
       </c>
       <c r="D19">
-        <v>0.9695</v>
+        <v>0.9694</v>
       </c>
       <c r="E19">
-        <v>50.11</v>
+        <v>50.08</v>
       </c>
       <c r="F19">
         <v>1477</v>
@@ -1246,7 +1246,7 @@
         <v>4.28</v>
       </c>
       <c r="I19">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J19" t="s">
         <v>71</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20">
-        <v>1610612755</v>
+        <v>1610612744</v>
       </c>
       <c r="B20" t="s">
         <v>29</v>
@@ -1266,22 +1266,22 @@
         <v>59</v>
       </c>
       <c r="D20">
-        <v>0.9597</v>
+        <v>0.9607</v>
       </c>
       <c r="E20">
-        <v>49.61</v>
+        <v>49.71</v>
       </c>
       <c r="F20">
-        <v>1475.6</v>
+        <v>1471.6</v>
       </c>
       <c r="G20">
-        <v>0.5600000000000001</v>
+        <v>-0.99</v>
       </c>
       <c r="H20">
-        <v>1.85</v>
+        <v>-5.81</v>
       </c>
       <c r="I20">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J20" t="s">
         <v>71</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21">
-        <v>1610612744</v>
+        <v>1610612755</v>
       </c>
       <c r="B21" t="s">
         <v>30</v>
@@ -1301,22 +1301,22 @@
         <v>60</v>
       </c>
       <c r="D21">
-        <v>0.9587</v>
+        <v>0.9589</v>
       </c>
       <c r="E21">
-        <v>49.65</v>
+        <v>49.59</v>
       </c>
       <c r="F21">
-        <v>1471.6</v>
+        <v>1475.6</v>
       </c>
       <c r="G21">
-        <v>-0.99</v>
+        <v>0.55</v>
       </c>
       <c r="H21">
-        <v>-5.81</v>
+        <v>1.85</v>
       </c>
       <c r="I21">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J21" t="s">
         <v>71</v>
@@ -1327,7 +1327,7 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
-        <v>1610612754</v>
+        <v>1610612741</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
@@ -1336,22 +1336,22 @@
         <v>61</v>
       </c>
       <c r="D22">
-        <v>0.6558</v>
+        <v>0.6812</v>
       </c>
       <c r="E22">
-        <v>34.45</v>
+        <v>35.96</v>
       </c>
       <c r="F22">
-        <v>1339.6</v>
+        <v>1371.5</v>
       </c>
       <c r="G22">
-        <v>-7.43</v>
+        <v>-4.88</v>
       </c>
       <c r="H22">
-        <v>0.59</v>
+        <v>-12.12</v>
       </c>
       <c r="I22">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J22" t="s">
         <v>71</v>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23">
-        <v>1610612741</v>
+        <v>1610612754</v>
       </c>
       <c r="B23" t="s">
         <v>32</v>
@@ -1371,22 +1371,22 @@
         <v>62</v>
       </c>
       <c r="D23">
-        <v>0.6487000000000001</v>
+        <v>0.6544</v>
       </c>
       <c r="E23">
-        <v>34.32</v>
+        <v>34.31</v>
       </c>
       <c r="F23">
-        <v>1371.5</v>
+        <v>1339.6</v>
       </c>
       <c r="G23">
-        <v>-4.88</v>
+        <v>-7.43</v>
       </c>
       <c r="H23">
-        <v>-12.12</v>
+        <v>0.59</v>
       </c>
       <c r="I23">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J23" t="s">
         <v>71</v>
@@ -1406,10 +1406,10 @@
         <v>63</v>
       </c>
       <c r="D24">
-        <v>0.632</v>
+        <v>0.6312</v>
       </c>
       <c r="E24">
-        <v>33.28</v>
+        <v>33.2</v>
       </c>
       <c r="F24">
         <v>1388.8</v>
@@ -1421,7 +1421,7 @@
         <v>-13.09</v>
       </c>
       <c r="I24">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J24" t="s">
         <v>71</v>
@@ -1441,10 +1441,10 @@
         <v>64</v>
       </c>
       <c r="D25">
-        <v>0.62</v>
+        <v>0.6196</v>
       </c>
       <c r="E25">
-        <v>32.91</v>
+        <v>32.84</v>
       </c>
       <c r="F25">
         <v>1371.2</v>
@@ -1456,7 +1456,7 @@
         <v>-11.5</v>
       </c>
       <c r="I25">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J25" t="s">
         <v>71</v>
@@ -1476,10 +1476,10 @@
         <v>65</v>
       </c>
       <c r="D26">
-        <v>0.6105</v>
+        <v>0.6103</v>
       </c>
       <c r="E26">
-        <v>32.48</v>
+        <v>32.43</v>
       </c>
       <c r="F26">
         <v>1362.8</v>
@@ -1491,7 +1491,7 @@
         <v>-5.8</v>
       </c>
       <c r="I26">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J26" t="s">
         <v>71</v>
@@ -1511,10 +1511,10 @@
         <v>66</v>
       </c>
       <c r="D27">
-        <v>0.5878</v>
+        <v>0.5875</v>
       </c>
       <c r="E27">
-        <v>30.25</v>
+        <v>30.2</v>
       </c>
       <c r="F27">
         <v>1306.2</v>
@@ -1526,7 +1526,7 @@
         <v>-13.15</v>
       </c>
       <c r="I27">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J27" t="s">
         <v>71</v>
@@ -1546,10 +1546,10 @@
         <v>67</v>
       </c>
       <c r="D28">
-        <v>0.5873</v>
+        <v>0.5865</v>
       </c>
       <c r="E28">
-        <v>30.97</v>
+        <v>30.87</v>
       </c>
       <c r="F28">
         <v>1363.7</v>
@@ -1561,7 +1561,7 @@
         <v>-19.87</v>
       </c>
       <c r="I28">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J28" t="s">
         <v>71</v>
@@ -1581,10 +1581,10 @@
         <v>68</v>
       </c>
       <c r="D29">
-        <v>0.5448</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="E29">
-        <v>27.99</v>
+        <v>27.85</v>
       </c>
       <c r="F29">
         <v>1314.3</v>
@@ -1596,7 +1596,7 @@
         <v>-8.25</v>
       </c>
       <c r="I29">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J29" t="s">
         <v>71</v>
@@ -1616,10 +1616,10 @@
         <v>69</v>
       </c>
       <c r="D30">
-        <v>0.5233</v>
+        <v>0.5214</v>
       </c>
       <c r="E30">
-        <v>26.21</v>
+        <v>26.1</v>
       </c>
       <c r="F30">
         <v>1248.5</v>
@@ -1631,7 +1631,7 @@
         <v>-14.92</v>
       </c>
       <c r="I30">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J30" t="s">
         <v>71</v>
@@ -1651,10 +1651,10 @@
         <v>70</v>
       </c>
       <c r="D31">
-        <v>0.5023</v>
+        <v>0.5024</v>
       </c>
       <c r="E31">
-        <v>25.39</v>
+        <v>25.35</v>
       </c>
       <c r="F31">
         <v>1286.6</v>
@@ -1666,7 +1666,7 @@
         <v>-14.6</v>
       </c>
       <c r="I31">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J31" t="s">
         <v>71</v>

--- a/nba/public/data/nba_rankings.xlsx
+++ b/nba/public/data/nba_rankings.xlsx
@@ -52,22 +52,25 @@
     <t>Oklahoma City Thunder</t>
   </si>
   <si>
+    <t>San Antonio Spurs</t>
+  </si>
+  <si>
     <t>Boston Celtics</t>
   </si>
   <si>
-    <t>San Antonio Spurs</t>
+    <t>New York Knicks</t>
+  </si>
+  <si>
+    <t>Cleveland Cavaliers</t>
+  </si>
+  <si>
+    <t>Detroit Pistons</t>
   </si>
   <si>
     <t>Denver Nuggets</t>
   </si>
   <si>
-    <t>Cleveland Cavaliers</t>
-  </si>
-  <si>
-    <t>Detroit Pistons</t>
-  </si>
-  <si>
-    <t>New York Knicks</t>
+    <t>Charlotte Hornets</t>
   </si>
   <si>
     <t>Houston Rockets</t>
@@ -76,39 +79,36 @@
     <t>Minnesota Timberwolves</t>
   </si>
   <si>
-    <t>Charlotte Hornets</t>
+    <t>Los Angeles Lakers</t>
+  </si>
+  <si>
+    <t>Toronto Raptors</t>
   </si>
   <si>
     <t>Atlanta Hawks</t>
   </si>
   <si>
-    <t>Toronto Raptors</t>
-  </si>
-  <si>
-    <t>Los Angeles Lakers</t>
-  </si>
-  <si>
     <t>LA Clippers</t>
   </si>
   <si>
     <t>Orlando Magic</t>
   </si>
   <si>
+    <t>Philadelphia 76ers</t>
+  </si>
+  <si>
     <t>Miami Heat</t>
   </si>
   <si>
+    <t>Golden State Warriors</t>
+  </si>
+  <si>
     <t>Phoenix Suns</t>
   </si>
   <si>
     <t>Portland Trail Blazers</t>
   </si>
   <si>
-    <t>Golden State Warriors</t>
-  </si>
-  <si>
-    <t>Philadelphia 76ers</t>
-  </si>
-  <si>
     <t>Chicago Bulls</t>
   </si>
   <si>
@@ -124,12 +124,12 @@
     <t>Dallas Mavericks</t>
   </si>
   <si>
+    <t>Memphis Grizzlies</t>
+  </si>
+  <si>
     <t>Utah Jazz</t>
   </si>
   <si>
-    <t>Memphis Grizzlies</t>
-  </si>
-  <si>
     <t>Sacramento Kings</t>
   </si>
   <si>
@@ -142,22 +142,25 @@
     <t>OKC</t>
   </si>
   <si>
+    <t>SAS</t>
+  </si>
+  <si>
     <t>BOS</t>
   </si>
   <si>
-    <t>SAS</t>
+    <t>NYK</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t>DET</t>
   </si>
   <si>
     <t>DEN</t>
   </si>
   <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>NYK</t>
+    <t>CHA</t>
   </si>
   <si>
     <t>HOU</t>
@@ -166,39 +169,36 @@
     <t>MIN</t>
   </si>
   <si>
-    <t>CHA</t>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>TOR</t>
   </si>
   <si>
     <t>ATL</t>
   </si>
   <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>LAL</t>
-  </si>
-  <si>
     <t>LAC</t>
   </si>
   <si>
     <t>ORL</t>
   </si>
   <si>
+    <t>PHI</t>
+  </si>
+  <si>
     <t>MIA</t>
   </si>
   <si>
+    <t>GSW</t>
+  </si>
+  <si>
     <t>PHX</t>
   </si>
   <si>
     <t>POR</t>
   </si>
   <si>
-    <t>GSW</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
     <t>CHI</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>DAL</t>
   </si>
   <si>
+    <t>MEM</t>
+  </si>
+  <si>
     <t>UTA</t>
   </si>
   <si>
-    <t>MEM</t>
-  </si>
-  <si>
     <t>SAC</t>
   </si>
   <si>
@@ -229,7 +229,7 @@
     <t>BKN</t>
   </si>
   <si>
-    <t>2026-04-23</t>
+    <t>2026-04-30</t>
   </si>
 </sst>
 </file>
@@ -636,22 +636,22 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>1.582</v>
+        <v>1.5812</v>
       </c>
       <c r="E2">
-        <v>73.83</v>
+        <v>73.92</v>
       </c>
       <c r="F2">
-        <v>1755.5</v>
+        <v>1763.4</v>
       </c>
       <c r="G2">
-        <v>11.76</v>
+        <v>11.7</v>
       </c>
       <c r="H2">
-        <v>15.42</v>
+        <v>14.8</v>
       </c>
       <c r="I2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J2" t="s">
         <v>71</v>
@@ -662,7 +662,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3">
-        <v>1610612738</v>
+        <v>1610612759</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -671,22 +671,22 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>1.5081</v>
+        <v>1.528</v>
       </c>
       <c r="E3">
-        <v>71.77</v>
+        <v>72.28</v>
       </c>
       <c r="F3">
-        <v>1680.2</v>
+        <v>1737.2</v>
       </c>
       <c r="G3">
-        <v>7.34</v>
+        <v>8.99</v>
       </c>
       <c r="H3">
-        <v>11.91</v>
+        <v>10.76</v>
       </c>
       <c r="I3">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J3" t="s">
         <v>71</v>
@@ -697,7 +697,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4">
-        <v>1610612759</v>
+        <v>1610612738</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -706,22 +706,22 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>1.482</v>
+        <v>1.5158</v>
       </c>
       <c r="E4">
-        <v>70.37</v>
+        <v>72.08</v>
       </c>
       <c r="F4">
-        <v>1737.4</v>
+        <v>1680.6</v>
       </c>
       <c r="G4">
-        <v>8.210000000000001</v>
+        <v>7.22</v>
       </c>
       <c r="H4">
-        <v>10.02</v>
+        <v>10.78</v>
       </c>
       <c r="I4">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J4" t="s">
         <v>71</v>
@@ -732,7 +732,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5">
-        <v>1610612743</v>
+        <v>1610612752</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -741,22 +741,22 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>1.4001</v>
+        <v>1.4386</v>
       </c>
       <c r="E5">
-        <v>67.44</v>
+        <v>69.12</v>
       </c>
       <c r="F5">
-        <v>1628.8</v>
+        <v>1648.8</v>
       </c>
       <c r="G5">
-        <v>4.83</v>
+        <v>7.29</v>
       </c>
       <c r="H5">
-        <v>8.18</v>
+        <v>12.06</v>
       </c>
       <c r="I5">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J5" t="s">
         <v>71</v>
@@ -776,22 +776,22 @@
         <v>45</v>
       </c>
       <c r="D6">
-        <v>1.3933</v>
+        <v>1.3671</v>
       </c>
       <c r="E6">
-        <v>67.33</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="F6">
-        <v>1642.1</v>
+        <v>1621.6</v>
       </c>
       <c r="G6">
-        <v>4.44</v>
+        <v>4.03</v>
       </c>
       <c r="H6">
-        <v>5.69</v>
+        <v>3.72</v>
       </c>
       <c r="I6">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J6" t="s">
         <v>71</v>
@@ -811,22 +811,22 @@
         <v>46</v>
       </c>
       <c r="D7">
-        <v>1.3888</v>
+        <v>1.3583</v>
       </c>
       <c r="E7">
-        <v>66.58</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="F7">
-        <v>1675</v>
+        <v>1663</v>
       </c>
       <c r="G7">
-        <v>7.65</v>
+        <v>7.41</v>
       </c>
       <c r="H7">
-        <v>11.2</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I7">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J7" t="s">
         <v>71</v>
@@ -837,7 +837,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8">
-        <v>1610612752</v>
+        <v>1610612743</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -846,22 +846,22 @@
         <v>47</v>
       </c>
       <c r="D8">
-        <v>1.3833</v>
+        <v>1.3443</v>
       </c>
       <c r="E8">
-        <v>66.95999999999999</v>
+        <v>65.33</v>
       </c>
       <c r="F8">
-        <v>1657.3</v>
+        <v>1597.7</v>
       </c>
       <c r="G8">
-        <v>6.57</v>
+        <v>4.61</v>
       </c>
       <c r="H8">
-        <v>3.19</v>
+        <v>3.71</v>
       </c>
       <c r="I8">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J8" t="s">
         <v>71</v>
@@ -872,7 +872,7 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9">
-        <v>1610612745</v>
+        <v>1610612766</v>
       </c>
       <c r="B9" t="s">
         <v>18</v>
@@ -881,22 +881,22 @@
         <v>48</v>
       </c>
       <c r="D9">
-        <v>1.2476</v>
+        <v>1.1884</v>
       </c>
       <c r="E9">
-        <v>61.62</v>
+        <v>59.24</v>
       </c>
       <c r="F9">
-        <v>1587</v>
+        <v>1595.9</v>
       </c>
       <c r="G9">
-        <v>4.22</v>
+        <v>2.7</v>
       </c>
       <c r="H9">
-        <v>10.52</v>
+        <v>-0.17</v>
       </c>
       <c r="I9">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J9" t="s">
         <v>71</v>
@@ -907,7 +907,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
@@ -916,22 +916,22 @@
         <v>49</v>
       </c>
       <c r="D10">
-        <v>1.183</v>
+        <v>1.1485</v>
       </c>
       <c r="E10">
-        <v>58.96</v>
+        <v>57.64</v>
       </c>
       <c r="F10">
-        <v>1565.3</v>
+        <v>1583.4</v>
       </c>
       <c r="G10">
-        <v>3.52</v>
+        <v>4.66</v>
       </c>
       <c r="H10">
-        <v>-1.83</v>
+        <v>6.24</v>
       </c>
       <c r="I10">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J10" t="s">
         <v>71</v>
@@ -942,7 +942,7 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11">
-        <v>1610612766</v>
+        <v>1610612750</v>
       </c>
       <c r="B11" t="s">
         <v>20</v>
@@ -951,22 +951,22 @@
         <v>50</v>
       </c>
       <c r="D11">
-        <v>1.1705</v>
+        <v>1.1455</v>
       </c>
       <c r="E11">
-        <v>58.45</v>
+        <v>57.49</v>
       </c>
       <c r="F11">
-        <v>1595.9</v>
+        <v>1596.5</v>
       </c>
       <c r="G11">
-        <v>2.43</v>
+        <v>3.5</v>
       </c>
       <c r="H11">
-        <v>-0.17</v>
+        <v>0.63</v>
       </c>
       <c r="I11">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J11" t="s">
         <v>71</v>
@@ -977,7 +977,7 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12">
-        <v>1610612737</v>
+        <v>1610612747</v>
       </c>
       <c r="B12" t="s">
         <v>21</v>
@@ -986,22 +986,22 @@
         <v>51</v>
       </c>
       <c r="D12">
-        <v>1.1299</v>
+        <v>1.1372</v>
       </c>
       <c r="E12">
-        <v>56.91</v>
+        <v>57.21</v>
       </c>
       <c r="F12">
-        <v>1526</v>
+        <v>1574.2</v>
       </c>
       <c r="G12">
-        <v>2.01</v>
+        <v>2.37</v>
       </c>
       <c r="H12">
-        <v>4.49</v>
+        <v>-0.28</v>
       </c>
       <c r="I12">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J12" t="s">
         <v>71</v>
@@ -1021,22 +1021,22 @@
         <v>52</v>
       </c>
       <c r="D13">
-        <v>1.1168</v>
+        <v>1.1359</v>
       </c>
       <c r="E13">
-        <v>56.31</v>
+        <v>57.15</v>
       </c>
       <c r="F13">
-        <v>1515.6</v>
+        <v>1536.1</v>
       </c>
       <c r="G13">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="H13">
-        <v>7.11</v>
+        <v>6.03</v>
       </c>
       <c r="I13">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J13" t="s">
         <v>71</v>
@@ -1047,7 +1047,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14">
-        <v>1610612747</v>
+        <v>1610612737</v>
       </c>
       <c r="B14" t="s">
         <v>23</v>
@@ -1056,22 +1056,22 @@
         <v>53</v>
       </c>
       <c r="D14">
-        <v>1.1002</v>
+        <v>1.1138</v>
       </c>
       <c r="E14">
-        <v>55.51</v>
+        <v>56.1</v>
       </c>
       <c r="F14">
-        <v>1570.6</v>
+        <v>1534.5</v>
       </c>
       <c r="G14">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="H14">
-        <v>7.93</v>
+        <v>-1.32</v>
       </c>
       <c r="I14">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J14" t="s">
         <v>71</v>
@@ -1091,10 +1091,10 @@
         <v>54</v>
       </c>
       <c r="D15">
-        <v>1.0983</v>
+        <v>1.1127</v>
       </c>
       <c r="E15">
-        <v>55.66</v>
+        <v>56.32</v>
       </c>
       <c r="F15">
         <v>1547.6</v>
@@ -1106,7 +1106,7 @@
         <v>1.77</v>
       </c>
       <c r="I15">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J15" t="s">
         <v>71</v>
@@ -1126,22 +1126,22 @@
         <v>55</v>
       </c>
       <c r="D16">
-        <v>1.0127</v>
+        <v>1.0298</v>
       </c>
       <c r="E16">
-        <v>51.91</v>
+        <v>52.45</v>
       </c>
       <c r="F16">
-        <v>1549.6</v>
+        <v>1561.5</v>
       </c>
       <c r="G16">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="H16">
-        <v>4.13</v>
+        <v>5.36</v>
       </c>
       <c r="I16">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J16" t="s">
         <v>71</v>
@@ -1152,7 +1152,7 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>1610612748</v>
+        <v>1610612755</v>
       </c>
       <c r="B17" t="s">
         <v>26</v>
@@ -1161,22 +1161,22 @@
         <v>56</v>
       </c>
       <c r="D17">
-        <v>1.0025</v>
+        <v>1.0215</v>
       </c>
       <c r="E17">
-        <v>51.48</v>
+        <v>52.22</v>
       </c>
       <c r="F17">
-        <v>1527.6</v>
+        <v>1475.3</v>
       </c>
       <c r="G17">
-        <v>2.05</v>
+        <v>0.42</v>
       </c>
       <c r="H17">
-        <v>0.27</v>
+        <v>-2.19</v>
       </c>
       <c r="I17">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J17" t="s">
         <v>71</v>
@@ -1187,7 +1187,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>1610612756</v>
+        <v>1610612748</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -1196,22 +1196,22 @@
         <v>57</v>
       </c>
       <c r="D18">
-        <v>0.9745</v>
+        <v>0.998</v>
       </c>
       <c r="E18">
-        <v>50.43</v>
+        <v>51.17</v>
       </c>
       <c r="F18">
-        <v>1506.7</v>
+        <v>1527.6</v>
       </c>
       <c r="G18">
-        <v>0.67</v>
+        <v>2.05</v>
       </c>
       <c r="H18">
-        <v>-5.68</v>
+        <v>0.27</v>
       </c>
       <c r="I18">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J18" t="s">
         <v>71</v>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19">
-        <v>1610612757</v>
+        <v>1610612744</v>
       </c>
       <c r="B19" t="s">
         <v>28</v>
@@ -1231,22 +1231,22 @@
         <v>58</v>
       </c>
       <c r="D19">
-        <v>0.9694</v>
+        <v>0.9816</v>
       </c>
       <c r="E19">
-        <v>50.08</v>
+        <v>50.56</v>
       </c>
       <c r="F19">
-        <v>1477</v>
+        <v>1471.6</v>
       </c>
       <c r="G19">
-        <v>-0.91</v>
+        <v>-0.93</v>
       </c>
       <c r="H19">
-        <v>4.28</v>
+        <v>-5.81</v>
       </c>
       <c r="I19">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J19" t="s">
         <v>71</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20">
-        <v>1610612744</v>
+        <v>1610612756</v>
       </c>
       <c r="B20" t="s">
         <v>29</v>
@@ -1266,22 +1266,22 @@
         <v>59</v>
       </c>
       <c r="D20">
-        <v>0.9607</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="E20">
         <v>49.71</v>
       </c>
       <c r="F20">
-        <v>1471.6</v>
+        <v>1498.7</v>
       </c>
       <c r="G20">
-        <v>-0.99</v>
+        <v>0.42</v>
       </c>
       <c r="H20">
-        <v>-5.81</v>
+        <v>-5.56</v>
       </c>
       <c r="I20">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J20" t="s">
         <v>71</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21">
-        <v>1610612755</v>
+        <v>1610612757</v>
       </c>
       <c r="B21" t="s">
         <v>30</v>
@@ -1301,22 +1301,22 @@
         <v>60</v>
       </c>
       <c r="D21">
-        <v>0.9589</v>
+        <v>0.8812</v>
       </c>
       <c r="E21">
-        <v>49.59</v>
+        <v>46.22</v>
       </c>
       <c r="F21">
-        <v>1475.6</v>
+        <v>1477.3</v>
       </c>
       <c r="G21">
-        <v>0.55</v>
+        <v>-1.97</v>
       </c>
       <c r="H21">
-        <v>1.85</v>
+        <v>-4.54</v>
       </c>
       <c r="I21">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J21" t="s">
         <v>71</v>
@@ -1336,10 +1336,10 @@
         <v>61</v>
       </c>
       <c r="D22">
-        <v>0.6812</v>
+        <v>0.6903</v>
       </c>
       <c r="E22">
-        <v>35.96</v>
+        <v>36.31</v>
       </c>
       <c r="F22">
         <v>1371.5</v>
@@ -1351,7 +1351,7 @@
         <v>-12.12</v>
       </c>
       <c r="I22">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J22" t="s">
         <v>71</v>
@@ -1371,10 +1371,10 @@
         <v>62</v>
       </c>
       <c r="D23">
-        <v>0.6544</v>
+        <v>0.6619</v>
       </c>
       <c r="E23">
-        <v>34.31</v>
+        <v>34.65</v>
       </c>
       <c r="F23">
         <v>1339.6</v>
@@ -1386,7 +1386,7 @@
         <v>0.59</v>
       </c>
       <c r="I23">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J23" t="s">
         <v>71</v>
@@ -1406,10 +1406,10 @@
         <v>63</v>
       </c>
       <c r="D24">
-        <v>0.6312</v>
+        <v>0.6391</v>
       </c>
       <c r="E24">
-        <v>33.2</v>
+        <v>33.44</v>
       </c>
       <c r="F24">
         <v>1388.8</v>
@@ -1421,7 +1421,7 @@
         <v>-13.09</v>
       </c>
       <c r="I24">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J24" t="s">
         <v>71</v>
@@ -1441,10 +1441,10 @@
         <v>64</v>
       </c>
       <c r="D25">
-        <v>0.6196</v>
+        <v>0.628</v>
       </c>
       <c r="E25">
-        <v>32.84</v>
+        <v>33.15</v>
       </c>
       <c r="F25">
         <v>1371.2</v>
@@ -1456,7 +1456,7 @@
         <v>-11.5</v>
       </c>
       <c r="I25">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J25" t="s">
         <v>71</v>
@@ -1476,10 +1476,10 @@
         <v>65</v>
       </c>
       <c r="D26">
-        <v>0.6103</v>
+        <v>0.62</v>
       </c>
       <c r="E26">
-        <v>32.43</v>
+        <v>32.78</v>
       </c>
       <c r="F26">
         <v>1362.8</v>
@@ -1491,7 +1491,7 @@
         <v>-5.8</v>
       </c>
       <c r="I26">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J26" t="s">
         <v>71</v>
@@ -1502,7 +1502,7 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27">
-        <v>1610612762</v>
+        <v>1610612763</v>
       </c>
       <c r="B27" t="s">
         <v>36</v>
@@ -1511,22 +1511,22 @@
         <v>66</v>
       </c>
       <c r="D27">
-        <v>0.5875</v>
+        <v>0.5944</v>
       </c>
       <c r="E27">
-        <v>30.2</v>
+        <v>31.14</v>
       </c>
       <c r="F27">
-        <v>1306.2</v>
+        <v>1363.7</v>
       </c>
       <c r="G27">
-        <v>-8.449999999999999</v>
+        <v>-6.83</v>
       </c>
       <c r="H27">
-        <v>-13.15</v>
+        <v>-19.87</v>
       </c>
       <c r="I27">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J27" t="s">
         <v>71</v>
@@ -1537,7 +1537,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28">
-        <v>1610612763</v>
+        <v>1610612762</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
@@ -1546,22 +1546,22 @@
         <v>67</v>
       </c>
       <c r="D28">
-        <v>0.5865</v>
+        <v>0.593</v>
       </c>
       <c r="E28">
-        <v>30.87</v>
+        <v>30.39</v>
       </c>
       <c r="F28">
-        <v>1363.7</v>
+        <v>1306.2</v>
       </c>
       <c r="G28">
-        <v>-6.83</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="H28">
-        <v>-19.87</v>
+        <v>-13.15</v>
       </c>
       <c r="I28">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J28" t="s">
         <v>71</v>
@@ -1581,10 +1581,10 @@
         <v>68</v>
       </c>
       <c r="D29">
-        <v>0.5427999999999999</v>
+        <v>0.5507</v>
       </c>
       <c r="E29">
-        <v>27.85</v>
+        <v>28.16</v>
       </c>
       <c r="F29">
         <v>1314.3</v>
@@ -1596,7 +1596,7 @@
         <v>-8.25</v>
       </c>
       <c r="I29">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J29" t="s">
         <v>71</v>
@@ -1616,10 +1616,10 @@
         <v>69</v>
       </c>
       <c r="D30">
-        <v>0.5214</v>
+        <v>0.5282</v>
       </c>
       <c r="E30">
-        <v>26.1</v>
+        <v>26.37</v>
       </c>
       <c r="F30">
         <v>1248.5</v>
@@ -1631,7 +1631,7 @@
         <v>-14.92</v>
       </c>
       <c r="I30">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J30" t="s">
         <v>71</v>
@@ -1651,10 +1651,10 @@
         <v>70</v>
       </c>
       <c r="D31">
-        <v>0.5024</v>
+        <v>0.5084</v>
       </c>
       <c r="E31">
-        <v>25.35</v>
+        <v>25.56</v>
       </c>
       <c r="F31">
         <v>1286.6</v>
@@ -1666,7 +1666,7 @@
         <v>-14.6</v>
       </c>
       <c r="I31">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J31" t="s">
         <v>71</v>
